--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -10176,6 +10176,21 @@
           <t>12.05.1992</t>
         </is>
       </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>UM+1174926</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>29-maktab</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="T86" t="inlineStr">
         <is>
           <t>91-957-18-58</t>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y179"/>
+  <dimension ref="A1:Y180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -5817,6 +5817,11 @@
           <t>26-03</t>
         </is>
       </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -10303,7 +10308,7 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -10408,7 +10413,7 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10518,7 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -13374,7 +13379,7 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -16916,6 +16921,11 @@
           <t>26-04</t>
         </is>
       </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -18860,6 +18870,11 @@
           <t>26-04</t>
         </is>
       </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -20593,6 +20608,11 @@
           <t>26-06</t>
         </is>
       </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20683,6 +20703,11 @@
           <t>26-06</t>
         </is>
       </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20771,6 +20796,81 @@
       <c r="W179" t="inlineStr">
         <is>
           <t>26-03</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Qulmatova Shabbona</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Qulmatova Shabbona</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -20823,30 +20823,21 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
           <t>Qulmatova Shabbona</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr">
         <is>
           <t>Yo'q</t>
         </is>
       </c>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
@@ -20857,7 +20848,11 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="T180" t="inlineStr"/>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>778338272</t>
+        </is>
+      </c>
       <c r="U180" t="inlineStr">
         <is>
           <t>TOPILDI</t>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -20828,14 +20828,49 @@
           <t>29.09.2026</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Azamat+qizi</t>
+        </is>
+      </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona</t>
+          <t>Qulmatova Shabbona Azamat+qizi</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>AE+4905104</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>61008085680019</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>05.11.2025</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>10.08.2008</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
           <t>Yo'q</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>UM+03730102</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>70-maktab</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -10183,7 +10183,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>UM+1174926</t>
+          <t>UM 1174926</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -20830,17 +20830,17 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Azamat+qizi</t>
+          <t>Azamat qizi</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Qulmatova Shabbona Azamat+qizi</t>
+          <t>Qulmatova Shabbona Azamat qizi</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>AE+4905104</t>
+          <t>AE4905104</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -20865,7 +20865,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>UM+03730102</t>
+          <t>UM 03730102</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y180"/>
+  <dimension ref="A1:Y181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20901,6 +20901,92 @@
       <c r="Y180" t="inlineStr">
         <is>
           <t>KUTILMOQDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Irgasheva Dinora</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Shodmon qizi</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Irgasheva Dinora Shodmon qizi</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>AC 2430931</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>60106035590029</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>15.11.2019</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>01.06.2003</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>UM 0441030</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>26-02</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y181"/>
+  <dimension ref="A1:Y182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20923,8 +20923,6 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
           <t>Shodmon qizi</t>
@@ -20955,14 +20953,11 @@
           <t>01.06.2003</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr">
         <is>
           <t>UM 0441030</t>
         </is>
       </c>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr">
         <is>
           <t>Umumiy o'rta maktab</t>
@@ -20973,7 +20968,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -20985,6 +20979,96 @@
         </is>
       </c>
       <c r="W181" t="inlineStr">
+        <is>
+          <t>26-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Shonazarova Vazira</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Botir qizi</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Shonazarova Vazira Botir qizi</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>AE 4233482</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>61311085680032</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>17.09.2025</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>13.11.2008</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>UM 03730412</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>78-maktab</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
         <is>
           <t>26-02</t>
         </is>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -20958,6 +20958,11 @@
           <t>UM 0441030</t>
         </is>
       </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>14-maktab</t>
+        </is>
+      </c>
       <c r="R181" t="inlineStr">
         <is>
           <t>Umumiy o'rta maktab</t>
@@ -21003,8 +21008,6 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
           <t>Botir qizi</t>
@@ -21035,13 +21038,11 @@
           <t>13.11.2008</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr">
         <is>
           <t>UM 03730412</t>
         </is>
       </c>
-      <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr">
         <is>
           <t>78-maktab</t>
@@ -21057,7 +21058,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr">
         <is>
           <t>TOPILDI</t>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y182"/>
+  <dimension ref="A1:Y183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21069,6 +21069,104 @@
         </is>
       </c>
       <c r="W182" t="inlineStr">
+        <is>
+          <t>26-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Samatova Oydin</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Sulaymon qizi</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Samatova Oydin Sulaymon qizi</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>AD8980430</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>42910905720012</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>11.10.2024</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>29.10.1990</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>OR-SH 0346677</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>91-219-20-99</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
         <is>
           <t>26-02</t>
         </is>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -20985,7 +20985,7 @@
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-06</t>
         </is>
       </c>
     </row>
@@ -21098,7 +21098,6 @@
           <t>146</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
           <t>Sulaymon qizi</t>
@@ -21129,13 +21128,11 @@
           <t>29.10.1990</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr">
         <is>
           <t>OR-SH 0346677</t>
         </is>
       </c>
-      <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr">
         <is>
           <t>Chiroqchi tuman 1-sonli ixtisoslashtirilgan maktab-internati</t>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y183"/>
+  <dimension ref="A1:Y184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21164,6 +21164,100 @@
         </is>
       </c>
       <c r="W183" t="inlineStr">
+        <is>
+          <t>26-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Nurillayeva Dilsuz</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Mashrabovna</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Nurillayeva Dilsuz Mashrabovna</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>AD4774693</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>42506912640010</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>05.10.2023</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>25.06.1991</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>K 1607691</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Kitob iqtisodiyot kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
         <is>
           <t>26-02</t>
         </is>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y184"/>
+  <dimension ref="A1:AA236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,6 +545,16 @@
           <t>Operator Tasdig'i</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Buyruq raqami</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Buyruq sanasi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -21193,7 +21203,6 @@
           <t>326</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
           <t>Mashrabovna</t>
@@ -21224,13 +21233,11 @@
           <t>25.06.1991</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr">
         <is>
           <t>K 1607691</t>
         </is>
       </c>
-      <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr">
         <is>
           <t>Kitob iqtisodiyot kasb-hunar kolleji</t>
@@ -21246,7 +21253,6 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -21260,6 +21266,4146 @@
       <c r="W184" t="inlineStr">
         <is>
           <t>26-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Abdixakimova Xurshida</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Abdixakim qizi</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Abdixakimova Xurshida Abdixakim qizi</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>AD2941659</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>60409065590039</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>04.04.2023</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>04.09.2006</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>UM 02174088</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>37-maktab</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>913200125 / 914581809</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 24-11</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>T-47</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Abdukarimova Nafosat</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Faxriddin qizi</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Abdukarimova Nafosat Faxriddin qizi</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>AD9031421</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>60205075590070</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>16.10.2024</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>02.05.2007</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>UM 03297283</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>18-maktab</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>906881531</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-22</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>T-29</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>25.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Abduvaliyeva Jasmina</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Erkin qizi</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Abduvaliyeva Jasmina Erkin qizi</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>AD8057487</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>61311075590048</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>30.07.2024</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>13.11.2007</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>UM 03452908</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>29-sonli ayrim fanlar chuqurlashtirilgan maktab</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>779992813</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>T-30/1</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Azizova Asila</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Bahodirxon qizi</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Azizova Asila Bahodirxon qizi</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>AE3401779</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>42412955590060</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>15.07.2025</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>24.12.1995</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>K 4626563</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Shahrisabz iqtisodiyot kolleji</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>919582758</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-19</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>T-32</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>14.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Baxtiyorova Dinora</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Akmal qizi</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Baxtiyorova Dinora Akmal qizi</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>AD7645847</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>62307075680084</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>27.06.2024</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>23.07.2007</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>PT 0017689</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>2-sonli politexnikum</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr"/>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-18</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>T-26</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>12.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Mahmudjonova Mohinur</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Sanjar qizi</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Mahmudjonova Mohinur Sanjar qizi</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>AD4538974</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>62504065680035</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>08.09.2023</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>25.04.2006</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>UM 02289977</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>290-maktab</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr"/>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>T-45</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>22.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Mahmudova Vasila</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Hujjat qizi</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Mahmudova Vasila Hujjat qizi</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>AD9687160</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>62206075680112</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>04.12.2024</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>22.06.2007</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>UM 03275718</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>81-maktab</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr"/>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>T-36</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>01.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Nasimova Durdona</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Yormahmat qizi</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Nasimova Durdona Yormahmat qizi</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>62605065680039</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>26.05.2006</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="T192" t="inlineStr"/>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 201 (24-11)</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>T-06</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>28.10.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Nishonova Hilola</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Faxriddin qizi</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Nishonova Hilola Faxriddin qizi</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>AD2578567</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>60205055720048</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>14.02.2023</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>02.05.2005</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>UM 01890968</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>24-maktab</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>914662205</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-19</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>T-33</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>14.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Nomazova Rayhona</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Murodullo qizi</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Nomazova Rayhona Murodullo qizi</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>AD9665620</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>62702075630033</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>03.12.2024</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>27.02.2007</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>UM 03287195</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>70-maktab</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr"/>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>T-44</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Norboboyeva Zahro</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Nuriddin qizi</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Norboboyeva Zahro Nuriddin qizi</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>61107075680027</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>11.07.2007</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+      <c r="T195" t="inlineStr"/>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 203 (24-13)</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>T-11</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>29.11.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Omonova Dilorom</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Toshkent qizi</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Omonova Dilorom Toshkent qizi</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+      <c r="T196" t="inlineStr"/>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 24-12</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>T-20</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>23.02.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Otaqulova Moxiniso</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Tursunpo'lat qizi</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Otaqulova Moxiniso Tursunpo'lat qizi</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>60703055720061</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>07.03.2005</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+      <c r="T197" t="inlineStr"/>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 201 (24-11)</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>T-07</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>28.10.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Qurbonova Gulida</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Xusan qizi</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Qurbonova Gulida Xusan qizi</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>AB3682339</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>41207975590067</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>07.04.2016</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>12.07.1997</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>K 4165742</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>2-Shahrisabz xizmat ko'rsatish kolleji</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>886949700</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-20</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>T-35</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>18.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Raimova Zulfizar</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Rasulovna</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Raimova Zulfizar Rasulovna</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>AD4408617</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>41007872560088</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>10.07.1987</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>10.07.1987</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>K 5489037</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Yakkabog' qurulish sanoat kolleji</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr"/>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-16</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>T-34</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Sayfilloyeva Anisa</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Jamshidzoda</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sayfilloyeva Anisa Jamshidzoda</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>AD8565644</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>61908085680094</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>10.09.2024</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>19.08.2008</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>UM 03275869</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>89-maktab</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr"/>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>T-22</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Sayfiyeva Parizod</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Zafarovna</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Sayfiyeva Parizod Zafarovna</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>AD2082802</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>60601065680048</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>25.11.2022</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>06.01.2006</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>UM 02151494</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>53-maktab</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr"/>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-21</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr"/>
+      <c r="AA201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Sayfullayeva Kumush</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Lutfullo qizi</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Sayfullayeva Kumush Lutfullo qizi</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>AD1789847</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>62009055680038</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>22.09.2022</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>20.09.2005</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>UM 01903229</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>82-maktab</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>887040920 / 975878105</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 24-13</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>T-30</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Shodiyeva Fayyoza</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Farxod qizi</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Shodiyeva Fayyoza Farxod qizi</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>60706065590040</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>07.06.2006</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="T203" t="inlineStr"/>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 204 (24-14)</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr"/>
+      <c r="AA203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>To'rayeva Elsenora</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Sobir qizi</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>To'rayeva Elsenora Sobir qizi</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
+      <c r="T204" t="inlineStr"/>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 24-12</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>T-21</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>23.02.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Uroqova Muslima</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Anvar qizi</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Uroqova Muslima Anvar qizi</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>AD6021065</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>61611065720061</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>05.02.2024</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>16.11.2006</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>UM 02140025</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>24-maktab</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>919579806 / 906750477</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 24-14</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr"/>
+      <c r="AA205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Usmonjonova Marjona</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Dilshod qizi</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Usmonjonova Marjona Dilshod qizi</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>AC0170536</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>61605025680021</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>09.11.2018</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>16.05.2002</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>D 0098091</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Qishloq xo'jalik kolleji</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>884901605 / 908787811</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 24-12</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr"/>
+      <c r="AA206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Xusanboyeva Fotimaxon</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Baxtiyor qizi</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Xusanboyeva Fotimaxon Baxtiyor qizi</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>AD4614901</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>60805045930053</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>15.09.2023</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>08.05.2004</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>UM 1347858</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>22-maktab</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr"/>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>T-30/2</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Yusupova Asila</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Yusupova Asila Iskandar qizi</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>AD0311873</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>61007015680048</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>13.04.2021</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>10.07.2001</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>UM 0085864</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>51-maktab</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr"/>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-20</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>Akademik ta'til olganlar</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>T-25</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Abdialimova Nilufar</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Akbar qizi</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Abdialimova Nilufar Akbar qizi</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>AD0968690</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>60908045720047</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>07.01.2022</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>09.08.2004</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>UM 1306544</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>3-maktab</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr"/>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 25-16</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>T-23</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>02.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Baxtiyorova Fotima</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Zarif qizi</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Baxtiyorova Fotima Zarif qizi</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>AD9120079</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>60510075680079</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>23.10.2024</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>05.10.2007</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>UM 03273958</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>22-maktab</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr"/>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>G'abborova Xosiyat</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Nosir qizi</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>G'abborova Xosiyat Nosir qizi</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>AD8770653</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>61011065630054</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>25.09.2024</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>10.11.2006</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>UM 03287373</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>78-maktab</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>974295606</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Hasanova Gulsevar</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Lochinbek qizi</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Hasanova Gulsevar Lochinbek qizi</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>61204065730042</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>12.04.2006</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
+      <c r="T212" t="inlineStr"/>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 202 (24-12)</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>T-09</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>30.10.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Jabborova Anora</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Nuriddin qizi</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Jabborova Anora Nuriddin qizi</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>AD8537425</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>62009075720031</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>09.09.2024</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>20.09.2007</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>UM 03264707</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>58-maktab</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr"/>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>T-37</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Jumanova Xolinisa</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Orif qizi</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Jumanova Xolinisa Orif qizi</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>AD9356181</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>60904075730067</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>11.11.2024</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>09.04.2007</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>UM 03300691</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>50-maktab</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>957022572</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>T-40</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Jumayeva Xurshida</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Safar qizi</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Jumayeva Xurshida Safar qizi</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>61201045630052</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>12.01.2004</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
+      <c r="T215" t="inlineStr"/>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 204 (24-14)</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr"/>
+      <c r="AA215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Mahmudova Munisa</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Mahsudjonovna</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Mahmudova Munisa Mahsudjonovna</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>62206055590013</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>22.06.2005</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="T216" t="inlineStr"/>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 205 (24-15)</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>30.10.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Meyliqulova Sabrina</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Baxtiyor qizi</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Meyliqulova Sabrina Baxtiyor qizi</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>AD8641562</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>61709075590063</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>16.09.2024</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>17.09.2007</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>UM 03296986</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>10-maktab</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr"/>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-16</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>T-24</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>02.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Numonova Feruza</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Mirhomid qizi</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Numonova Feruza Mirhomid qizi</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>62808027890020</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>28.08.2002</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
+      <c r="T218" t="inlineStr"/>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 203 (24-13)</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>T-05</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>13.10.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Omonova Sumbula</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Farxod qizi</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Omonova Sumbula Farxod qizi</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>AD1292785</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>60404055590037</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>23,04,2022</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>UM 01924159</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>36-sonli ayrim fanlar chuqur o'rgatiladigan ixtisoslashtirilgan maktab</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>779845421</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Qarshiyeva Ruxshona</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Otabek qizi</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Qarshiyeva Ruxshona Otabek qizi</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>AD8751204</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>60512075590040</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>24.09.2024</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>05.12.2007</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>PT 0256788</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>1-sonli politexnikum</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>918157227</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Salimova Zarina</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Sobirjon qizi</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Salimova Zarina Sobirjon qizi</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>AD8890500</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>42110975590034</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>07.10.2024</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>21.10.1997</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>K 4174786</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Shahrisabz yengil sanoat va xizmat ko'rsatish kolleji</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>880019709 / 916340177</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 24-15</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>T-27</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>18.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Saydaliyeva Sevinch</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Alimdjan qizi</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Saydaliyeva Sevinch Alimdjan qizi</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>AD3193422</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>60904075590012</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>03.05.2023</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>09.04.2007</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>PT 0176960</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Sharisabz shahar 2-sonli kasb-hunar maktabi</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-20</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr"/>
+      <c r="AA222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Soliyeva E'zoza</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Sherbobo qizi</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Soliyeva E'zoza Sherbobo qizi</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>AD4615905</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>61803065680094</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>15.09.2023</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>18.03.2006</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>UM 02151153</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>44-maktab</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr"/>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Suyunova Marjona</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Ravshan qizi</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Suyunova Marjona Ravshan qizi</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>60704065720162</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>07.04.2006</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr"/>
+      <c r="T224" t="inlineStr"/>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 202 (24-12)</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr"/>
+      <c r="AA224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Suyunova Ruxshona</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Karimjon qizi</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Suyunova Ruxshona Karimjon qizi</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>61405065680104</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>14.05.2006</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
+      <c r="T225" t="inlineStr"/>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 203 (24-13)</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>T-12</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>29.11.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Suyunova Shaxlo</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Tohir qizi</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Suyunova Shaxlo Tohir qizi</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>61305065720094</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>13.05.2006</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr"/>
+      <c r="T226" t="inlineStr"/>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr"/>
+      <c r="AA226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>To'xtayeva Shirida</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Sirojiddin qizi</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>To'xtayeva Shirida Sirojiddin qizi</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>AD1403124</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>61906055680059</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>30.05.2022</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>19.06.2005</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>UM 1296145</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>7-maktab</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>990598714</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Toshkentova Sevinchoy</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Zayniddin qizi</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Toshkentova Sevinchoy Zayniddin qizi</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>AD6867124</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>60505075730035</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>18.04.2024</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>05.05.2007</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>UM 03301249</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>72-maktab</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr"/>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Tug'izova Zahro</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Tohir qizi</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Tug'izova Zahro Tohir qizi</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>62912005590041</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>29.12.2000</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr"/>
+      <c r="T229" t="inlineStr"/>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 205 (24-15)</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>T-08</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>30.10.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Tursunova Sevinch</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Turg'un qizi</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Tursunova Sevinch Turg'un qizi</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>61905075680098</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>19.05.2007</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr"/>
+      <c r="T230" t="inlineStr"/>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr"/>
+      <c r="AA230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Usmonova Jasmina</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Nodir qizi</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Usmonova Jasmina Nodir qizi</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>AD9134105</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>62712075590017</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>24.10.2024</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>27.12.2007</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>UM 03298099</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>45-maktab</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>919603730</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>T-13</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>16.12.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Usmonova Shabbona</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Botir qizi</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Usmonova Shabbona Botir qizi</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>AD9713077</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>61412075590059</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>06.12.2024</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>14.12.2007</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>UM 03295752</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>7-maktab</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>505890781</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Xamrayeva Niginabonu</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Jamshid qizi</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Xamrayeva Niginabonu Jamshid qizi</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>AD9506052</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>61508075590121</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>21,11,2024</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>UM 03295886</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>10-maktab</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr"/>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Yoqubova Maftuna</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Hushvaqt qizi</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Yoqubova Maftuna Hushvaqt qizi</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>AE2747402</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>40312902560107</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>20,05,2025</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>K 1234480</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>Miroqi sport pedagogika kolleji</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr"/>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Yuldosheva Iroda</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Hasanovna</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Yuldosheva Iroda Hasanovna</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>AB7535578</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>40108945590034</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>22,08,2017</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>K 2404534</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>Shahrisabz pedagogika kolleji</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr"/>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Ziyadullayeva Zahro</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Ubaydullo qizi</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Ziyadullayeva Zahro Ubaydullo qizi</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>AD8888020</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>62609075590027</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>07,10,2024</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>UM 03295463</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>1-maktab</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>972904017</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>T-14/T-15</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>20.01.2026/21.01.2026</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -33093,7 +33093,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T334" t="inlineStr"/>
       <c r="V334" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -33889,7 +33888,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T344" t="inlineStr"/>
       <c r="V344" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34045,7 +34043,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T346" t="inlineStr"/>
       <c r="V346" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34121,7 +34118,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T347" t="inlineStr"/>
       <c r="V347" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34197,7 +34193,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T348" t="inlineStr"/>
       <c r="V348" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34353,7 +34348,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T350" t="inlineStr"/>
       <c r="V350" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34429,7 +34423,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T351" t="inlineStr"/>
       <c r="V351" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34505,7 +34498,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T352" t="inlineStr"/>
       <c r="V352" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34661,7 +34653,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T354" t="inlineStr"/>
       <c r="V354" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34817,7 +34808,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T356" t="inlineStr"/>
       <c r="V356" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34893,7 +34883,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T357" t="inlineStr"/>
       <c r="V357" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35049,7 +35038,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T359" t="inlineStr"/>
       <c r="V359" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35125,7 +35113,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T360" t="inlineStr"/>
       <c r="V360" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35441,7 +35428,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T364" t="inlineStr"/>
       <c r="V364" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35597,7 +35583,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T366" t="inlineStr"/>
       <c r="V366" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35673,7 +35658,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T367" t="inlineStr"/>
       <c r="V367" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35829,7 +35813,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T369" t="inlineStr"/>
       <c r="V369" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36065,7 +36048,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T372" t="inlineStr"/>
       <c r="V372" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36301,7 +36283,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T375" t="inlineStr"/>
       <c r="V375" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36537,7 +36518,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T378" t="inlineStr"/>
       <c r="V378" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36613,7 +36593,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T379" t="inlineStr"/>
       <c r="V379" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36849,7 +36828,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T382" t="inlineStr"/>
       <c r="V382" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36925,7 +36903,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T383" t="inlineStr"/>
       <c r="V383" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37161,7 +37138,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T386" t="inlineStr"/>
       <c r="V386" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37317,7 +37293,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T388" t="inlineStr"/>
       <c r="V388" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37393,7 +37368,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T389" t="inlineStr"/>
       <c r="V389" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37469,7 +37443,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T390" t="inlineStr"/>
       <c r="V390" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37625,7 +37598,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T392" t="inlineStr"/>
       <c r="V392" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37781,7 +37753,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T394" t="inlineStr"/>
       <c r="V394" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37857,7 +37828,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T395" t="inlineStr"/>
       <c r="V395" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38253,7 +38223,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T400" t="inlineStr"/>
       <c r="V400" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38409,7 +38378,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T402" t="inlineStr"/>
       <c r="V402" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38485,7 +38453,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T403" t="inlineStr"/>
       <c r="V403" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38561,7 +38528,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T404" t="inlineStr"/>
       <c r="V404" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38877,7 +38843,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T408" t="inlineStr"/>
       <c r="V408" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38953,7 +38918,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T409" t="inlineStr"/>
       <c r="V409" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39109,7 +39073,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T411" t="inlineStr"/>
       <c r="V411" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39425,7 +39388,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T415" t="inlineStr"/>
       <c r="V415" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39581,7 +39543,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T417" t="inlineStr"/>
       <c r="V417" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39657,7 +39618,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T418" t="inlineStr"/>
       <c r="V418" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39733,7 +39693,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T419" t="inlineStr"/>
       <c r="V419" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39809,7 +39768,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T420" t="inlineStr"/>
       <c r="V420" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39965,7 +39923,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T422" t="inlineStr"/>
       <c r="V422" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40121,7 +40078,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T424" t="inlineStr"/>
       <c r="V424" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40277,7 +40233,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T426" t="inlineStr"/>
       <c r="V426" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40513,7 +40468,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T429" t="inlineStr"/>
       <c r="V429" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40669,7 +40623,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T431" t="inlineStr"/>
       <c r="V431" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40825,7 +40778,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T433" t="inlineStr"/>
       <c r="V433" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40981,7 +40933,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T435" t="inlineStr"/>
       <c r="V435" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41137,7 +41088,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T437" t="inlineStr"/>
       <c r="V437" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41293,7 +41243,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T439" t="inlineStr"/>
       <c r="V439" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41449,7 +41398,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T441" t="inlineStr"/>
       <c r="V441" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41525,7 +41473,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T442" t="inlineStr"/>
       <c r="V442" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41601,7 +41548,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T443" t="inlineStr"/>
       <c r="V443" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -43037,7 +42983,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T461" t="inlineStr"/>
       <c r="V461" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -43273,7 +43218,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T464" t="inlineStr"/>
       <c r="V464" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -43349,7 +43293,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T465" t="inlineStr"/>
       <c r="V465" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -43425,7 +43368,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T466" t="inlineStr"/>
       <c r="V466" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -43741,7 +43683,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T470" t="inlineStr"/>
       <c r="V470" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44057,7 +43998,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T474" t="inlineStr"/>
       <c r="V474" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44133,7 +44073,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T475" t="inlineStr"/>
       <c r="V475" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44194,10 +44133,6 @@
           <t>27.04.1997</t>
         </is>
       </c>
-      <c r="O476" t="inlineStr"/>
-      <c r="Q476" t="inlineStr"/>
-      <c r="R476" t="inlineStr"/>
-      <c r="T476" t="inlineStr"/>
       <c r="V476" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44353,7 +44288,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T478" t="inlineStr"/>
       <c r="V478" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44429,7 +44363,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T479" t="inlineStr"/>
       <c r="V479" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44505,7 +44438,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T480" t="inlineStr"/>
       <c r="V480" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44581,7 +44513,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T481" t="inlineStr"/>
       <c r="V481" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44624,7 +44555,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>AB6959079</t>
+          <t>AD 4323840</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
@@ -44657,7 +44588,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T482" t="inlineStr"/>
       <c r="V482" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44733,7 +44663,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T483" t="inlineStr"/>
       <c r="V483" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44889,7 +44818,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T485" t="inlineStr"/>
       <c r="V485" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44965,7 +44893,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T486" t="inlineStr"/>
       <c r="V486" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45026,10 +44953,6 @@
           <t>31.01.1996</t>
         </is>
       </c>
-      <c r="O487" t="inlineStr"/>
-      <c r="Q487" t="inlineStr"/>
-      <c r="R487" t="inlineStr"/>
-      <c r="T487" t="inlineStr"/>
       <c r="V487" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45105,7 +45028,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T488" t="inlineStr"/>
       <c r="V488" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45341,7 +45263,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T491" t="inlineStr"/>
       <c r="V491" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45497,7 +45418,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T493" t="inlineStr"/>
       <c r="V493" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45573,7 +45493,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T494" t="inlineStr"/>
       <c r="V494" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45649,7 +45568,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T495" t="inlineStr"/>
       <c r="V495" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45805,7 +45723,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T497" t="inlineStr"/>
       <c r="V497" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45961,7 +45878,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T499" t="inlineStr"/>
       <c r="V499" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46117,7 +46033,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T501" t="inlineStr"/>
       <c r="V501" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46513,7 +46428,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T506" t="inlineStr"/>
       <c r="V506" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46589,7 +46503,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T507" t="inlineStr"/>
       <c r="V507" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46665,7 +46578,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T508" t="inlineStr"/>
       <c r="V508" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46741,7 +46653,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T509" t="inlineStr"/>
       <c r="V509" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47057,7 +46968,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T513" t="inlineStr"/>
       <c r="V513" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47133,7 +47043,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T514" t="inlineStr"/>
       <c r="V514" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47289,7 +47198,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T516" t="inlineStr"/>
       <c r="V516" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47605,7 +47513,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T520" t="inlineStr"/>
       <c r="V520" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47761,7 +47668,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T522" t="inlineStr"/>
       <c r="V522" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47917,7 +47823,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T524" t="inlineStr"/>
       <c r="V524" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48153,7 +48058,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T527" t="inlineStr"/>
       <c r="V527" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48219,7 +48123,6 @@
           <t>IM 000125</t>
         </is>
       </c>
-      <c r="Q528" t="inlineStr"/>
       <c r="R528" t="inlineStr">
         <is>
           <t>Umumiy o'rta maktab</t>
@@ -48305,7 +48208,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T529" t="inlineStr"/>
       <c r="V529" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48381,7 +48283,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T530" t="inlineStr"/>
       <c r="V530" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48457,7 +48358,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T531" t="inlineStr"/>
       <c r="V531" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48533,7 +48433,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T532" t="inlineStr"/>
       <c r="V532" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48609,7 +48508,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T533" t="inlineStr"/>
       <c r="V533" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48685,7 +48583,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T534" t="inlineStr"/>
       <c r="V534" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48761,7 +48658,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T535" t="inlineStr"/>
       <c r="V535" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48837,7 +48733,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T536" t="inlineStr"/>
       <c r="V536" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48913,7 +48808,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T537" t="inlineStr"/>
       <c r="V537" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48989,7 +48883,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T538" t="inlineStr"/>
       <c r="V538" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49065,7 +48958,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T539" t="inlineStr"/>
       <c r="V539" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49141,7 +49033,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T540" t="inlineStr"/>
       <c r="V540" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49202,10 +49093,6 @@
           <t>20.03.2002</t>
         </is>
       </c>
-      <c r="O541" t="inlineStr"/>
-      <c r="Q541" t="inlineStr"/>
-      <c r="R541" t="inlineStr"/>
-      <c r="T541" t="inlineStr"/>
       <c r="V541" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49281,7 +49168,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T542" t="inlineStr"/>
       <c r="V542" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49357,7 +49243,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T543" t="inlineStr"/>
       <c r="V543" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49433,7 +49318,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T544" t="inlineStr"/>
       <c r="V544" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49509,7 +49393,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T545" t="inlineStr"/>
       <c r="V545" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49665,7 +49548,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T547" t="inlineStr"/>
       <c r="V547" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49741,7 +49623,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T548" t="inlineStr"/>
       <c r="V548" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49882,10 +49763,6 @@
           <t>19.07.1995</t>
         </is>
       </c>
-      <c r="O550" t="inlineStr"/>
-      <c r="Q550" t="inlineStr"/>
-      <c r="R550" t="inlineStr"/>
-      <c r="T550" t="inlineStr"/>
       <c r="V550" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -50041,7 +49918,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T552" t="inlineStr"/>
       <c r="V552" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -50117,7 +49993,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T553" t="inlineStr"/>
       <c r="V553" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -50353,7 +50228,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T556" t="inlineStr"/>
       <c r="V556" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -50429,7 +50303,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T557" t="inlineStr"/>
       <c r="V557" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -8866,7 +8866,7 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -21345,7 +21345,7 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
@@ -21525,7 +21525,7 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
@@ -21785,7 +21785,7 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
@@ -21870,7 +21870,7 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
@@ -21930,7 +21930,7 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
@@ -22020,7 +22020,7 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
@@ -22105,7 +22105,7 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
@@ -22165,7 +22165,7 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
@@ -22215,7 +22215,7 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
@@ -22275,7 +22275,7 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
@@ -22450,7 +22450,7 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -22700,7 +22700,7 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
@@ -22890,7 +22890,7 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -22970,7 +22970,7 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -23045,7 +23045,7 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
@@ -23215,7 +23215,7 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
@@ -23390,7 +23390,7 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
@@ -23450,7 +23450,7 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
@@ -23535,7 +23535,7 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
@@ -23625,7 +23625,7 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
@@ -23820,7 +23820,7 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
@@ -23880,7 +23880,7 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
@@ -23965,7 +23965,7 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z219" t="inlineStr">
@@ -24055,7 +24055,7 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
@@ -24145,7 +24145,7 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
@@ -24235,7 +24235,7 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -24310,7 +24310,7 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z223" t="inlineStr">
@@ -24370,7 +24370,7 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -24420,7 +24420,7 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
@@ -24480,7 +24480,7 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -24560,7 +24560,7 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z227" t="inlineStr">
@@ -24645,7 +24645,7 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z228" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z229" t="inlineStr">
@@ -24765,7 +24765,7 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -24845,7 +24845,7 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z231" t="inlineStr">
@@ -24935,7 +24935,7 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z232" t="inlineStr">
@@ -25015,7 +25015,7 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z233" t="inlineStr">
@@ -25095,7 +25095,7 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z234" t="inlineStr">
@@ -25175,7 +25175,7 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z235" t="inlineStr">
@@ -25260,7 +25260,7 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="Z236" t="inlineStr">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25510,7 +25510,7 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25750,7 +25750,7 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25830,7 +25830,7 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -25990,7 +25990,7 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -26230,7 +26230,7 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26310,7 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -26470,7 +26470,7 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -26550,7 +26550,7 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -26630,7 +26630,7 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -26710,7 +26710,7 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -26790,7 +26790,7 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27030,7 +27030,7 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27190,7 +27190,7 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27270,7 +27270,7 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27430,7 +27430,7 @@
       </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27510,7 +27510,7 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27590,7 +27590,7 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27670,7 +27670,7 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27750,7 +27750,7 @@
       </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27910,7 +27910,7 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -27990,7 +27990,7 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28150,7 +28150,7 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28230,7 +28230,7 @@
       </c>
       <c r="Y273" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28390,7 +28390,7 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28470,7 +28470,7 @@
       </c>
       <c r="Y276" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="Y277" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28630,7 +28630,7 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28710,7 +28710,7 @@
       </c>
       <c r="Y279" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="Y280" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28870,7 +28870,7 @@
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="Y282" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="Y283" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29110,7 +29110,7 @@
       </c>
       <c r="Y284" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29190,7 +29190,7 @@
       </c>
       <c r="Y285" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="Y286" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29350,7 +29350,7 @@
       </c>
       <c r="Y287" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29430,7 +29430,7 @@
       </c>
       <c r="Y288" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="Y289" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29590,7 +29590,7 @@
       </c>
       <c r="Y290" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29670,7 +29670,7 @@
       </c>
       <c r="Y291" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="Y292" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29830,7 +29830,7 @@
       </c>
       <c r="Y293" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29910,7 +29910,7 @@
       </c>
       <c r="Y294" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="Y295" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -30070,7 +30070,7 @@
       </c>
       <c r="Y296" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -30150,7 +30150,7 @@
       </c>
       <c r="Y297" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="Y298" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -30310,7 +30310,7 @@
       </c>
       <c r="Y299" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -30390,7 +30390,7 @@
       </c>
       <c r="Y300" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="Y301" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -30550,7 +30550,7 @@
       </c>
       <c r="Y302" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -30630,7 +30630,7 @@
       </c>
       <c r="Y303" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="Y304" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="Y305" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -30870,7 +30870,7 @@
       </c>
       <c r="Y306" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -30950,7 +30950,7 @@
       </c>
       <c r="Y307" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31030,7 +31030,7 @@
       </c>
       <c r="Y308" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31110,7 +31110,7 @@
       </c>
       <c r="Y309" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="Y310" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31270,7 +31270,7 @@
       </c>
       <c r="Y311" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31350,7 +31350,7 @@
       </c>
       <c r="Y312" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="Y313" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31510,7 +31510,7 @@
       </c>
       <c r="Y314" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31590,7 +31590,7 @@
       </c>
       <c r="Y315" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="Y316" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31750,7 +31750,7 @@
       </c>
       <c r="Y317" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="Y318" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31910,7 +31910,7 @@
       </c>
       <c r="Y319" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -31990,7 +31990,7 @@
       </c>
       <c r="Y320" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="Y321" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="Y322" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -32230,7 +32230,7 @@
       </c>
       <c r="Y323" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -32310,7 +32310,7 @@
       </c>
       <c r="Y324" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="Y325" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="Y326" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -32550,7 +32550,7 @@
       </c>
       <c r="Y327" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="Y328" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -32710,7 +32710,7 @@
       </c>
       <c r="Y329" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -32790,7 +32790,7 @@
       </c>
       <c r="Y330" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="Y331" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -32950,7 +32950,7 @@
       </c>
       <c r="Y332" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -33030,7 +33030,7 @@
       </c>
       <c r="Y333" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -33105,7 +33105,7 @@
       </c>
       <c r="Y334" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -33185,7 +33185,7 @@
       </c>
       <c r="Y335" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -33265,7 +33265,7 @@
       </c>
       <c r="Y336" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -33345,7 +33345,7 @@
       </c>
       <c r="Y337" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -33425,7 +33425,7 @@
       </c>
       <c r="Y338" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -33505,7 +33505,7 @@
       </c>
       <c r="Y339" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -33585,7 +33585,7 @@
       </c>
       <c r="Y340" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -33665,7 +33665,7 @@
       </c>
       <c r="Y341" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -33745,7 +33745,7 @@
       </c>
       <c r="Y342" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -33825,7 +33825,7 @@
       </c>
       <c r="Y343" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -33900,7 +33900,7 @@
       </c>
       <c r="Y344" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -33980,7 +33980,7 @@
       </c>
       <c r="Y345" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -34055,7 +34055,7 @@
       </c>
       <c r="Y346" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -34130,7 +34130,7 @@
       </c>
       <c r="Y347" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -34205,7 +34205,7 @@
       </c>
       <c r="Y348" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -34285,7 +34285,7 @@
       </c>
       <c r="Y349" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -34360,7 +34360,7 @@
       </c>
       <c r="Y350" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -34435,7 +34435,7 @@
       </c>
       <c r="Y351" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -34510,7 +34510,7 @@
       </c>
       <c r="Y352" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -34590,7 +34590,7 @@
       </c>
       <c r="Y353" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -34665,7 +34665,7 @@
       </c>
       <c r="Y354" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -34745,7 +34745,7 @@
       </c>
       <c r="Y355" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -34820,7 +34820,7 @@
       </c>
       <c r="Y356" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -34895,7 +34895,7 @@
       </c>
       <c r="Y357" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -34975,7 +34975,7 @@
       </c>
       <c r="Y358" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35050,7 +35050,7 @@
       </c>
       <c r="Y359" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35125,7 +35125,7 @@
       </c>
       <c r="Y360" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35205,7 +35205,7 @@
       </c>
       <c r="Y361" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35285,7 +35285,7 @@
       </c>
       <c r="Y362" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="Y363" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35440,7 +35440,7 @@
       </c>
       <c r="Y364" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35520,7 +35520,7 @@
       </c>
       <c r="Y365" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="Y366" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35670,7 +35670,7 @@
       </c>
       <c r="Y367" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="Y368" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35825,7 +35825,7 @@
       </c>
       <c r="Y369" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35905,7 +35905,7 @@
       </c>
       <c r="Y370" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -35985,7 +35985,7 @@
       </c>
       <c r="Y371" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36060,7 +36060,7 @@
       </c>
       <c r="Y372" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36140,7 +36140,7 @@
       </c>
       <c r="Y373" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36220,7 +36220,7 @@
       </c>
       <c r="Y374" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36295,7 +36295,7 @@
       </c>
       <c r="Y375" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36375,7 +36375,7 @@
       </c>
       <c r="Y376" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36455,7 +36455,7 @@
       </c>
       <c r="Y377" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36530,7 +36530,7 @@
       </c>
       <c r="Y378" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36605,7 +36605,7 @@
       </c>
       <c r="Y379" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36685,7 +36685,7 @@
       </c>
       <c r="Y380" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36765,7 +36765,7 @@
       </c>
       <c r="Y381" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36840,7 +36840,7 @@
       </c>
       <c r="Y382" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36915,7 +36915,7 @@
       </c>
       <c r="Y383" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -36995,7 +36995,7 @@
       </c>
       <c r="Y384" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37075,7 +37075,7 @@
       </c>
       <c r="Y385" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37150,7 +37150,7 @@
       </c>
       <c r="Y386" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37230,7 +37230,7 @@
       </c>
       <c r="Y387" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37305,7 +37305,7 @@
       </c>
       <c r="Y388" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37380,7 +37380,7 @@
       </c>
       <c r="Y389" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37455,7 +37455,7 @@
       </c>
       <c r="Y390" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37535,7 +37535,7 @@
       </c>
       <c r="Y391" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37610,7 +37610,7 @@
       </c>
       <c r="Y392" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37690,7 +37690,7 @@
       </c>
       <c r="Y393" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37765,7 +37765,7 @@
       </c>
       <c r="Y394" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37840,7 +37840,7 @@
       </c>
       <c r="Y395" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="Y396" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38000,7 +38000,7 @@
       </c>
       <c r="Y397" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38080,7 +38080,7 @@
       </c>
       <c r="Y398" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38160,7 +38160,7 @@
       </c>
       <c r="Y399" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38235,7 +38235,7 @@
       </c>
       <c r="Y400" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38315,7 +38315,7 @@
       </c>
       <c r="Y401" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="Y402" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38465,7 +38465,7 @@
       </c>
       <c r="Y403" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38540,7 +38540,7 @@
       </c>
       <c r="Y404" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38620,7 +38620,7 @@
       </c>
       <c r="Y405" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38700,7 +38700,7 @@
       </c>
       <c r="Y406" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="Y407" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38855,7 +38855,7 @@
       </c>
       <c r="Y408" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -38930,7 +38930,7 @@
       </c>
       <c r="Y409" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39010,7 +39010,7 @@
       </c>
       <c r="Y410" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39085,7 +39085,7 @@
       </c>
       <c r="Y411" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39165,7 +39165,7 @@
       </c>
       <c r="Y412" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39245,7 +39245,7 @@
       </c>
       <c r="Y413" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39325,7 +39325,7 @@
       </c>
       <c r="Y414" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39400,7 +39400,7 @@
       </c>
       <c r="Y415" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39480,7 +39480,7 @@
       </c>
       <c r="Y416" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="Y417" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39630,7 +39630,7 @@
       </c>
       <c r="Y418" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39705,7 +39705,7 @@
       </c>
       <c r="Y419" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39780,7 +39780,7 @@
       </c>
       <c r="Y420" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39860,7 +39860,7 @@
       </c>
       <c r="Y421" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -39935,7 +39935,7 @@
       </c>
       <c r="Y422" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40015,7 +40015,7 @@
       </c>
       <c r="Y423" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40090,7 +40090,7 @@
       </c>
       <c r="Y424" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40170,7 +40170,7 @@
       </c>
       <c r="Y425" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40245,7 +40245,7 @@
       </c>
       <c r="Y426" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40325,7 +40325,7 @@
       </c>
       <c r="Y427" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40405,7 +40405,7 @@
       </c>
       <c r="Y428" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40480,7 +40480,7 @@
       </c>
       <c r="Y429" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40560,7 +40560,7 @@
       </c>
       <c r="Y430" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40635,7 +40635,7 @@
       </c>
       <c r="Y431" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40715,7 +40715,7 @@
       </c>
       <c r="Y432" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40790,7 +40790,7 @@
       </c>
       <c r="Y433" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40870,7 +40870,7 @@
       </c>
       <c r="Y434" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -40945,7 +40945,7 @@
       </c>
       <c r="Y435" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -41025,7 +41025,7 @@
       </c>
       <c r="Y436" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -41100,7 +41100,7 @@
       </c>
       <c r="Y437" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -41180,7 +41180,7 @@
       </c>
       <c r="Y438" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -41255,7 +41255,7 @@
       </c>
       <c r="Y439" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="Y440" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -41410,7 +41410,7 @@
       </c>
       <c r="Y441" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -41485,7 +41485,7 @@
       </c>
       <c r="Y442" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -41560,7 +41560,7 @@
       </c>
       <c r="Y443" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -41640,7 +41640,7 @@
       </c>
       <c r="Y444" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -41720,7 +41720,7 @@
       </c>
       <c r="Y445" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -41800,7 +41800,7 @@
       </c>
       <c r="Y446" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -41880,7 +41880,7 @@
       </c>
       <c r="Y447" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -41960,7 +41960,7 @@
       </c>
       <c r="Y448" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -42040,7 +42040,7 @@
       </c>
       <c r="Y449" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -42120,7 +42120,7 @@
       </c>
       <c r="Y450" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -42200,7 +42200,7 @@
       </c>
       <c r="Y451" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -42280,7 +42280,7 @@
       </c>
       <c r="Y452" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -42360,7 +42360,7 @@
       </c>
       <c r="Y453" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -42440,7 +42440,7 @@
       </c>
       <c r="Y454" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -42520,7 +42520,7 @@
       </c>
       <c r="Y455" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -42600,7 +42600,7 @@
       </c>
       <c r="Y456" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -42680,7 +42680,7 @@
       </c>
       <c r="Y457" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -42760,7 +42760,7 @@
       </c>
       <c r="Y458" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -42840,7 +42840,7 @@
       </c>
       <c r="Y459" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -42920,7 +42920,7 @@
       </c>
       <c r="Y460" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -42995,7 +42995,7 @@
       </c>
       <c r="Y461" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -43075,7 +43075,7 @@
       </c>
       <c r="Y462" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -43155,7 +43155,7 @@
       </c>
       <c r="Y463" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -43230,7 +43230,7 @@
       </c>
       <c r="Y464" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="Y465" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -43380,7 +43380,7 @@
       </c>
       <c r="Y466" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -43460,7 +43460,7 @@
       </c>
       <c r="Y467" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -43540,7 +43540,7 @@
       </c>
       <c r="Y468" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -43620,7 +43620,7 @@
       </c>
       <c r="Y469" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -43695,7 +43695,7 @@
       </c>
       <c r="Y470" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -43775,7 +43775,7 @@
       </c>
       <c r="Y471" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -43855,7 +43855,7 @@
       </c>
       <c r="Y472" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -43935,7 +43935,7 @@
       </c>
       <c r="Y473" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44010,7 +44010,7 @@
       </c>
       <c r="Y474" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44085,7 +44085,7 @@
       </c>
       <c r="Y475" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44145,7 +44145,7 @@
       </c>
       <c r="Y476" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44225,7 +44225,7 @@
       </c>
       <c r="Y477" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44300,7 +44300,7 @@
       </c>
       <c r="Y478" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44375,7 +44375,7 @@
       </c>
       <c r="Y479" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44450,7 +44450,7 @@
       </c>
       <c r="Y480" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44525,7 +44525,7 @@
       </c>
       <c r="Y481" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44600,7 +44600,7 @@
       </c>
       <c r="Y482" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44675,7 +44675,7 @@
       </c>
       <c r="Y483" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44755,7 +44755,7 @@
       </c>
       <c r="Y484" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44830,7 +44830,7 @@
       </c>
       <c r="Y485" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44905,7 +44905,7 @@
       </c>
       <c r="Y486" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -44965,7 +44965,7 @@
       </c>
       <c r="Y487" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -45040,7 +45040,7 @@
       </c>
       <c r="Y488" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -45120,7 +45120,7 @@
       </c>
       <c r="Y489" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -45200,7 +45200,7 @@
       </c>
       <c r="Y490" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -45275,7 +45275,7 @@
       </c>
       <c r="Y491" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -45355,7 +45355,7 @@
       </c>
       <c r="Y492" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -45430,7 +45430,7 @@
       </c>
       <c r="Y493" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -45505,7 +45505,7 @@
       </c>
       <c r="Y494" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -45580,7 +45580,7 @@
       </c>
       <c r="Y495" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -45660,7 +45660,7 @@
       </c>
       <c r="Y496" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -45735,7 +45735,7 @@
       </c>
       <c r="Y497" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -45815,7 +45815,7 @@
       </c>
       <c r="Y498" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -45890,7 +45890,7 @@
       </c>
       <c r="Y499" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -45970,7 +45970,7 @@
       </c>
       <c r="Y500" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -46045,7 +46045,7 @@
       </c>
       <c r="Y501" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -46125,7 +46125,7 @@
       </c>
       <c r="Y502" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -46205,7 +46205,7 @@
       </c>
       <c r="Y503" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -46285,7 +46285,7 @@
       </c>
       <c r="Y504" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -46365,7 +46365,7 @@
       </c>
       <c r="Y505" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -46440,7 +46440,7 @@
       </c>
       <c r="Y506" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="Y507" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -46590,7 +46590,7 @@
       </c>
       <c r="Y508" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -46665,7 +46665,7 @@
       </c>
       <c r="Y509" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -46745,7 +46745,7 @@
       </c>
       <c r="Y510" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -46825,7 +46825,7 @@
       </c>
       <c r="Y511" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -46905,7 +46905,7 @@
       </c>
       <c r="Y512" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -46980,7 +46980,7 @@
       </c>
       <c r="Y513" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -47055,7 +47055,7 @@
       </c>
       <c r="Y514" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -47135,7 +47135,7 @@
       </c>
       <c r="Y515" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -47210,7 +47210,7 @@
       </c>
       <c r="Y516" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -47290,7 +47290,7 @@
       </c>
       <c r="Y517" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -47370,7 +47370,7 @@
       </c>
       <c r="Y518" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -47450,7 +47450,7 @@
       </c>
       <c r="Y519" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -47525,7 +47525,7 @@
       </c>
       <c r="Y520" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -47605,7 +47605,7 @@
       </c>
       <c r="Y521" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -47680,7 +47680,7 @@
       </c>
       <c r="Y522" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -47760,7 +47760,7 @@
       </c>
       <c r="Y523" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -47835,7 +47835,7 @@
       </c>
       <c r="Y524" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -47915,7 +47915,7 @@
       </c>
       <c r="Y525" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -47995,7 +47995,7 @@
       </c>
       <c r="Y526" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -48070,7 +48070,7 @@
       </c>
       <c r="Y527" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -48145,7 +48145,7 @@
       </c>
       <c r="Y528" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -48220,7 +48220,7 @@
       </c>
       <c r="Y529" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -48295,7 +48295,7 @@
       </c>
       <c r="Y530" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -48370,7 +48370,7 @@
       </c>
       <c r="Y531" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -48445,7 +48445,7 @@
       </c>
       <c r="Y532" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -48520,7 +48520,7 @@
       </c>
       <c r="Y533" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -48595,7 +48595,7 @@
       </c>
       <c r="Y534" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -48670,7 +48670,7 @@
       </c>
       <c r="Y535" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -48745,7 +48745,7 @@
       </c>
       <c r="Y536" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -48820,7 +48820,7 @@
       </c>
       <c r="Y537" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -48895,7 +48895,7 @@
       </c>
       <c r="Y538" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -48970,7 +48970,7 @@
       </c>
       <c r="Y539" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -49045,7 +49045,7 @@
       </c>
       <c r="Y540" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -49105,7 +49105,7 @@
       </c>
       <c r="Y541" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -49180,7 +49180,7 @@
       </c>
       <c r="Y542" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -49255,7 +49255,7 @@
       </c>
       <c r="Y543" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -49330,7 +49330,7 @@
       </c>
       <c r="Y544" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -49405,7 +49405,7 @@
       </c>
       <c r="Y545" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -49485,7 +49485,7 @@
       </c>
       <c r="Y546" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -49560,7 +49560,7 @@
       </c>
       <c r="Y547" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -49635,7 +49635,7 @@
       </c>
       <c r="Y548" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -49715,7 +49715,7 @@
       </c>
       <c r="Y549" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -49775,7 +49775,7 @@
       </c>
       <c r="Y550" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -49855,7 +49855,7 @@
       </c>
       <c r="Y551" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -49930,7 +49930,7 @@
       </c>
       <c r="Y552" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -50005,7 +50005,7 @@
       </c>
       <c r="Y553" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -50085,7 +50085,7 @@
       </c>
       <c r="Y554" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -50165,7 +50165,7 @@
       </c>
       <c r="Y555" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -50240,7 +50240,7 @@
       </c>
       <c r="Y556" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -50315,7 +50315,7 @@
       </c>
       <c r="Y557" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -33963,6 +33963,11 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="T345" t="inlineStr">
         <is>
           <t>902890316</t>
@@ -39923,6 +39928,11 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
       <c r="V422" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40078,6 +40088,16 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>883823800 / 914510727</t>
+        </is>
+      </c>
       <c r="V424" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -43218,6 +43238,16 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>886341692 / 973868774</t>
+        </is>
+      </c>
       <c r="V464" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44073,6 +44103,16 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
+          <t>910702172 / 90008906</t>
+        </is>
+      </c>
       <c r="V475" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44133,6 +44173,31 @@
           <t>27.04.1997</t>
         </is>
       </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>K 6071373</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>Kitob sanoat va xizmat ko'rsatish kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>332079255 / 973816690</t>
+        </is>
+      </c>
       <c r="V476" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44288,6 +44353,16 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>973512025 / 905170817</t>
+        </is>
+      </c>
       <c r="V478" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44893,6 +44968,16 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="T486" t="inlineStr">
+        <is>
+          <t>906792298 / 912245369</t>
+        </is>
+      </c>
       <c r="V486" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44953,6 +45038,31 @@
           <t>31.01.1996</t>
         </is>
       </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>K 6070161</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>Kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="T487" t="inlineStr">
+        <is>
+          <t>500303196 / 973841481</t>
+        </is>
+      </c>
       <c r="V487" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45493,6 +45603,16 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="T494" t="inlineStr">
+        <is>
+          <t>951880530</t>
+        </is>
+      </c>
       <c r="V494" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48358,6 +48478,16 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="T531" t="inlineStr">
+        <is>
+          <t>912185816</t>
+        </is>
+      </c>
       <c r="V531" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48433,6 +48563,16 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="S532" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="T532" t="inlineStr">
+        <is>
+          <t>915979292 / 501118920</t>
+        </is>
+      </c>
       <c r="V532" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48508,6 +48648,16 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T533" t="inlineStr">
+        <is>
+          <t>505109703 / 873227515</t>
+        </is>
+      </c>
       <c r="V533" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48583,6 +48733,16 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T534" t="inlineStr">
+        <is>
+          <t>886323773 / 914708493</t>
+        </is>
+      </c>
       <c r="V534" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48733,6 +48893,16 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T536" t="inlineStr">
+        <is>
+          <t>918198931</t>
+        </is>
+      </c>
       <c r="V536" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49093,6 +49263,31 @@
           <t>20.03.2002</t>
         </is>
       </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>D 0094389</t>
+        </is>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>Sharisabz tuman Chorshanbe agrosanoat kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="T541" t="inlineStr">
+        <is>
+          <t>975895253 / 873225253</t>
+        </is>
+      </c>
       <c r="V541" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49243,6 +49438,16 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="S543" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="T543" t="inlineStr">
+        <is>
+          <t>881309088 / 935831388</t>
+        </is>
+      </c>
       <c r="V543" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49318,6 +49523,16 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="T544" t="inlineStr">
+        <is>
+          <t>918142047 / 888040008</t>
+        </is>
+      </c>
       <c r="V544" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49393,6 +49608,16 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="T545" t="inlineStr">
+        <is>
+          <t>913211605</t>
+        </is>
+      </c>
       <c r="V545" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49623,6 +49848,16 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="T548" t="inlineStr">
+        <is>
+          <t>883862204 / 887789709</t>
+        </is>
+      </c>
       <c r="V548" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49763,6 +49998,21 @@
           <t>19.07.1995</t>
         </is>
       </c>
+      <c r="Q550" t="inlineStr">
+        <is>
+          <t>Kasb-hunar kolleji</t>
+        </is>
+      </c>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T550" t="inlineStr">
+        <is>
+          <t>870350795 / 971997200</t>
+        </is>
+      </c>
       <c r="V550" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49918,6 +50168,16 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="S552" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="T552" t="inlineStr">
+        <is>
+          <t>916402192 / 883807881</t>
+        </is>
+      </c>
       <c r="V552" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49993,6 +50253,16 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="S553" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="T553" t="inlineStr">
+        <is>
+          <t>919634966 / 908988509</t>
+        </is>
+      </c>
       <c r="V553" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -50226,6 +50496,16 @@
       <c r="R556" t="inlineStr">
         <is>
           <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="T556" t="inlineStr">
+        <is>
+          <t>777350767 / 973550702</t>
         </is>
       </c>
       <c r="V556" t="inlineStr">

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA557"/>
+  <dimension ref="A1:AB557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +555,11 @@
           <t>Buyruq sanasi</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Bazaga kiritilganligi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB557"/>
+  <dimension ref="A1:AB560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50604,6 +50604,276 @@
         </is>
       </c>
     </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>557</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Abdiraimova Shahzoda</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>Dilshod qizi</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Abdiraimova Shahzoda Dilshod qizi</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>ABDIRAIMOVA SHAHZODA DILSHOD QIZI</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>AD8711360</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>61511075720098</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>20.09.2024</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>15.11.2007</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V558" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs</t>
+        </is>
+      </c>
+      <c r="W558" t="inlineStr">
+        <is>
+          <t>25-16</t>
+        </is>
+      </c>
+      <c r="X558" t="inlineStr">
+        <is>
+          <t>MOS (TO'LIQ)</t>
+        </is>
+      </c>
+      <c r="Y558" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="AB558" t="inlineStr">
+        <is>
+          <t>KIRITILDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>558</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Hayitova Xolida</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>Asad qizi</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Hayitova Xolida Asad qizi</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>HAYITOVA XOLIDA ASAD QIZI</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>AD5343254</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>61112065720083</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>06.12.2023</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>11.12.2006</t>
+        </is>
+      </c>
+      <c r="Q559" t="inlineStr">
+        <is>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V559" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs</t>
+        </is>
+      </c>
+      <c r="W559" t="inlineStr">
+        <is>
+          <t>25-16</t>
+        </is>
+      </c>
+      <c r="X559" t="inlineStr">
+        <is>
+          <t>MOS (TO'LIQ)</t>
+        </is>
+      </c>
+      <c r="Y559" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="AB559" t="inlineStr">
+        <is>
+          <t>KIRITILDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>559</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Shog'dorova Marjona</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>Eshtemir qizi</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>Shog'dorova Marjona Eshtemir qizi</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>SHOG'DOROVA MARJONA ESHTEMIR QIZI</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>AD9143185</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>63006075720080</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>24.10.2024</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>30.06.2007</t>
+        </is>
+      </c>
+      <c r="Q560" t="inlineStr">
+        <is>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V560" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs</t>
+        </is>
+      </c>
+      <c r="W560" t="inlineStr">
+        <is>
+          <t>25-16</t>
+        </is>
+      </c>
+      <c r="X560" t="inlineStr">
+        <is>
+          <t>MOS (TO'LIQ)</t>
+        </is>
+      </c>
+      <c r="Y560" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="AB560" t="inlineStr">
+        <is>
+          <t>KIRITILDI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB560"/>
+  <dimension ref="A1:AB563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50874,6 +50874,327 @@
         </is>
       </c>
     </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>560</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Tursunmurodova Diyora</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr"/>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>Jasur qizi</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>Tursunmurodova Diyora Jasur qizi</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>AD9513015</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>61609075680011</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>21.11.2024</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>16.09.2007</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>Mavjud</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>UM 03274052</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr"/>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati, Kitob tumani 25-sonli umumiy o'rta ta'lim maktabini</t>
+        </is>
+      </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="T561" t="inlineStr">
+        <is>
+          <t>887611310</t>
+        </is>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="W561" t="inlineStr">
+        <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="Y561" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="AB561" t="inlineStr">
+        <is>
+          <t>KIRITILDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>561</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Rashidova Shaxzoda</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr"/>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>Suyun qizi</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>Rashidova Shaxzoda Suyun qizi</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>AD6348784</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>61408075590081</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>04.03.2024</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>14.08.2007</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>Mavjud</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>UM 02171747</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr"/>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>Sesoni umumiy o'rta ta'lim maktabini</t>
+        </is>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="T562" t="inlineStr">
+        <is>
+          <t>94-806-00-14</t>
+        </is>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="W562" t="inlineStr">
+        <is>
+          <t>26-02</t>
+        </is>
+      </c>
+      <c r="Y562" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="AB562" t="inlineStr">
+        <is>
+          <t>KIRITILDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>562</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Rashidova Shaxzoda</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr"/>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>Suyun qizi</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>Rashidova Shaxzoda Suyun qizi</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>AD6348784</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>61408075590081</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>04.03.2024</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>14.08.2007</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>Mavjud</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>UM 02171747</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr"/>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>5-sonli umumiy o'rta ta'lim maktabini</t>
+        </is>
+      </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="S563" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>94-806-00-14</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="W563" t="inlineStr">
+        <is>
+          <t>24-15</t>
+        </is>
+      </c>
+      <c r="Y563" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+      <c r="AB563" t="inlineStr">
+        <is>
+          <t>KIRITILDI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB563"/>
+  <dimension ref="A1:AB562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50893,7 +50893,6 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E561" t="inlineStr"/>
       <c r="F561" t="inlineStr">
         <is>
           <t>30.09.2026</t>
@@ -50939,7 +50938,6 @@
           <t>UM 03274052</t>
         </is>
       </c>
-      <c r="P561" t="inlineStr"/>
       <c r="Q561" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati, Kitob tumani 25-sonli umumiy o'rta ta'lim maktabini</t>
@@ -51000,7 +50998,6 @@
           <t>To'lov qildi</t>
         </is>
       </c>
-      <c r="E562" t="inlineStr"/>
       <c r="F562" t="inlineStr">
         <is>
           <t>30.09.2026</t>
@@ -51046,10 +51043,9 @@
           <t>UM 02171747</t>
         </is>
       </c>
-      <c r="P562" t="inlineStr"/>
       <c r="Q562" t="inlineStr">
         <is>
-          <t>Sesoni umumiy o'rta ta'lim maktabini</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="R562" t="inlineStr">
@@ -51074,7 +51070,7 @@
       </c>
       <c r="W562" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>24-15</t>
         </is>
       </c>
       <c r="Y562" t="inlineStr">
@@ -51083,113 +51079,6 @@
         </is>
       </c>
       <c r="AB562" t="inlineStr">
-        <is>
-          <t>KIRITILDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="n">
-        <v>562</v>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>Rashidova Shaxzoda</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>Hamshiralik ishi - 3 yillik</t>
-        </is>
-      </c>
-      <c r="D563" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E563" t="inlineStr"/>
-      <c r="F563" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="G563" t="inlineStr">
-        <is>
-          <t>Suyun qizi</t>
-        </is>
-      </c>
-      <c r="H563" t="inlineStr">
-        <is>
-          <t>Rashidova Shaxzoda Suyun qizi</t>
-        </is>
-      </c>
-      <c r="J563" t="inlineStr">
-        <is>
-          <t>AD6348784</t>
-        </is>
-      </c>
-      <c r="K563" t="inlineStr">
-        <is>
-          <t>61408075590081</t>
-        </is>
-      </c>
-      <c r="L563" t="inlineStr">
-        <is>
-          <t>04.03.2024</t>
-        </is>
-      </c>
-      <c r="M563" t="inlineStr">
-        <is>
-          <t>14.08.2007</t>
-        </is>
-      </c>
-      <c r="N563" t="inlineStr">
-        <is>
-          <t>Mavjud</t>
-        </is>
-      </c>
-      <c r="O563" t="inlineStr">
-        <is>
-          <t>UM 02171747</t>
-        </is>
-      </c>
-      <c r="P563" t="inlineStr"/>
-      <c r="Q563" t="inlineStr">
-        <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabini</t>
-        </is>
-      </c>
-      <c r="R563" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="S563" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="T563" t="inlineStr">
-        <is>
-          <t>94-806-00-14</t>
-        </is>
-      </c>
-      <c r="U563" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="W563" t="inlineStr">
-        <is>
-          <t>24-15</t>
-        </is>
-      </c>
-      <c r="Y563" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
-        </is>
-      </c>
-      <c r="AB563" t="inlineStr">
         <is>
           <t>KIRITILDI</t>
         </is>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -676,6 +676,11 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>KIRITILDI</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -50020,7 +50020,7 @@
       </c>
       <c r="T550" t="inlineStr">
         <is>
-          <t>870350795 / 971997200</t>
+          <t>991234567</t>
         </is>
       </c>
       <c r="V550" t="inlineStr">

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -39955,7 +39955,7 @@
       </c>
       <c r="Y422" t="inlineStr">
         <is>
-          <t>TASDIQLANDI</t>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -40120,7 +40120,7 @@
       </c>
       <c r="Y424" t="inlineStr">
         <is>
-          <t>TASDIQLANDI</t>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -43265,7 +43265,7 @@
       </c>
       <c r="W464" t="inlineStr">
         <is>
-          <t>25-20</t>
+          <t>25-21</t>
         </is>
       </c>
       <c r="Y464" t="inlineStr">

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB562"/>
+  <dimension ref="A1:AB563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51089,6 +51089,104 @@
         </is>
       </c>
     </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>562</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Zaripova Setora</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>Zuxriddin qizi</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>Zaripova Setora Zuxriddin qizi</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>AD8594631</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>60609075730014</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>12.09.2024</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>06.09.2007</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr"/>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>UM 03299021</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr"/>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>1-sonli umumiy o'rta ta'lim maktabini</t>
+        </is>
+      </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="S563" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>773893666 / 606090757</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V563" t="inlineStr">
+        <is>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
+        </is>
+      </c>
+      <c r="W563" t="inlineStr">
+        <is>
+          <t>25-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -51080,7 +51080,7 @@
       </c>
       <c r="Y562" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
       <c r="AB562" t="inlineStr">
@@ -51113,7 +51113,6 @@
           <t>226</t>
         </is>
       </c>
-      <c r="F563" t="inlineStr"/>
       <c r="G563" t="inlineStr">
         <is>
           <t>Zuxriddin qizi</t>
@@ -51144,13 +51143,11 @@
           <t>06.09.2007</t>
         </is>
       </c>
-      <c r="N563" t="inlineStr"/>
       <c r="O563" t="inlineStr">
         <is>
           <t>UM 03299021</t>
         </is>
       </c>
-      <c r="P563" t="inlineStr"/>
       <c r="Q563" t="inlineStr">
         <is>
           <t>1-sonli umumiy o'rta ta'lim maktabini</t>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -51183,6 +51183,16 @@
           <t>25-17</t>
         </is>
       </c>
+      <c r="Y563" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="AB563" t="inlineStr">
+        <is>
+          <t>KIRITILMAGAN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>996810119 / 978550581</t>
+          <t>+998 88 848-08-27 / +998 97 855-05-81 (Onasi)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>918715737</t>
+          <t>+998 91 871-57-37</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>93-019-06-86</t>
+          <t>+998 93 019-06-86</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>97-110-03-25, 91-071-06-83</t>
+          <t>+998 88 710-03-25 / +998 88 471-06-83 (Onasi)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>919483879 / 885967179</t>
+          <t>+998 91 948-38-79 / +998 88 596-71-79 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>885888187 / 902433774</t>
+          <t>+998 90 243-37-74 / +998 88 588-81-87 (Onasi)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>875910918 / 885660802</t>
+          <t>+998 87 591-09-18 / +998 88 566-08-02 (Onasi)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>333890503 / 949791283</t>
+          <t>+998 33 389-05-03 / +998 94 979-12-83 (Otasi)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>700343131</t>
+          <t>+998 70 034-31-31 / +998 70 034-31-31 (O'zi)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1701,6 +1701,7 @@
           <t>2020</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -1823,7 +1824,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>953672602</t>
+          <t>+998 95 367-26-02 / +998 90 616-15-60 (Buvasi)</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1938,7 +1939,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>940790106</t>
+          <t>+998 94 079-01-06 / +998 93 513-75-74 (Otasi)</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2058,7 +2059,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>876360708 / 976363774</t>
+          <t>+998 87 636-07-08 / +998 97 636-37-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2168,7 +2169,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>886331318</t>
+          <t>+998 88 633-13-18</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2286,6 +2287,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>+998 70 120-22-08 / +998 70 125-22-08 (Onasi)</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -2403,7 +2409,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>991312508 / 880068282</t>
+          <t>+998 99 131-25-08 / +998 87 607-82-87 (Onasi)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2523,7 +2529,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>776021708 / 702191108</t>
+          <t>+998 77 602-17-08 / +998 70 219-11-08 (Otasi)</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2638,7 +2644,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>774231707 / 956162509</t>
+          <t>+998 77 432-17-07 / +998 95 616-35-09 (Onasi)</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2758,7 +2764,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>770629890</t>
+          <t>+998 77 062-98-90</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2868,7 +2874,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>883090228 / 886177808</t>
+          <t>+998 88 309-02-28 / +998 88 005-78-08 (Onasi)</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2974,7 +2980,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>887886042</t>
+          <t>+998 88 788-60-42 / +998 91 638-32-71 (Onasi)</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3089,7 +3095,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>914551195</t>
+          <t>+998 88 402-04-08 / +998 99 063-04-19 (Otasi)</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3209,7 +3215,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>881009504 / 976325574</t>
+          <t>+998 88 100-95-04 / +998 97 632-55-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3319,7 +3325,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>919490481</t>
+          <t>+998 91 988-15-08 / +998 91 949-04-81 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3439,7 +3445,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>886177860 / 914577860</t>
+          <t>+998 88 617-78-60 / +998 91 457-78-60 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3544,7 +3550,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>917090876</t>
+          <t>+998 91 709-08-76</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3664,7 +3670,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>906752661</t>
+          <t>+998 87 631-04-77 / +998 87 321-04-77 (Turmush o'rtog'i)</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3765,7 +3771,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>99-186-30-23 / 95-228-24-62</t>
+          <t>+998 99 186-30-23 / +998 99 186-30-23 (O'zi)</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3880,7 +3886,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>997307709</t>
+          <t>+998 70 518-05-60 / +998 99 730-77-09 (Onasi)</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3988,7 +3994,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>99-153-48-38 / 70-034-22-44</t>
+          <t>+998 99 153-48-38 / +998 70 034-22-44 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4108,7 +4114,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>880052965 / 874861208</t>
+          <t>+998 88 005-29-65 / +998 87 486-12-08 (Onasi)</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4223,7 +4229,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>887381981 / 957401981</t>
+          <t>+998 77 629-45-08 / +998 88 738-19-82 (Onasi)</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4326,6 +4332,7 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -4441,7 +4448,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>97-589-00-62 / 91-956-10-93</t>
+          <t>+998 97 589-00-62 / +998 91 956-10-93 (Onasi)</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4551,7 +4558,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>870102621</t>
+          <t>+998 87 010-26-21 / +998 97 701-17-83 (Onasi)</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4666,7 +4673,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>91-005-49-08, 93-553-33-51</t>
+          <t>+998 91 005-49-08 / +998 93 553-33-51 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4781,7 +4788,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>875681508</t>
+          <t>+998 87 568-15-08 / +998 88 585-70-68 (Otasi)</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4896,7 +4903,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>973350582 / 978635082</t>
+          <t>+998 97 335-05-82 / +998 97 863-50-82 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5021,7 +5028,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>914606562</t>
+          <t>+998 91 217-70-09 / +998 91 460-65-62 (Akasi)</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5136,7 +5143,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>908785105 / 916397685</t>
+          <t>+998 88 623-38-08 / +998 77 021-67-05 (Onasi)</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5256,7 +5263,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>973873803</t>
+          <t>+998 87 495-26-08 / +998 97 387-38-03 (Onasi)</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5364,7 +5371,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>952590625 / 991523371</t>
+          <t>+998 95 259-06-25 / +998 99 152-33-71 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5479,7 +5486,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>881151031 / 881840585</t>
+          <t>+998 88 115-10-31 / +998 88 184-05-85 (Onasi)</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5604,7 +5611,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>912174355</t>
+          <t>+998 91 217-43-55</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5719,7 +5726,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>99-526-47-09</t>
+          <t>+998 88 340-30-08 / +998 99 526-47-09 (Onasi)</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5829,7 +5836,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>873588797 / 886321972</t>
+          <t>+998 87 358-87-97 / +998 88 632-19-72 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -5939,7 +5946,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>936367986</t>
+          <t>+998 93 636-79-86</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6059,7 +6066,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>976180259</t>
+          <t>+998 97 618-02-59</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -6179,7 +6186,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>919524344 / 904422247</t>
+          <t>+998 91 952-43-44 / +998 90 442-22-47 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -6282,6 +6289,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>+998 50 011-14-09 / +998 97 389-11-74 (Onasi)</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -6399,7 +6411,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>918112208 / 918151309</t>
+          <t>+998 91 811-22-08 / +998 91 815-13-09 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6519,7 +6531,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>880880124</t>
+          <t>+998 88 088-01-24</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6639,7 +6651,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>950202813 / 950702813</t>
+          <t>+998 95 020-28-13 / +998 77 275-28-13 (Onasi)</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6754,7 +6766,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>97-857-74-04</t>
+          <t>+998 97 852-74-04 / +998 97 852-74-04 (O'zi)</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6869,7 +6881,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>999430596 / 959399205</t>
+          <t>+998 99 943-05-96 / +998 95 939-92-05 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6989,7 +7001,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>946034407 / 912138081</t>
+          <t>+998 94 603-44-07 / +998 90 301-50-78 (Otasi)</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7109,7 +7121,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>700349505 / 994688406</t>
+          <t>+998 70 034-95-05 / +998 99 468-84-06 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -7209,7 +7221,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>904403666 / 912204218</t>
+          <t>+998 90 440-36-66 / +998 91 224-77-21 (Turmush o'rtog'i)</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -7329,7 +7341,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>701206508 / 995698112</t>
+          <t>+998 70 120-65-08 / +998 99 569-81-12 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -7444,7 +7456,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>996739929 / 973194003</t>
+          <t>+998 99 673-99-29 / +998 99 673-99-29 (O'zi)</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7554,7 +7566,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>883848545</t>
+          <t>+998 88 384-85-45</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -7657,7 +7669,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>88-030-66-01+/+97-087-49-05</t>
+          <t>+998 88 494-38-00 / +998 88 044-98-02 (Yangasi)</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7777,7 +7789,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>332960708 / 881360926</t>
+          <t>+998 33 296-07-08 / +998 88 136-09-26 (Onasi)</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7887,7 +7899,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>943387727</t>
+          <t>+998 91 810-81-91 / +998 90 099-57-63 (Onasi)</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -8007,7 +8019,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>887326111 / 906176883</t>
+          <t>+998 88 732-61-11 / +998 90 617-68-83 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -8110,7 +8122,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>939034744</t>
+          <t>+998 50 450-42-40 / +998 93 903-47-44 (Onasi)</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -8220,7 +8232,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>912171430 / 941343403</t>
+          <t>+998 91 217-14-30 / +998 94 134-34-03 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -8338,6 +8350,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>+998 91 844-03-08 / +998 91 959-42-15 (Onasi)</t>
+        </is>
+      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -8453,7 +8470,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>505899948</t>
+          <t>+998 50 589-99-48 / +998 50 734-73-86 (Onasi)</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8571,6 +8588,11 @@
           <t>2019</t>
         </is>
       </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>+998 87 213-02-40 / +998 88 618-85-80 (O'zi)</t>
+        </is>
+      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -8686,6 +8708,11 @@
           <t>2012</t>
         </is>
       </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>+998 88 388-93-26 / +998 99 685-13-21 (O'zi)</t>
+        </is>
+      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -8796,7 +8823,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>— (bo‘sh)</t>
+          <t>+998 94 069-30-27 / +998 94 069-30-27 (O'zi)</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8854,6 +8881,7 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
+      <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -8976,7 +9004,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>883887912 / 877160130</t>
+          <t>+998 87 716-01-30 / +998 88 388-79-12 (Onasi)</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -9091,7 +9119,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>886030021</t>
+          <t>+998 88 817-96-08 / +998 95 075-30-86 (O'zi)</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -9211,7 +9239,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>900709579</t>
+          <t>+998 87 463-79-08 / +998 91 070-95-79 (Onasi)</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -9326,7 +9354,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>919490180 / 877511981</t>
+          <t>+998 87 751-19-81 / +998 91 949-01-80 (Onasi)</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -9439,7 +9467,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>88-803-91-93, 88-726-14-12</t>
+          <t>+998 88 803-91-93 / +998 88 726-14-12 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9552,6 +9580,7 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -9662,7 +9691,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>88-399-00-96</t>
+          <t>+998 88 399-00-96</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9787,7 +9816,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>876590027</t>
+          <t>+998 87 659-00-27 / +998 87 079-08-68 (Onasi)</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9895,7 +9924,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>70-188-54-32 / 95-805-01-86</t>
+          <t>+998 70 188-54-32 / +998 95 805-01-86 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -10003,7 +10032,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>99-168-20-82 / 77-042-74-06</t>
+          <t>+998 99 168-20-82 / +998 99 168-20-82 (Onasi)</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -10116,6 +10145,7 @@
           <t>2018</t>
         </is>
       </c>
+      <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr">
         <is>
           <t>To'liq</t>
@@ -10218,7 +10248,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>91-957-18-58</t>
+          <t>+998 91 957-18-58</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -10306,6 +10336,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>+998 91 071-02-83 / +998 91 071-02-83 (Onasi)</t>
+        </is>
+      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -10411,6 +10446,7 @@
           <t>2000</t>
         </is>
       </c>
+      <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -10516,6 +10552,7 @@
           <t>2008</t>
         </is>
       </c>
+      <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -10638,7 +10675,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>970012780 / 973157721</t>
+          <t>+998 87 800-66-37 / +998 97 001-27-80 (Onasi)</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10748,7 +10785,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>973889978 / 880407877</t>
+          <t>+998 97 388-99-78 / +998 90 877-55-86 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10868,7 +10905,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>509071311 / 500331311</t>
+          <t>+998 50 907-13-11 / +998 97 380-89-65 (Otasi)</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10988,7 +11025,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>975855793 / 776070824</t>
+          <t>+998 77 607-08-24 / +998 87 399-01-79 (Onasi)</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -11103,7 +11140,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>77-068-30-17</t>
+          <t>+998 95 153-84-08 / +998 99 128-49-80 (Onasi)</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -11228,7 +11265,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>992460829 / 701080829</t>
+          <t>+998 70 108-08-29 / +998 99 246-08-29 (Onasi)</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -11343,7 +11380,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>919491627 / 900698998</t>
+          <t>+998 91 949-16-27 / +998 90 069-89-98 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -11436,6 +11473,7 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -11548,7 +11586,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>888298280 / 883038280</t>
+          <t>+998 88 829-82-80 / +998 88 303-82-80 (Turmush o'rtog'i)</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -11656,7 +11694,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>99-524-08-10 / 95-524-81-80</t>
+          <t>+998 99 106-08-10 / +998 95 527-81-80 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11776,7 +11814,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>772131924 / 919584082</t>
+          <t>+998 77 213-19-24 / +998 91 548-40-82 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11896,7 +11934,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>876450108 / 990427984</t>
+          <t>+998 87 645-01-08 / +998 99 042-79-84 (Onasi)</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -12011,7 +12049,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>908841208</t>
+          <t>+998 90 884-12-08 / +998 91 957-27-17 (Akasi)</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -12121,7 +12159,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>873920025 / 873920021</t>
+          <t>+998 87 392-00-25 / +998 87 392-00-21 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -12241,7 +12279,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>933565022 / 910901627</t>
+          <t>+998 93 356-50-22 / +998 91 090-16-27 (Onasi)</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -12356,7 +12394,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>88-827-07-18, 88-386-04-85</t>
+          <t>+998 88 387-94-04 / +998 88 381-39-79 (Onasi)</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -12466,7 +12504,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>976188504</t>
+          <t>+998 95 465-64-08 / +998 97 618-85-04 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -12591,7 +12629,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>908785105 / 916397685</t>
+          <t>+998 90 878-51-05 / +998 91 639-76-85 (Otasi)</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -12711,7 +12749,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>503019503 / 997304804</t>
+          <t>+998 50 158-27-29 / +998 99 730-48-04 (Onasi)</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -12831,7 +12869,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>908788108</t>
+          <t>+998 90 878-81-08</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -12941,7 +12979,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>919595774</t>
+          <t>+998 91 959-57-71 / +998 91 959-57-71 (Onasi)</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -13054,6 +13092,7 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -13169,7 +13208,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>880632608, 973360140</t>
+          <t>+998 88 063-26-08 / +998 97 336-01-40 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -13289,7 +13328,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>773900314 / 779656308</t>
+          <t>+998 77 965-63-08 / +998 97 139-06-77 (Onasi)</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -13382,6 +13421,7 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -13494,7 +13534,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>976312909 / 953332960</t>
+          <t>+998 91 635-45-56 / +998 95 333-29-60 (Turmush o'rtog'i)</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -13607,6 +13647,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>+998 50 503-05-39 / +998 91 951-05-36 (Akasi)</t>
+        </is>
+      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>CHALA</t>
@@ -13724,7 +13769,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>885581535 / 886331535</t>
+          <t>+998 88 558-15-35 / +998 88 633-15-35 (Onasi)</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -13834,7 +13879,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>888191006 / 888606150</t>
+          <t>+998 88 860-61-50 / +998 90 877-61-50 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -13949,7 +13994,7 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>770578758 / 704897375</t>
+          <t>+998 70 489-73-75 / +998 77 057-87-58 (Onasi)</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -14069,7 +14114,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>93-152-25-77, 77-086-77-25</t>
+          <t>+998 93 152-25-77 / +998 77 086-77-25 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -14189,7 +14234,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>880001458 / 905176163</t>
+          <t>+998 88 000-14-58 / +998 90 517-61-63 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -14299,7 +14344,7 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>330578323 / 334248323</t>
+          <t>+998 70 478-09-27 / +998 33 057-83-23 (Onasi)</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -14419,7 +14464,7 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>885020703 / 880037679</t>
+          <t>+998 88 502-07-03 / +998 88 003-76-79 (Onasi)</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
@@ -14539,7 +14584,7 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>919614037 / 918021670</t>
+          <t>+998 91 802-16-70 / +998 91 961-40-37 (Onasi)</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -14659,7 +14704,7 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>200132207</t>
+          <t>+998 77 085-06-27 / +998 88 085-06-27 (Onasi)</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -14774,7 +14819,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>704785808</t>
+          <t>+998 70 478-58-08 / +998 88 753-84-86 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -14877,6 +14922,7 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -14980,7 +15026,7 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>908780280</t>
+          <t>+998 90 878-02-80 / +998 95 269-48-78 (Onasi)</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -15095,7 +15141,7 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>996152272</t>
+          <t>+998 87 941-19-20 / +998 99 615-22-72 (Turmush o'rtog'i)</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -15220,7 +15266,7 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>883367774 / 907163142</t>
+          <t>+998 88 336-77-74 / +998 90 716-31-42 (Onasi)</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -15330,7 +15376,7 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>955838858</t>
+          <t>+998 95 583-88-58 / +998 91 641-75-32 (Onasi)</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -15445,7 +15491,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>885890027 / 957701169</t>
+          <t>+998 88 868-99-08 / +998 95 770-11-69 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -15560,7 +15606,7 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>916499228 / 976015200</t>
+          <t>+998 91 464-92-28 / +998 88 601-52-00 (Onasi)</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -15675,7 +15721,7 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>908942471 / 919496471</t>
+          <t>+998 90 894-24-71 / +998 91 949-64-71 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -15795,7 +15841,7 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>971880757 / 973810757</t>
+          <t>+998 87 485-36-08 / +998 97 188-07-57 (Onasi)</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
@@ -15905,7 +15951,7 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>880115819</t>
+          <t>+998 88 011-58-19</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -16015,7 +16061,7 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>936031585 / 882651585</t>
+          <t>+998 87 561-08-88 / +998 93 603-15-85 (Onasi)</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -16135,7 +16181,7 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>770209066 / 991638468</t>
+          <t>+998 77 020-90-66 / +998 97 617-50-37 (Onasi)</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
@@ -16250,7 +16296,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>910707501 / 908698209</t>
+          <t>+998 91 070-75-01 / +998 90 869-82-09 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -16365,7 +16411,7 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>995658681</t>
+          <t>+998 95 939-07-05 / +998 99 143-79-03 (Otasi)</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -16480,7 +16526,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>919600814 / 912250767</t>
+          <t>+998 91 960-08-14 / +998 91 225-07-67 (Onasi)</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -16595,7 +16641,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>995658681</t>
+          <t>+998 77 809-81-30 / +998 99 565-86-81 (Onasi)</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -16710,7 +16756,7 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>995658681</t>
+          <t>+998 77 809-82-30 / +998 99 565-86-81 (Onasi)</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
@@ -16823,7 +16869,7 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>97-573-22-92</t>
+          <t>+998 97 573-22-92</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
@@ -16933,7 +16979,7 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>882633833</t>
+          <t>+998 77 029-02-74 / +998 88 263-38-33 (Onasi)</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
@@ -17043,7 +17089,7 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>880669272 / 952556670</t>
+          <t>+998 87 369-08-72 / +998 88 066-92-72 (Otasi)</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
@@ -17141,7 +17187,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>875615296 / 772322878</t>
+          <t>+998 87 561-52-96 / +998 77 232-28-78 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
@@ -17266,7 +17312,7 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>334948423 / 991840519</t>
+          <t>+998 33 494-84-23 / +998 33 494-84-23 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
@@ -17381,7 +17427,7 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>700720614 / 992558990</t>
+          <t>+998 70 072-06-14 / +998 95 774-15-64 (Onasi)</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
@@ -17489,7 +17535,7 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>970662692</t>
+          <t>+998 97 066-26-92</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
@@ -17614,7 +17660,7 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>870004608</t>
+          <t>+998 87 000-46-08 / +998 77 108-80-48 (Onasi)</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
@@ -17729,7 +17775,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>876310721 / 875280782</t>
+          <t>+998 87 631-07-21 / +998 87 528-07-82 (Onasi)</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -17842,7 +17888,7 @@
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>88-587-27-01 / 91-070-41-07</t>
+          <t>+998 88 587-27-01 / +998 88 490-68-72 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
@@ -17946,7 +17992,7 @@
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>87-116-03-03</t>
+          <t>+998 87 116-03-03 / +998 87 116-03-03 (Onasi)</t>
         </is>
       </c>
       <c r="U154" t="inlineStr">
@@ -18066,7 +18112,7 @@
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>888659008 / 881861712</t>
+          <t>+998 88 865-90-08 / +998 88 186-17-12 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U155" t="inlineStr">
@@ -18181,7 +18227,7 @@
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>772254208</t>
+          <t>+998 77 225-42-08 / +998 99 945-13-82 (Onasi)</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
@@ -18294,7 +18340,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>883851378, 884188278</t>
+          <t>+998 88 385-13-78 / +998 88 418-82-78 (Otasi)</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -18419,7 +18465,7 @@
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>997422473</t>
+          <t>+998 95 147-08-25 / +998 99 742-24-73 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U158" t="inlineStr">
@@ -18534,7 +18580,7 @@
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>995590930</t>
+          <t>+998 99 559-09-30 / +998 95 182-01-95 (O'zi)</t>
         </is>
       </c>
       <c r="U159" t="inlineStr">
@@ -18657,7 +18703,7 @@
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>879340301</t>
+          <t>+998 87 934-03-01 / +998 88 722-88-84 (Onasi)</t>
         </is>
       </c>
       <c r="U160" t="inlineStr">
@@ -18777,7 +18823,7 @@
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>908631674 / 908810610</t>
+          <t>+998 90 881-06-10 / +998 90 863-16-74 (Onasi)</t>
         </is>
       </c>
       <c r="U161" t="inlineStr">
@@ -18882,7 +18928,7 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>976760905 / 876317371</t>
+          <t>+998 97 676-09-05 / +998 87 631-73-71 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
@@ -18992,7 +19038,7 @@
       </c>
       <c r="T163" t="inlineStr">
         <is>
-          <t>881708081 / 880410227</t>
+          <t>+998 88 041-02-27 / +998 88 170-80-81 (Otasi)</t>
         </is>
       </c>
       <c r="U163" t="inlineStr">
@@ -19105,7 +19151,7 @@
       </c>
       <c r="T164" t="inlineStr">
         <is>
-          <t>33-380-11-21 / 88-009-61-66</t>
+          <t>+998 33 380-11-21 / +998 93 562-94-05 (Turmush o'rtog'i)</t>
         </is>
       </c>
       <c r="U164" t="inlineStr">
@@ -19225,7 +19271,7 @@
       </c>
       <c r="T165" t="inlineStr">
         <is>
-          <t>701202277 / 880096166</t>
+          <t>+998 70 681-61-77 / +998 88 009-61-66 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U165" t="inlineStr">
@@ -19340,7 +19386,7 @@
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>880088028</t>
+          <t>+998 97 008-80-28 / +998 88 008-80-28 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U166" t="inlineStr">
@@ -19465,7 +19511,7 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>887291401 / 976198484</t>
+          <t>+998 88 729-14-01 / +998 97 619-84-84 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
@@ -19585,7 +19631,7 @@
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t>773710028 / 956652882</t>
+          <t>+998 77 371-00-28 / +998 95 665-28-82 (Onasi)</t>
         </is>
       </c>
       <c r="U168" t="inlineStr">
@@ -19705,7 +19751,7 @@
       </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>771219093 / 889770693</t>
+          <t>+998 77 121-90-93 / +998 88 977-06-93 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U169" t="inlineStr">
@@ -19820,7 +19866,7 @@
       </c>
       <c r="T170" t="inlineStr">
         <is>
-          <t>914551195</t>
+          <t>+998 90 489-13-00 / +998 90 870-88-27 (Onasi)</t>
         </is>
       </c>
       <c r="U170" t="inlineStr">
@@ -19945,7 +19991,7 @@
       </c>
       <c r="T171" t="inlineStr">
         <is>
-          <t>905181884 / 875613002</t>
+          <t>+998 90 518-18-84 / +998 87 561-30-02 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U171" t="inlineStr">
@@ -20065,7 +20111,7 @@
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>908785105 / 916397685</t>
+          <t>+998 33 115-80-83 / +998 97 618-83-80 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U172" t="inlineStr">
@@ -20180,7 +20226,7 @@
       </c>
       <c r="T173" t="inlineStr">
         <is>
-          <t>912240018</t>
+          <t>+998 91 224-00-18</t>
         </is>
       </c>
       <c r="U173" t="inlineStr">
@@ -20290,7 +20336,7 @@
       </c>
       <c r="T174" t="inlineStr">
         <is>
-          <t>886199703 / 876295108</t>
+          <t>+998 88 619-97-03 / +998 87 629-51-08 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U174" t="inlineStr">
@@ -20410,7 +20456,7 @@
       </c>
       <c r="T175" t="inlineStr">
         <is>
-          <t>90-341-06-76 / 91-898-04-95</t>
+          <t>+998 90 341-06-76 / +998 91 898-04-95 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U175" t="inlineStr">
@@ -20525,7 +20571,7 @@
       </c>
       <c r="T176" t="inlineStr">
         <is>
-          <t>977997671</t>
+          <t>+998 97 799-76-71</t>
         </is>
       </c>
       <c r="U176" t="inlineStr">
@@ -20618,6 +20664,11 @@
           <t>2008</t>
         </is>
       </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>+998 93 891-85-90 / +998 97 635-02-69 (Onasi)</t>
+        </is>
+      </c>
       <c r="U177" t="inlineStr">
         <is>
           <t>Chala</t>
@@ -20713,6 +20764,7 @@
           <t>2018</t>
         </is>
       </c>
+      <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr">
         <is>
           <t>Chala</t>
@@ -20810,7 +20862,7 @@
       </c>
       <c r="T179" t="inlineStr">
         <is>
-          <t>97-960-25-35 / 91-216-23-04</t>
+          <t>+998 97 960-25-35 / +998 91 216-23-04 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
@@ -20905,7 +20957,7 @@
       </c>
       <c r="T180" t="inlineStr">
         <is>
-          <t>778338272</t>
+          <t>+998 77 833-82-72</t>
         </is>
       </c>
       <c r="U180" t="inlineStr">
@@ -20993,6 +21045,7 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -21078,6 +21131,7 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -21170,7 +21224,7 @@
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t>91-219-20-99</t>
+          <t>+998 91 219-20-99</t>
         </is>
       </c>
       <c r="U183" t="inlineStr">
@@ -21263,6 +21317,7 @@
           <t>2010</t>
         </is>
       </c>
+      <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -21340,7 +21395,7 @@
       </c>
       <c r="T185" t="inlineStr">
         <is>
-          <t>913200125 / 914581809</t>
+          <t>+998 91 320-01-25 / +998 91 458-18-09 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
@@ -21430,7 +21485,7 @@
       </c>
       <c r="T186" t="inlineStr">
         <is>
-          <t>906881531</t>
+          <t>+998 90 688-15-31</t>
         </is>
       </c>
       <c r="V186" t="inlineStr">
@@ -21520,7 +21575,7 @@
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>779992813</t>
+          <t>+998 77 999-28-13</t>
         </is>
       </c>
       <c r="V187" t="inlineStr">
@@ -21610,7 +21665,7 @@
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>919582758</t>
+          <t>+998 91 958-27-58</t>
         </is>
       </c>
       <c r="V188" t="inlineStr">
@@ -21698,6 +21753,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-18</t>
@@ -21783,6 +21839,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
@@ -21868,6 +21925,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
@@ -21928,6 +21986,7 @@
           <t>26.05.2006</t>
         </is>
       </c>
+      <c r="T192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 201 (24-11)</t>
@@ -22015,7 +22074,7 @@
       </c>
       <c r="T193" t="inlineStr">
         <is>
-          <t>914662205</t>
+          <t>+998 91 466-22-05</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
@@ -22103,6 +22162,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
@@ -22163,6 +22223,7 @@
           <t>11.07.2007</t>
         </is>
       </c>
+      <c r="T195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 203 (24-13)</t>
@@ -22213,6 +22274,7 @@
           <t>Omonova Dilorom Toshkent qizi</t>
         </is>
       </c>
+      <c r="T196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 24-12</t>
@@ -22273,6 +22335,7 @@
           <t>07.03.2005</t>
         </is>
       </c>
+      <c r="T197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 201 (24-11)</t>
@@ -22360,7 +22423,7 @@
       </c>
       <c r="T198" t="inlineStr">
         <is>
-          <t>886949700</t>
+          <t>+998 88 694-97-00</t>
         </is>
       </c>
       <c r="V198" t="inlineStr">
@@ -22448,6 +22511,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-16</t>
@@ -22533,6 +22597,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
@@ -22618,6 +22683,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-21</t>
@@ -22695,7 +22761,7 @@
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>887040920 / 975878105</t>
+          <t>+998 88 704-09-20 / +998 97 587-81-05 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V202" t="inlineStr">
@@ -22758,6 +22824,7 @@
           <t>07.06.2006</t>
         </is>
       </c>
+      <c r="T203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 204 (24-14)</t>
@@ -22798,6 +22865,7 @@
           <t>To'rayeva Elsenora Sobir qizi</t>
         </is>
       </c>
+      <c r="T204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 24-12</t>
@@ -22885,7 +22953,7 @@
       </c>
       <c r="T205" t="inlineStr">
         <is>
-          <t>919579806 / 906750477</t>
+          <t>+998 91 957-98-06 / +998 90 675-04-77 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V205" t="inlineStr">
@@ -22965,7 +23033,7 @@
       </c>
       <c r="T206" t="inlineStr">
         <is>
-          <t>884901605 / 908787811</t>
+          <t>+998 88 490-16-05 / +998 90 878-78-11 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V206" t="inlineStr">
@@ -23043,6 +23111,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
@@ -23128,6 +23197,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T208" t="inlineStr"/>
       <c r="V208" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-20</t>
@@ -23213,6 +23283,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 25-16</t>
@@ -23298,6 +23369,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
@@ -23385,7 +23457,7 @@
       </c>
       <c r="T211" t="inlineStr">
         <is>
-          <t>974295606</t>
+          <t>+998 97 429-56-06</t>
         </is>
       </c>
       <c r="V211" t="inlineStr">
@@ -23448,6 +23520,7 @@
           <t>12.04.2006</t>
         </is>
       </c>
+      <c r="T212" t="inlineStr"/>
       <c r="V212" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 202 (24-12)</t>
@@ -23533,6 +23606,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T213" t="inlineStr"/>
       <c r="V213" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
@@ -23620,7 +23694,7 @@
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>957022572</t>
+          <t>+998 95 702-25-72</t>
         </is>
       </c>
       <c r="V214" t="inlineStr">
@@ -23683,6 +23757,7 @@
           <t>12.01.2004</t>
         </is>
       </c>
+      <c r="T215" t="inlineStr"/>
       <c r="V215" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 204 (24-14)</t>
@@ -23733,6 +23808,7 @@
           <t>22.06.2005</t>
         </is>
       </c>
+      <c r="T216" t="inlineStr"/>
       <c r="V216" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 205 (24-15)</t>
@@ -23818,6 +23894,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T217" t="inlineStr"/>
       <c r="V217" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-16</t>
@@ -23878,6 +23955,7 @@
           <t>28.08.2002</t>
         </is>
       </c>
+      <c r="T218" t="inlineStr"/>
       <c r="V218" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 203 (24-13)</t>
@@ -23960,7 +24038,7 @@
       </c>
       <c r="T219" t="inlineStr">
         <is>
-          <t>779845421</t>
+          <t>+998 77 984-54-21</t>
         </is>
       </c>
       <c r="V219" t="inlineStr">
@@ -24050,7 +24128,7 @@
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>918157227</t>
+          <t>+998 91 815-72-27</t>
         </is>
       </c>
       <c r="V220" t="inlineStr">
@@ -24140,7 +24218,7 @@
       </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t>880019709 / 916340177</t>
+          <t>+998 88 001-97-09 / +998 91 634-01-77 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V221" t="inlineStr">
@@ -24228,11 +24306,7 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T222" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
+      <c r="T222" t="inlineStr"/>
       <c r="V222" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-20</t>
@@ -24308,6 +24382,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T223" t="inlineStr"/>
       <c r="V223" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
@@ -24368,6 +24443,7 @@
           <t>07.04.2006</t>
         </is>
       </c>
+      <c r="T224" t="inlineStr"/>
       <c r="V224" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 202 (24-12)</t>
@@ -24418,6 +24494,7 @@
           <t>14.05.2006</t>
         </is>
       </c>
+      <c r="T225" t="inlineStr"/>
       <c r="V225" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 203 (24-13)</t>
@@ -24478,6 +24555,7 @@
           <t>13.05.2006</t>
         </is>
       </c>
+      <c r="T226" t="inlineStr"/>
       <c r="V226" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
@@ -24555,7 +24633,7 @@
       </c>
       <c r="T227" t="inlineStr">
         <is>
-          <t>990598714</t>
+          <t>+998 99 059-87-14</t>
         </is>
       </c>
       <c r="V227" t="inlineStr">
@@ -24643,6 +24721,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T228" t="inlineStr"/>
       <c r="V228" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
@@ -24703,6 +24782,7 @@
           <t>29.12.2000</t>
         </is>
       </c>
+      <c r="T229" t="inlineStr"/>
       <c r="V229" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 205 (24-15)</t>
@@ -24763,6 +24843,7 @@
           <t>19.05.2007</t>
         </is>
       </c>
+      <c r="T230" t="inlineStr"/>
       <c r="V230" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
@@ -24840,7 +24921,7 @@
       </c>
       <c r="T231" t="inlineStr">
         <is>
-          <t>919603730</t>
+          <t>+998 91 960-37-30</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
@@ -24930,7 +25011,7 @@
       </c>
       <c r="T232" t="inlineStr">
         <is>
-          <t>505890781</t>
+          <t>+998 50 589-07-81</t>
         </is>
       </c>
       <c r="V232" t="inlineStr">
@@ -25013,6 +25094,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T233" t="inlineStr"/>
       <c r="V233" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
@@ -25093,6 +25175,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T234" t="inlineStr"/>
       <c r="V234" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
@@ -25173,6 +25256,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T235" t="inlineStr"/>
       <c r="V235" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
@@ -25255,7 +25339,7 @@
       </c>
       <c r="T236" t="inlineStr">
         <is>
-          <t>972904017</t>
+          <t>+998 97 290-40-17</t>
         </is>
       </c>
       <c r="V236" t="inlineStr">
@@ -25298,6 +25382,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 268</t>
+        </is>
+      </c>
       <c r="G237" t="inlineStr">
         <is>
           <t>Xolbotir qizi</t>
@@ -25345,7 +25434,7 @@
       </c>
       <c r="T237" t="inlineStr">
         <is>
-          <t>976330414 / 914705957</t>
+          <t>+998 97 633-04-14 / +998 91 470-59-57 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V237" t="inlineStr">
@@ -25378,6 +25467,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 216</t>
+        </is>
+      </c>
       <c r="G238" t="inlineStr">
         <is>
           <t>Tolibovna</t>
@@ -25425,7 +25519,7 @@
       </c>
       <c r="T238" t="inlineStr">
         <is>
-          <t>919541129 / 990168533</t>
+          <t>+998 91 954-11-29 / +998 99 016-85-33 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V238" t="inlineStr">
@@ -25458,6 +25552,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 33</t>
+        </is>
+      </c>
       <c r="G239" t="inlineStr">
         <is>
           <t>Xasan qizi</t>
@@ -25505,7 +25604,7 @@
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>992216864 / 936660215</t>
+          <t>+998 99 221-68-64 / +998 93 666-02-15 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V239" t="inlineStr">
@@ -25538,6 +25637,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>26/27 SH/A269</t>
+        </is>
+      </c>
       <c r="G240" t="inlineStr">
         <is>
           <t>Azamat qizi</t>
@@ -25585,7 +25689,7 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>881787006 / 883820676</t>
+          <t>+998 88 178-70-06 / +998 88 382-06-76 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
@@ -25665,7 +25769,7 @@
       </c>
       <c r="T241" t="inlineStr">
         <is>
-          <t>991532272 / 913206776</t>
+          <t>+998 99 153-22-72 / +998 91 320-67-76 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V241" t="inlineStr">
@@ -25745,7 +25849,7 @@
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>912195314 / 912631980</t>
+          <t>+998 91 219-53-14 / +998 91 263-19-80 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V242" t="inlineStr">
@@ -25825,7 +25929,7 @@
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>334306560 / 888498097</t>
+          <t>+998 33 430-65-60 / +998 88 849-80-97 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
@@ -25905,7 +26009,7 @@
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>919468306 / 906078708</t>
+          <t>+998 91 946-83-06 / +998 90 607-87-08 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V244" t="inlineStr">
@@ -25938,6 +26042,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 6</t>
+        </is>
+      </c>
       <c r="G245" t="inlineStr">
         <is>
           <t>Qurbonali qizi</t>
@@ -25985,7 +26094,7 @@
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>885860697 / 885851406</t>
+          <t>+998 88 586-06-97 / +998 88 585-14-06 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
@@ -26065,7 +26174,7 @@
       </c>
       <c r="T246" t="inlineStr">
         <is>
-          <t>976191200 / 906681675</t>
+          <t>+998 97 619-12-00 / +998 90 668-16-75 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V246" t="inlineStr">
@@ -26145,7 +26254,7 @@
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>992063680 / 996490750</t>
+          <t>+998 99 206-36-80 / +998 99 649-07-50 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
@@ -26225,7 +26334,7 @@
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>935200878 / 941718040</t>
+          <t>+998 93 520-08-78 / +998 94 171-80-40 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
@@ -26305,7 +26414,7 @@
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>904403280 / 912572096</t>
+          <t>+998 90 440-32-80 / +998 91 257-20-96 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
@@ -26385,7 +26494,7 @@
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>952710247 / 913100459</t>
+          <t>+998 95 271-02-47 / +998 91 310-04-59 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V250" t="inlineStr">
@@ -26465,7 +26574,7 @@
       </c>
       <c r="T251" t="inlineStr">
         <is>
-          <t>913227323 / 914547926</t>
+          <t>+998 91 322-73-23 / +998 91 454-79-26 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
@@ -26498,6 +26607,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 33</t>
+        </is>
+      </c>
       <c r="G252" t="inlineStr">
         <is>
           <t>Husan qizi</t>
@@ -26545,7 +26659,7 @@
       </c>
       <c r="T252" t="inlineStr">
         <is>
-          <t>940800126 / 930723177</t>
+          <t>+998 94 080-01-26 / +998 93 072-31-77 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V252" t="inlineStr">
@@ -26578,6 +26692,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 220</t>
+        </is>
+      </c>
       <c r="G253" t="inlineStr">
         <is>
           <t>Baxtiyor qizi</t>
@@ -26625,7 +26744,7 @@
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>908152500 / 948170193</t>
+          <t>+998 90 815-25-00 / +998 94 817-01-93 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
@@ -26658,6 +26777,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 277</t>
+        </is>
+      </c>
       <c r="G254" t="inlineStr">
         <is>
           <t>Tura qizi</t>
@@ -26705,7 +26829,7 @@
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>908152500 / 948170193</t>
+          <t>+998 90 815-25-00 / +998 94 817-01-93 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V254" t="inlineStr">
@@ -26785,7 +26909,7 @@
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>995539807 / 992301484</t>
+          <t>+998 99 553-98-07 / +998 99 230-14-84 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
@@ -26818,6 +26942,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>25/26 SH/A57</t>
+        </is>
+      </c>
       <c r="G256" t="inlineStr">
         <is>
           <t>Akram qizi</t>
@@ -26865,7 +26994,7 @@
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>916438055 / 912576076</t>
+          <t>+998 91 643-80-55 / +998 91 257-60-76 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V256" t="inlineStr">
@@ -26945,7 +27074,7 @@
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>912214978 / 995714978</t>
+          <t>+998 91 221-49-78 / +998 99 571-49-78 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
@@ -27025,7 +27154,7 @@
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>908905142 / 912155152</t>
+          <t>+998 90 890-51-42 / +998 91 215-51-52 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V258" t="inlineStr">
@@ -27105,7 +27234,7 @@
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>912241622 / 914703538</t>
+          <t>+998 91 224-16-22 / +998 91 470-35-38 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
@@ -27185,7 +27314,7 @@
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>908635351 / 903422205</t>
+          <t>+998 90 863-53-51 / +998 90 342-22-05 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V260" t="inlineStr">
@@ -27265,7 +27394,7 @@
       </c>
       <c r="T261" t="inlineStr">
         <is>
-          <t>973872825 / 912184436</t>
+          <t>+998 97 387-28-25 / +998 91 218-44-36 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
@@ -27345,7 +27474,7 @@
       </c>
       <c r="T262" t="inlineStr">
         <is>
-          <t>974412205 / 882051475</t>
+          <t>+998 97 441-22-05 / +998 88 205-14-75 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V262" t="inlineStr">
@@ -27425,7 +27554,7 @@
       </c>
       <c r="T263" t="inlineStr">
         <is>
-          <t>886329515 / 884889515</t>
+          <t>+998 88 632-95-15 / +998 88 488-95-15 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V263" t="inlineStr">
@@ -27505,7 +27634,7 @@
       </c>
       <c r="T264" t="inlineStr">
         <is>
-          <t>912190617 / 912173481</t>
+          <t>+998 91 219-06-17 / +998 91 217-34-81 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V264" t="inlineStr">
@@ -27585,7 +27714,7 @@
       </c>
       <c r="T265" t="inlineStr">
         <is>
-          <t>918133661 / 919463882</t>
+          <t>+998 91 813-36-61 / +998 91 946-38-82 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V265" t="inlineStr">
@@ -27665,7 +27794,7 @@
       </c>
       <c r="T266" t="inlineStr">
         <is>
-          <t>906755744 / 973894007</t>
+          <t>+998 90 675-57-44 / +998 97 389-40-07 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V266" t="inlineStr">
@@ -27745,7 +27874,7 @@
       </c>
       <c r="T267" t="inlineStr">
         <is>
-          <t>888028181 / 906070503</t>
+          <t>+998 88 802-81-81 / +998 90 607-05-03 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V267" t="inlineStr">
@@ -27825,7 +27954,7 @@
       </c>
       <c r="T268" t="inlineStr">
         <is>
-          <t>904289236 / 913203000</t>
+          <t>+998 90 428-92-36 / +998 91 320-30-00 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V268" t="inlineStr">
@@ -27905,7 +28034,7 @@
       </c>
       <c r="T269" t="inlineStr">
         <is>
-          <t>950549107 / 909288704</t>
+          <t>+998 95 054-91-07 / +998 90 928-87-04 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V269" t="inlineStr">
@@ -27985,7 +28114,7 @@
       </c>
       <c r="T270" t="inlineStr">
         <is>
-          <t>904289236 / 913203000</t>
+          <t>+998 90 428-92-36 / +998 91 320-30-00 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V270" t="inlineStr">
@@ -28018,6 +28147,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 226</t>
+        </is>
+      </c>
       <c r="G271" t="inlineStr">
         <is>
           <t>Jobur qizi</t>
@@ -28065,7 +28199,7 @@
       </c>
       <c r="T271" t="inlineStr">
         <is>
-          <t>995407843 / 917750559</t>
+          <t>+998 99 540-78-43 / +998 91 775-05-59 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V271" t="inlineStr">
@@ -28145,7 +28279,7 @@
       </c>
       <c r="T272" t="inlineStr">
         <is>
-          <t>908856713 / 912134195</t>
+          <t>+998 90 885-67-13 / +998 91 213-41-95 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V272" t="inlineStr">
@@ -28178,6 +28312,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>26/27 SH/A252</t>
+        </is>
+      </c>
       <c r="G273" t="inlineStr">
         <is>
           <t>Alisher qizi</t>
@@ -28225,7 +28364,7 @@
       </c>
       <c r="T273" t="inlineStr">
         <is>
-          <t>957110793 / 957720793</t>
+          <t>+998 95 711-07-93 / +998 95 772-07-93 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V273" t="inlineStr">
@@ -28258,6 +28397,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 285</t>
+        </is>
+      </c>
       <c r="G274" t="inlineStr">
         <is>
           <t>Abdurahmonovna</t>
@@ -28305,7 +28449,7 @@
       </c>
       <c r="T274" t="inlineStr">
         <is>
-          <t>952274001 / 914672374</t>
+          <t>+998 95 227-40-01 / +998 91 467-23-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V274" t="inlineStr">
@@ -28338,6 +28482,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 285</t>
+        </is>
+      </c>
       <c r="G275" t="inlineStr">
         <is>
           <t>Soyibjon qizi</t>
@@ -28385,7 +28534,7 @@
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>943337608 / 943302274</t>
+          <t>+998 94 333-76-08 / +998 94 330-22-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V275" t="inlineStr">
@@ -28465,7 +28614,7 @@
       </c>
       <c r="T276" t="inlineStr">
         <is>
-          <t>990530148 / 990537640</t>
+          <t>+998 99 053-01-48 / +998 99 053-76-40 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V276" t="inlineStr">
@@ -28498,6 +28647,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 286</t>
+        </is>
+      </c>
       <c r="G277" t="inlineStr">
         <is>
           <t>Shog'dor qizi</t>
@@ -28545,7 +28699,7 @@
       </c>
       <c r="T277" t="inlineStr">
         <is>
-          <t>979054705 / 994192374</t>
+          <t>+998 97 905-47-05 / +998 99 419-23-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V277" t="inlineStr">
@@ -28625,7 +28779,7 @@
       </c>
       <c r="T278" t="inlineStr">
         <is>
-          <t>777270736 / 934225072</t>
+          <t>+998 77 727-07-36 / +998 93 422-50-72 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V278" t="inlineStr">
@@ -28705,7 +28859,7 @@
       </c>
       <c r="T279" t="inlineStr">
         <is>
-          <t>885868797 / 946967447</t>
+          <t>+998 88 586-87-97 / +998 94 696-74-47 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V279" t="inlineStr">
@@ -28785,7 +28939,7 @@
       </c>
       <c r="T280" t="inlineStr">
         <is>
-          <t>979511206 / 907208236</t>
+          <t>+998 97 951-12-06 / +998 90 720-82-36 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V280" t="inlineStr">
@@ -28865,7 +29019,7 @@
       </c>
       <c r="T281" t="inlineStr">
         <is>
-          <t>973886880</t>
+          <t>+998 97 388-68-80</t>
         </is>
       </c>
       <c r="V281" t="inlineStr">
@@ -28945,7 +29099,7 @@
       </c>
       <c r="T282" t="inlineStr">
         <is>
-          <t>971419410 / 971519410</t>
+          <t>+998 97 141-94-10 / +998 97 151-94-10 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V282" t="inlineStr">
@@ -29025,7 +29179,7 @@
       </c>
       <c r="T283" t="inlineStr">
         <is>
-          <t>914744356 / 881662111</t>
+          <t>+998 91 474-43-56 / +998 88 166-21-11 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V283" t="inlineStr">
@@ -29105,7 +29259,7 @@
       </c>
       <c r="T284" t="inlineStr">
         <is>
-          <t>912214978 / 995714978</t>
+          <t>+998 91 221-49-78 / +998 99 571-49-78 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V284" t="inlineStr">
@@ -29185,7 +29339,7 @@
       </c>
       <c r="T285" t="inlineStr">
         <is>
-          <t>976327478 / 973886699</t>
+          <t>+998 97 632-74-78 / +998 97 388-66-99 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V285" t="inlineStr">
@@ -29265,7 +29419,7 @@
       </c>
       <c r="T286" t="inlineStr">
         <is>
-          <t>919517206 / 906397273</t>
+          <t>+998 91 951-72-06 / +998 90 639-72-73 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V286" t="inlineStr">
@@ -29345,7 +29499,7 @@
       </c>
       <c r="T287" t="inlineStr">
         <is>
-          <t>971110305 / 883863117</t>
+          <t>+998 97 111-03-05 / +998 88 386-31-17 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V287" t="inlineStr">
@@ -29425,7 +29579,7 @@
       </c>
       <c r="T288" t="inlineStr">
         <is>
-          <t>913216025 / 903425000</t>
+          <t>+998 91 321-60-25 / +998 90 342-50-00 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V288" t="inlineStr">
@@ -29458,6 +29612,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 288</t>
+        </is>
+      </c>
       <c r="G289" t="inlineStr">
         <is>
           <t>Boynazar qizi</t>
@@ -29505,7 +29664,7 @@
       </c>
       <c r="T289" t="inlineStr">
         <is>
-          <t>937610582 / 947063805</t>
+          <t>+998 93 761-05-82 / +998 94 706-38-05 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V289" t="inlineStr">
@@ -29585,7 +29744,7 @@
       </c>
       <c r="T290" t="inlineStr">
         <is>
-          <t>973872825 / 912184436</t>
+          <t>+998 97 387-28-25 / +998 91 218-44-36 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V290" t="inlineStr">
@@ -29665,7 +29824,7 @@
       </c>
       <c r="T291" t="inlineStr">
         <is>
-          <t>887682775 / 912184436</t>
+          <t>+998 88 768-27-75 / +998 91 218-44-36 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V291" t="inlineStr">
@@ -29745,7 +29904,7 @@
       </c>
       <c r="T292" t="inlineStr">
         <is>
-          <t>883831100 / 973891100</t>
+          <t>+998 88 383-11-00 / +998 97 389-11-00 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V292" t="inlineStr">
@@ -29778,6 +29937,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 259</t>
+        </is>
+      </c>
       <c r="G293" t="inlineStr">
         <is>
           <t>Xolbobo qizi</t>
@@ -29825,7 +29989,7 @@
       </c>
       <c r="T293" t="inlineStr">
         <is>
-          <t>951109377 / 950179377</t>
+          <t>+998 95 110-93-77 / +998 95 017-93-77 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V293" t="inlineStr">
@@ -29858,6 +30022,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 235</t>
+        </is>
+      </c>
       <c r="G294" t="inlineStr">
         <is>
           <t>Luqmon o'g'li</t>
@@ -29905,7 +30074,7 @@
       </c>
       <c r="T294" t="inlineStr">
         <is>
-          <t>336382834 / 336128707</t>
+          <t>+998 33 638-28-34 / +998 33 612-87-07 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V294" t="inlineStr">
@@ -29985,7 +30154,7 @@
       </c>
       <c r="T295" t="inlineStr">
         <is>
-          <t>888017588 / 887531005</t>
+          <t>+998 88 801-75-88 / +998 88 753-10-05 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V295" t="inlineStr">
@@ -30065,7 +30234,7 @@
       </c>
       <c r="T296" t="inlineStr">
         <is>
-          <t>970679977 / 774772487</t>
+          <t>+998 97 067-99-77 / +998 77 477-24-87 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V296" t="inlineStr">
@@ -30145,7 +30314,7 @@
       </c>
       <c r="T297" t="inlineStr">
         <is>
-          <t>888041384 / 883801384</t>
+          <t>+998 88 804-13-84 / +998 88 380-13-84 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V297" t="inlineStr">
@@ -30225,7 +30394,7 @@
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>888041384 / 883801384</t>
+          <t>+998 88 804-13-84 / +998 88 380-13-84 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V298" t="inlineStr">
@@ -30305,7 +30474,7 @@
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>912173507 / 883031190</t>
+          <t>+998 91 217-35-07 / +998 88 303-11-90 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V299" t="inlineStr">
@@ -30385,7 +30554,7 @@
       </c>
       <c r="T300" t="inlineStr">
         <is>
-          <t>880062616 / 889247677</t>
+          <t>+998 88 006-26-16 / +998 88 924-76-77 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V300" t="inlineStr">
@@ -30418,6 +30587,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 239</t>
+        </is>
+      </c>
       <c r="G301" t="inlineStr">
         <is>
           <t>Eshpo'lat o'g'li</t>
@@ -30465,7 +30639,7 @@
       </c>
       <c r="T301" t="inlineStr">
         <is>
-          <t>996633126 / 919605337</t>
+          <t>+998 99 663-31-26 / +998 91 960-53-37 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V301" t="inlineStr">
@@ -30498,6 +30672,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>24/25 SH/A 41</t>
+        </is>
+      </c>
       <c r="G302" t="inlineStr">
         <is>
           <t>Shavkat qizi</t>
@@ -30545,7 +30724,7 @@
       </c>
       <c r="T302" t="inlineStr">
         <is>
-          <t>919565650 / 908849873</t>
+          <t>+998 91 956-56-50 / +998 90 884-98-73 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V302" t="inlineStr">
@@ -30625,7 +30804,7 @@
       </c>
       <c r="T303" t="inlineStr">
         <is>
-          <t>884900511 / 906161546</t>
+          <t>+998 88 490-05-11 / +998 90 616-15-46 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V303" t="inlineStr">
@@ -30705,7 +30884,7 @@
       </c>
       <c r="T304" t="inlineStr">
         <is>
-          <t>947390802 / 991431601</t>
+          <t>+998 94 739-08-02 / +998 99 143-16-01 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V304" t="inlineStr">
@@ -30785,7 +30964,7 @@
       </c>
       <c r="T305" t="inlineStr">
         <is>
-          <t>973804217 / 901211217</t>
+          <t>+998 97 380-42-17 / +998 90 121-12-17 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V305" t="inlineStr">
@@ -30818,6 +30997,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 241</t>
+        </is>
+      </c>
       <c r="G306" t="inlineStr">
         <is>
           <t>Yorqin qizi</t>
@@ -30865,7 +31049,7 @@
       </c>
       <c r="T306" t="inlineStr">
         <is>
-          <t>909605337 / 996633126</t>
+          <t>+998 90 960-53-37 / +998 99 663-31-26 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V306" t="inlineStr">
@@ -30945,7 +31129,7 @@
       </c>
       <c r="T307" t="inlineStr">
         <is>
-          <t>907880027 / 905180666</t>
+          <t>+998 90 788-00-27 / +998 90 518-06-66 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V307" t="inlineStr">
@@ -31025,7 +31209,7 @@
       </c>
       <c r="T308" t="inlineStr">
         <is>
-          <t>990616341 / 916330215</t>
+          <t>+998 99 061-63-41 / +998 91 633-02-15 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V308" t="inlineStr">
@@ -31105,7 +31289,7 @@
       </c>
       <c r="T309" t="inlineStr">
         <is>
-          <t>883831100 / 973891100</t>
+          <t>+998 88 383-11-00 / +998 97 389-11-00 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V309" t="inlineStr">
@@ -31185,7 +31369,7 @@
       </c>
       <c r="T310" t="inlineStr">
         <is>
-          <t>902880568 / 908806000</t>
+          <t>+998 90 288-05-68 / +998 90 880-60-00 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V310" t="inlineStr">
@@ -31265,7 +31449,7 @@
       </c>
       <c r="T311" t="inlineStr">
         <is>
-          <t>886170996 / 976342474</t>
+          <t>+998 88 617-09-96 / +998 97 634-24-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V311" t="inlineStr">
@@ -31298,6 +31482,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 286</t>
+        </is>
+      </c>
       <c r="G312" t="inlineStr">
         <is>
           <t>Tufli qizi</t>
@@ -31345,7 +31534,7 @@
       </c>
       <c r="T312" t="inlineStr">
         <is>
-          <t>952291405 / 330707669</t>
+          <t>+998 95 229-14-05 / +998 33 070-76-69 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V312" t="inlineStr">
@@ -31425,7 +31614,7 @@
       </c>
       <c r="T313" t="inlineStr">
         <is>
-          <t>771262702 / 994527549</t>
+          <t>+998 77 126-27-02 / +998 99 452-75-49 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V313" t="inlineStr">
@@ -31505,7 +31694,7 @@
       </c>
       <c r="T314" t="inlineStr">
         <is>
-          <t>888338593 / 888040691</t>
+          <t>+998 88 833-85-93 / +998 88 804-06-91 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V314" t="inlineStr">
@@ -31585,7 +31774,7 @@
       </c>
       <c r="T315" t="inlineStr">
         <is>
-          <t>886321747 / 880322575</t>
+          <t>+998 88 632-17-47 / +998 88 032-25-75 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V315" t="inlineStr">
@@ -31618,6 +31807,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 506</t>
+        </is>
+      </c>
       <c r="G316" t="inlineStr">
         <is>
           <t>Ne'mat qizi</t>
@@ -31665,7 +31859,7 @@
       </c>
       <c r="T316" t="inlineStr">
         <is>
-          <t>973889414 / 973880407</t>
+          <t>+998 97 388-94-14 / +998 97 388-04-07 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V316" t="inlineStr">
@@ -31745,7 +31939,7 @@
       </c>
       <c r="T317" t="inlineStr">
         <is>
-          <t>919525425 / 979516700</t>
+          <t>+998 91 952-54-25 / +998 97 951-67-00 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V317" t="inlineStr">
@@ -31825,7 +32019,7 @@
       </c>
       <c r="T318" t="inlineStr">
         <is>
-          <t>973803700 / 883808105</t>
+          <t>+998 97 380-37-00 / +998 88 380-81-05 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V318" t="inlineStr">
@@ -31858,6 +32052,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A509</t>
+        </is>
+      </c>
       <c r="G319" t="inlineStr">
         <is>
           <t>Narzullo qizi</t>
@@ -31905,7 +32104,7 @@
       </c>
       <c r="T319" t="inlineStr">
         <is>
-          <t>888030719 / 888000719</t>
+          <t>+998 88 803-07-19 / +998 88 800-07-19 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V319" t="inlineStr">
@@ -31985,7 +32184,7 @@
       </c>
       <c r="T320" t="inlineStr">
         <is>
-          <t>880308590 / 915603500</t>
+          <t>+998 88 030-85-90 / +998 91 560-35-00 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V320" t="inlineStr">
@@ -32065,7 +32264,7 @@
       </c>
       <c r="T321" t="inlineStr">
         <is>
-          <t>888030374 / 880037607</t>
+          <t>+998 88 803-03-74 / +998 88 003-76-07 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V321" t="inlineStr">
@@ -32145,7 +32344,7 @@
       </c>
       <c r="T322" t="inlineStr">
         <is>
-          <t>918152595 / 914663041</t>
+          <t>+998 91 815-25-95 / +998 91 466-30-41 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V322" t="inlineStr">
@@ -32225,7 +32424,7 @@
       </c>
       <c r="T323" t="inlineStr">
         <is>
-          <t>908700205 / 882635505</t>
+          <t>+998 90 870-02-05 / +998 88 263-55-05 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V323" t="inlineStr">
@@ -32305,7 +32504,7 @@
       </c>
       <c r="T324" t="inlineStr">
         <is>
-          <t>990941251 / 943551251</t>
+          <t>+998 99 094-12-51 / +998 94 355-12-51 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V324" t="inlineStr">
@@ -32385,7 +32584,7 @@
       </c>
       <c r="T325" t="inlineStr">
         <is>
-          <t>950133622</t>
+          <t>+998 95 013-36-22</t>
         </is>
       </c>
       <c r="V325" t="inlineStr">
@@ -32465,7 +32664,7 @@
       </c>
       <c r="T326" t="inlineStr">
         <is>
-          <t>954994838 / 919633693</t>
+          <t>+998 95 499-48-38 / +998 91 963-36-93 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V326" t="inlineStr">
@@ -32545,7 +32744,7 @@
       </c>
       <c r="T327" t="inlineStr">
         <is>
-          <t>912620302 / 901300802</t>
+          <t>+998 91 262-03-02 / +998 90 130-08-02 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V327" t="inlineStr">
@@ -32625,7 +32824,7 @@
       </c>
       <c r="T328" t="inlineStr">
         <is>
-          <t>918195904 / 908792252</t>
+          <t>+998 91 819-59-04 / +998 90 879-22-52 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V328" t="inlineStr">
@@ -32705,7 +32904,7 @@
       </c>
       <c r="T329" t="inlineStr">
         <is>
-          <t>508702406 / 884789001</t>
+          <t>+998 50 870-24-06 / +998 88 478-90-01 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V329" t="inlineStr">
@@ -32738,6 +32937,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 520</t>
+        </is>
+      </c>
       <c r="G330" t="inlineStr">
         <is>
           <t>Qurbonmurodovna</t>
@@ -32785,7 +32989,7 @@
       </c>
       <c r="T330" t="inlineStr">
         <is>
-          <t>935968407 / 931141501</t>
+          <t>+998 93 596-84-07 / +998 93 114-15-01 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V330" t="inlineStr">
@@ -32865,7 +33069,7 @@
       </c>
       <c r="T331" t="inlineStr">
         <is>
-          <t>885864202 / 997067167</t>
+          <t>+998 88 586-42-02 / +998 99 706-71-67 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V331" t="inlineStr">
@@ -32945,7 +33149,7 @@
       </c>
       <c r="T332" t="inlineStr">
         <is>
-          <t>944829988 / 918113199</t>
+          <t>+998 94 482-99-88 / +998 91 811-31-99 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V332" t="inlineStr">
@@ -33025,7 +33229,7 @@
       </c>
       <c r="T333" t="inlineStr">
         <is>
-          <t>886336067</t>
+          <t>+998 88 633-60-67</t>
         </is>
       </c>
       <c r="V333" t="inlineStr">
@@ -33103,6 +33307,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T334" t="inlineStr"/>
       <c r="V334" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -33133,6 +33338,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 186</t>
+        </is>
+      </c>
       <c r="G335" t="inlineStr">
         <is>
           <t>Faxriddin qizi</t>
@@ -33180,7 +33390,7 @@
       </c>
       <c r="T335" t="inlineStr">
         <is>
-          <t>906752661</t>
+          <t>+998 90 675-26-61</t>
         </is>
       </c>
       <c r="V335" t="inlineStr">
@@ -33260,7 +33470,7 @@
       </c>
       <c r="T336" t="inlineStr">
         <is>
-          <t>880497904 / 971801718</t>
+          <t>+998 88 049-79-04 / +998 97 180-17-18 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V336" t="inlineStr">
@@ -33293,6 +33503,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 116</t>
+        </is>
+      </c>
       <c r="G337" t="inlineStr">
         <is>
           <t>Sayit qizi</t>
@@ -33340,7 +33555,7 @@
       </c>
       <c r="T337" t="inlineStr">
         <is>
-          <t>886199121</t>
+          <t>+998 88 619-91-21</t>
         </is>
       </c>
       <c r="V337" t="inlineStr">
@@ -33420,7 +33635,7 @@
       </c>
       <c r="T338" t="inlineStr">
         <is>
-          <t>770319926 / 993522269</t>
+          <t>+998 77 031-99-26 / +998 99 352-22-69 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V338" t="inlineStr">
@@ -33500,7 +33715,7 @@
       </c>
       <c r="T339" t="inlineStr">
         <is>
-          <t>917757776 / 912180386</t>
+          <t>+998 91 775-77-76 / +998 91 218-03-86 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V339" t="inlineStr">
@@ -33580,7 +33795,7 @@
       </c>
       <c r="T340" t="inlineStr">
         <is>
-          <t>919629117</t>
+          <t>+998 91 962-91-17</t>
         </is>
       </c>
       <c r="V340" t="inlineStr">
@@ -33660,7 +33875,7 @@
       </c>
       <c r="T341" t="inlineStr">
         <is>
-          <t>978883920 / 976327701</t>
+          <t>+998 97 888-39-20 / +998 97 632-77-01 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V341" t="inlineStr">
@@ -33740,7 +33955,7 @@
       </c>
       <c r="T342" t="inlineStr">
         <is>
-          <t>914748292</t>
+          <t>+998 91 474-82-92</t>
         </is>
       </c>
       <c r="V342" t="inlineStr">
@@ -33820,7 +34035,7 @@
       </c>
       <c r="T343" t="inlineStr">
         <is>
-          <t>770239697 / 975242470</t>
+          <t>+998 77 023-96-97 / +998 97 524-24-70 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V343" t="inlineStr">
@@ -33898,6 +34113,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T344" t="inlineStr"/>
       <c r="V344" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -33980,7 +34196,7 @@
       </c>
       <c r="T345" t="inlineStr">
         <is>
-          <t>902890316</t>
+          <t>+998 90 289-03-16</t>
         </is>
       </c>
       <c r="V345" t="inlineStr">
@@ -34058,6 +34274,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T346" t="inlineStr"/>
       <c r="V346" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34133,6 +34350,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T347" t="inlineStr"/>
       <c r="V347" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34163,6 +34381,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 327</t>
+        </is>
+      </c>
       <c r="G348" t="inlineStr">
         <is>
           <t>Otabek qizi</t>
@@ -34208,6 +34431,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T348" t="inlineStr"/>
       <c r="V348" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34285,7 +34509,7 @@
       </c>
       <c r="T349" t="inlineStr">
         <is>
-          <t>970662133 / 916363305</t>
+          <t>+998 97 066-21-33 / +998 91 636-33-05 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V349" t="inlineStr">
@@ -34363,6 +34587,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T350" t="inlineStr"/>
       <c r="V350" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34438,6 +34663,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T351" t="inlineStr"/>
       <c r="V351" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34513,6 +34739,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T352" t="inlineStr"/>
       <c r="V352" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34590,7 +34817,7 @@
       </c>
       <c r="T353" t="inlineStr">
         <is>
-          <t>770922107</t>
+          <t>+998 77 092-21-07</t>
         </is>
       </c>
       <c r="V353" t="inlineStr">
@@ -34668,6 +34895,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T354" t="inlineStr"/>
       <c r="V354" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34745,7 +34973,7 @@
       </c>
       <c r="T355" t="inlineStr">
         <is>
-          <t>880138306</t>
+          <t>+998 88 013-83-06</t>
         </is>
       </c>
       <c r="V355" t="inlineStr">
@@ -34823,6 +35051,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T356" t="inlineStr"/>
       <c r="V356" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34898,6 +35127,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T357" t="inlineStr"/>
       <c r="V357" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34975,7 +35205,7 @@
       </c>
       <c r="T358" t="inlineStr">
         <is>
-          <t>918193927</t>
+          <t>+998 91 819-39-27</t>
         </is>
       </c>
       <c r="V358" t="inlineStr">
@@ -35053,6 +35283,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T359" t="inlineStr"/>
       <c r="V359" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35128,6 +35359,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T360" t="inlineStr"/>
       <c r="V360" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35205,7 +35437,7 @@
       </c>
       <c r="T361" t="inlineStr">
         <is>
-          <t>904404581</t>
+          <t>+998 90 440-45-81</t>
         </is>
       </c>
       <c r="V361" t="inlineStr">
@@ -35285,7 +35517,7 @@
       </c>
       <c r="T362" t="inlineStr">
         <is>
-          <t>772193606</t>
+          <t>+998 77 219-36-06</t>
         </is>
       </c>
       <c r="V362" t="inlineStr">
@@ -35318,6 +35550,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 15</t>
+        </is>
+      </c>
       <c r="G363" t="inlineStr">
         <is>
           <t>Qahramon qizi</t>
@@ -35365,7 +35602,7 @@
       </c>
       <c r="T363" t="inlineStr">
         <is>
-          <t>918144219</t>
+          <t>+998 91 814-42-19</t>
         </is>
       </c>
       <c r="V363" t="inlineStr">
@@ -35443,6 +35680,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T364" t="inlineStr"/>
       <c r="V364" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35473,6 +35711,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 10</t>
+        </is>
+      </c>
       <c r="G365" t="inlineStr">
         <is>
           <t>Azamat qizi</t>
@@ -35520,7 +35763,7 @@
       </c>
       <c r="T365" t="inlineStr">
         <is>
-          <t>505069607</t>
+          <t>+998 50 506-96-07</t>
         </is>
       </c>
       <c r="V365" t="inlineStr">
@@ -35598,6 +35841,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T366" t="inlineStr"/>
       <c r="V366" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35673,6 +35917,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T367" t="inlineStr"/>
       <c r="V367" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35750,7 +35995,7 @@
       </c>
       <c r="T368" t="inlineStr">
         <is>
-          <t>883810031</t>
+          <t>+998 88 381-00-31</t>
         </is>
       </c>
       <c r="V368" t="inlineStr">
@@ -35828,6 +36073,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T369" t="inlineStr"/>
       <c r="V369" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35905,7 +36151,7 @@
       </c>
       <c r="T370" t="inlineStr">
         <is>
-          <t>882384979</t>
+          <t>+998 88 238-49-79</t>
         </is>
       </c>
       <c r="V370" t="inlineStr">
@@ -35938,6 +36184,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>25/26 SH/A84</t>
+        </is>
+      </c>
       <c r="G371" t="inlineStr">
         <is>
           <t>Faxriddin qizi</t>
@@ -35985,7 +36236,7 @@
       </c>
       <c r="T371" t="inlineStr">
         <is>
-          <t>335639507 / 773901307</t>
+          <t>+998 33 563-95-07 / +998 77 390-13-07 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V371" t="inlineStr">
@@ -36063,6 +36314,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T372" t="inlineStr"/>
       <c r="V372" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36140,7 +36392,7 @@
       </c>
       <c r="T373" t="inlineStr">
         <is>
-          <t>914660507</t>
+          <t>+998 91 466-05-07</t>
         </is>
       </c>
       <c r="V373" t="inlineStr">
@@ -36220,7 +36472,7 @@
       </c>
       <c r="T374" t="inlineStr">
         <is>
-          <t>952997704</t>
+          <t>+998 95 299-77-04</t>
         </is>
       </c>
       <c r="V374" t="inlineStr">
@@ -36298,6 +36550,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T375" t="inlineStr"/>
       <c r="V375" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36328,6 +36581,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 26</t>
+        </is>
+      </c>
       <c r="G376" t="inlineStr">
         <is>
           <t>A'zam qizi</t>
@@ -36375,7 +36633,7 @@
       </c>
       <c r="T376" t="inlineStr">
         <is>
-          <t>990710819</t>
+          <t>+998 99 071-08-19</t>
         </is>
       </c>
       <c r="V376" t="inlineStr">
@@ -36455,7 +36713,7 @@
       </c>
       <c r="T377" t="inlineStr">
         <is>
-          <t>505010182 / 880780686</t>
+          <t>+998 50 501-01-82 / +998 88 078-06-86 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V377" t="inlineStr">
@@ -36488,6 +36746,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 28</t>
+        </is>
+      </c>
       <c r="G378" t="inlineStr">
         <is>
           <t>Hikmatullo qizi</t>
@@ -36533,6 +36796,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T378" t="inlineStr"/>
       <c r="V378" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36608,6 +36872,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T379" t="inlineStr"/>
       <c r="V379" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36638,6 +36903,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 107</t>
+        </is>
+      </c>
       <c r="G380" t="inlineStr">
         <is>
           <t>Nodir qizi</t>
@@ -36685,7 +36955,7 @@
       </c>
       <c r="T380" t="inlineStr">
         <is>
-          <t>940825116</t>
+          <t>+998 94 082-51-16</t>
         </is>
       </c>
       <c r="V380" t="inlineStr">
@@ -36765,7 +37035,7 @@
       </c>
       <c r="T381" t="inlineStr">
         <is>
-          <t>904449209</t>
+          <t>+998 90 444-92-09</t>
         </is>
       </c>
       <c r="V381" t="inlineStr">
@@ -36843,6 +37113,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T382" t="inlineStr"/>
       <c r="V382" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36918,6 +37189,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T383" t="inlineStr"/>
       <c r="V383" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36995,7 +37267,7 @@
       </c>
       <c r="T384" t="inlineStr">
         <is>
-          <t>945540709</t>
+          <t>+998 94 554-07-09</t>
         </is>
       </c>
       <c r="V384" t="inlineStr">
@@ -37075,7 +37347,7 @@
       </c>
       <c r="T385" t="inlineStr">
         <is>
-          <t>957021033</t>
+          <t>+998 95 702-10-33</t>
         </is>
       </c>
       <c r="V385" t="inlineStr">
@@ -37153,6 +37425,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T386" t="inlineStr"/>
       <c r="V386" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37230,7 +37503,7 @@
       </c>
       <c r="T387" t="inlineStr">
         <is>
-          <t>909505103</t>
+          <t>+998 90 950-51-03</t>
         </is>
       </c>
       <c r="V387" t="inlineStr">
@@ -37263,6 +37536,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>26/27 SH/A40</t>
+        </is>
+      </c>
       <c r="G388" t="inlineStr">
         <is>
           <t>Ramziddin qizi</t>
@@ -37308,6 +37586,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T388" t="inlineStr"/>
       <c r="V388" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37383,6 +37662,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T389" t="inlineStr"/>
       <c r="V389" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37458,6 +37738,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T390" t="inlineStr"/>
       <c r="V390" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37535,7 +37816,7 @@
       </c>
       <c r="T391" t="inlineStr">
         <is>
-          <t>998191107</t>
+          <t>+998 99 819-11-07</t>
         </is>
       </c>
       <c r="V391" t="inlineStr">
@@ -37613,6 +37894,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T392" t="inlineStr"/>
       <c r="V392" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37690,7 +37972,7 @@
       </c>
       <c r="T393" t="inlineStr">
         <is>
-          <t>880979477</t>
+          <t>+998 88 097-94-77</t>
         </is>
       </c>
       <c r="V393" t="inlineStr">
@@ -37768,6 +38050,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T394" t="inlineStr"/>
       <c r="V394" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37843,6 +38126,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T395" t="inlineStr"/>
       <c r="V395" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37920,7 +38204,7 @@
       </c>
       <c r="T396" t="inlineStr">
         <is>
-          <t>883892930</t>
+          <t>+998 88 389-29-30</t>
         </is>
       </c>
       <c r="V396" t="inlineStr">
@@ -38000,7 +38284,7 @@
       </c>
       <c r="T397" t="inlineStr">
         <is>
-          <t>908762272</t>
+          <t>+998 90 876-22-72</t>
         </is>
       </c>
       <c r="V397" t="inlineStr">
@@ -38033,6 +38317,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 140</t>
+        </is>
+      </c>
       <c r="G398" t="inlineStr">
         <is>
           <t>Sheraliyevna</t>
@@ -38080,7 +38369,7 @@
       </c>
       <c r="T398" t="inlineStr">
         <is>
-          <t>914636267</t>
+          <t>+998 91 463-62-67</t>
         </is>
       </c>
       <c r="V398" t="inlineStr">
@@ -38113,6 +38402,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>25/26 SH/A149</t>
+        </is>
+      </c>
       <c r="G399" t="inlineStr">
         <is>
           <t>Hamzaxon qizi</t>
@@ -38160,7 +38454,7 @@
       </c>
       <c r="T399" t="inlineStr">
         <is>
-          <t>908745552</t>
+          <t>+998 90 874-55-52</t>
         </is>
       </c>
       <c r="V399" t="inlineStr">
@@ -38238,6 +38532,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T400" t="inlineStr"/>
       <c r="V400" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38315,7 +38610,7 @@
       </c>
       <c r="T401" t="inlineStr">
         <is>
-          <t>886110082</t>
+          <t>+998 88 611-00-82</t>
         </is>
       </c>
       <c r="V401" t="inlineStr">
@@ -38393,6 +38688,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T402" t="inlineStr"/>
       <c r="V402" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38468,6 +38764,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T403" t="inlineStr"/>
       <c r="V403" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38498,6 +38795,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 142</t>
+        </is>
+      </c>
       <c r="G404" t="inlineStr">
         <is>
           <t>Mansur qizi</t>
@@ -38543,6 +38845,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T404" t="inlineStr"/>
       <c r="V404" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38573,6 +38876,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>25/26 SH/A150</t>
+        </is>
+      </c>
       <c r="G405" t="inlineStr">
         <is>
           <t>Muhiddin qizi</t>
@@ -38620,7 +38928,7 @@
       </c>
       <c r="T405" t="inlineStr">
         <is>
-          <t>500069607</t>
+          <t>+998 50 006-96-07</t>
         </is>
       </c>
       <c r="V405" t="inlineStr">
@@ -38700,7 +39008,7 @@
       </c>
       <c r="T406" t="inlineStr">
         <is>
-          <t>883858414</t>
+          <t>+998 88 385-84-14</t>
         </is>
       </c>
       <c r="V406" t="inlineStr">
@@ -38780,7 +39088,7 @@
       </c>
       <c r="T407" t="inlineStr">
         <is>
-          <t>978008474</t>
+          <t>+998 97 800-84-74</t>
         </is>
       </c>
       <c r="V407" t="inlineStr">
@@ -38858,6 +39166,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T408" t="inlineStr"/>
       <c r="V408" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38933,6 +39242,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T409" t="inlineStr"/>
       <c r="V409" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39010,7 +39320,7 @@
       </c>
       <c r="T410" t="inlineStr">
         <is>
-          <t>976447414</t>
+          <t>+998 97 644-74-14</t>
         </is>
       </c>
       <c r="V410" t="inlineStr">
@@ -39088,6 +39398,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T411" t="inlineStr"/>
       <c r="V411" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39165,7 +39476,7 @@
       </c>
       <c r="T412" t="inlineStr">
         <is>
-          <t>881640078</t>
+          <t>+998 88 164-00-78</t>
         </is>
       </c>
       <c r="V412" t="inlineStr">
@@ -39245,7 +39556,7 @@
       </c>
       <c r="T413" t="inlineStr">
         <is>
-          <t>771108681</t>
+          <t>+998 77 110-86-81</t>
         </is>
       </c>
       <c r="V413" t="inlineStr">
@@ -39278,6 +39589,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>26/27 SH/A66</t>
+        </is>
+      </c>
       <c r="G414" t="inlineStr">
         <is>
           <t>Ozod o'g'li</t>
@@ -39325,7 +39641,7 @@
       </c>
       <c r="T414" t="inlineStr">
         <is>
-          <t>887860115</t>
+          <t>+998 88 786-01-15</t>
         </is>
       </c>
       <c r="V414" t="inlineStr">
@@ -39403,6 +39719,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T415" t="inlineStr"/>
       <c r="V415" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39480,7 +39797,7 @@
       </c>
       <c r="T416" t="inlineStr">
         <is>
-          <t>908857597</t>
+          <t>+998 90 885-75-97</t>
         </is>
       </c>
       <c r="V416" t="inlineStr">
@@ -39558,6 +39875,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T417" t="inlineStr"/>
       <c r="V417" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39633,6 +39951,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T418" t="inlineStr"/>
       <c r="V418" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39708,6 +40027,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T419" t="inlineStr"/>
       <c r="V419" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39783,6 +40103,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T420" t="inlineStr"/>
       <c r="V420" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39860,7 +40181,7 @@
       </c>
       <c r="T421" t="inlineStr">
         <is>
-          <t>906397808</t>
+          <t>+998 90 639-78-08</t>
         </is>
       </c>
       <c r="V421" t="inlineStr">
@@ -39943,6 +40264,7 @@
           <t>2008</t>
         </is>
       </c>
+      <c r="T422" t="inlineStr"/>
       <c r="V422" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39973,6 +40295,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 74</t>
+        </is>
+      </c>
       <c r="G423" t="inlineStr">
         <is>
           <t>Nishon qizi</t>
@@ -40020,7 +40347,7 @@
       </c>
       <c r="T423" t="inlineStr">
         <is>
-          <t>915970964</t>
+          <t>+998 91 597-09-64</t>
         </is>
       </c>
       <c r="V423" t="inlineStr">
@@ -40105,7 +40432,7 @@
       </c>
       <c r="T424" t="inlineStr">
         <is>
-          <t>883823800 / 914510727</t>
+          <t>+998 88 382-38-00 / +998 91 451-07-27 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V424" t="inlineStr">
@@ -40185,7 +40512,7 @@
       </c>
       <c r="T425" t="inlineStr">
         <is>
-          <t>880790724</t>
+          <t>+998 88 079-07-24</t>
         </is>
       </c>
       <c r="V425" t="inlineStr">
@@ -40218,6 +40545,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 76</t>
+        </is>
+      </c>
       <c r="G426" t="inlineStr">
         <is>
           <t>Zafar qizi</t>
@@ -40263,6 +40595,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T426" t="inlineStr"/>
       <c r="V426" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40340,7 +40673,7 @@
       </c>
       <c r="T427" t="inlineStr">
         <is>
-          <t>999681288</t>
+          <t>+998 99 968-12-88</t>
         </is>
       </c>
       <c r="V427" t="inlineStr">
@@ -40373,6 +40706,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 78</t>
+        </is>
+      </c>
       <c r="G428" t="inlineStr">
         <is>
           <t>Elyorjon qizi</t>
@@ -40420,7 +40758,7 @@
       </c>
       <c r="T428" t="inlineStr">
         <is>
-          <t>916448265</t>
+          <t>+998 91 644-82-65</t>
         </is>
       </c>
       <c r="V428" t="inlineStr">
@@ -40453,6 +40791,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A79</t>
+        </is>
+      </c>
       <c r="G429" t="inlineStr">
         <is>
           <t>Ziyodulla qizi</t>
@@ -40498,6 +40841,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T429" t="inlineStr"/>
       <c r="V429" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40575,7 +40919,7 @@
       </c>
       <c r="T430" t="inlineStr">
         <is>
-          <t>884240448</t>
+          <t>+998 88 424-04-48</t>
         </is>
       </c>
       <c r="V430" t="inlineStr">
@@ -40653,6 +40997,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T431" t="inlineStr"/>
       <c r="V431" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40683,6 +41028,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 385</t>
+        </is>
+      </c>
       <c r="G432" t="inlineStr">
         <is>
           <t>Abduvoxid qizi</t>
@@ -40730,7 +41080,7 @@
       </c>
       <c r="T432" t="inlineStr">
         <is>
-          <t>970277807</t>
+          <t>+998 97 027-78-07</t>
         </is>
       </c>
       <c r="V432" t="inlineStr">
@@ -40808,6 +41158,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T433" t="inlineStr"/>
       <c r="V433" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40885,7 +41236,7 @@
       </c>
       <c r="T434" t="inlineStr">
         <is>
-          <t>992756184</t>
+          <t>+998 99 275-61-84</t>
         </is>
       </c>
       <c r="V434" t="inlineStr">
@@ -40963,6 +41314,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T435" t="inlineStr"/>
       <c r="V435" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40993,6 +41345,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 159</t>
+        </is>
+      </c>
       <c r="G436" t="inlineStr">
         <is>
           <t>Gulamovna</t>
@@ -41040,7 +41397,7 @@
       </c>
       <c r="T436" t="inlineStr">
         <is>
-          <t>932284551</t>
+          <t>+998 93 228-45-51</t>
         </is>
       </c>
       <c r="V436" t="inlineStr">
@@ -41073,6 +41430,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 177</t>
+        </is>
+      </c>
       <c r="G437" t="inlineStr">
         <is>
           <t>Sodiq qizi</t>
@@ -41118,6 +41480,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T437" t="inlineStr"/>
       <c r="V437" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41195,7 +41558,7 @@
       </c>
       <c r="T438" t="inlineStr">
         <is>
-          <t>334021770</t>
+          <t>+998 33 402-17-70</t>
         </is>
       </c>
       <c r="V438" t="inlineStr">
@@ -41273,6 +41636,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T439" t="inlineStr"/>
       <c r="V439" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41350,7 +41714,7 @@
       </c>
       <c r="T440" t="inlineStr">
         <is>
-          <t>919453085</t>
+          <t>+998 91 945-30-85</t>
         </is>
       </c>
       <c r="V440" t="inlineStr">
@@ -41428,6 +41792,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T441" t="inlineStr"/>
       <c r="V441" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41503,6 +41868,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T442" t="inlineStr"/>
       <c r="V442" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41533,6 +41899,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A94</t>
+        </is>
+      </c>
       <c r="G443" t="inlineStr">
         <is>
           <t>Orif qizi</t>
@@ -41578,6 +41949,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T443" t="inlineStr"/>
       <c r="V443" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41655,7 +42027,7 @@
       </c>
       <c r="T444" t="inlineStr">
         <is>
-          <t>887537800</t>
+          <t>+998 88 753-78-00</t>
         </is>
       </c>
       <c r="V444" t="inlineStr">
@@ -41733,11 +42105,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T445" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
+      <c r="T445" t="inlineStr"/>
       <c r="V445" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41768,6 +42136,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 98</t>
+        </is>
+      </c>
       <c r="G446" t="inlineStr">
         <is>
           <t>Nuriddin qizi</t>
@@ -41815,7 +42188,7 @@
       </c>
       <c r="T446" t="inlineStr">
         <is>
-          <t>979708727</t>
+          <t>+998 97 970-87-27</t>
         </is>
       </c>
       <c r="V446" t="inlineStr">
@@ -41895,7 +42268,7 @@
       </c>
       <c r="T447" t="inlineStr">
         <is>
-          <t>884906402</t>
+          <t>+998 88 490-64-02</t>
         </is>
       </c>
       <c r="V447" t="inlineStr">
@@ -41928,6 +42301,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 100</t>
+        </is>
+      </c>
       <c r="G448" t="inlineStr">
         <is>
           <t>Habibullo qizi</t>
@@ -41975,7 +42353,7 @@
       </c>
       <c r="T448" t="inlineStr">
         <is>
-          <t>906778076</t>
+          <t>+998 90 677-80-76</t>
         </is>
       </c>
       <c r="V448" t="inlineStr">
@@ -42055,7 +42433,7 @@
       </c>
       <c r="T449" t="inlineStr">
         <is>
-          <t>888058587</t>
+          <t>+998 88 805-85-87</t>
         </is>
       </c>
       <c r="V449" t="inlineStr">
@@ -42135,7 +42513,7 @@
       </c>
       <c r="T450" t="inlineStr">
         <is>
-          <t>919471088</t>
+          <t>+998 91 947-10-88</t>
         </is>
       </c>
       <c r="V450" t="inlineStr">
@@ -42168,6 +42546,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A 103</t>
+        </is>
+      </c>
       <c r="G451" t="inlineStr">
         <is>
           <t>Dagar qizi</t>
@@ -42215,7 +42598,7 @@
       </c>
       <c r="T451" t="inlineStr">
         <is>
-          <t>919616175</t>
+          <t>+998 91 961-61-75</t>
         </is>
       </c>
       <c r="V451" t="inlineStr">
@@ -42295,7 +42678,7 @@
       </c>
       <c r="T452" t="inlineStr">
         <is>
-          <t>992223551</t>
+          <t>+998 99 222-35-51</t>
         </is>
       </c>
       <c r="V452" t="inlineStr">
@@ -42328,6 +42711,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>26/27 SH/A105</t>
+        </is>
+      </c>
       <c r="G453" t="inlineStr">
         <is>
           <t>G'ulomjon qizi</t>
@@ -42375,7 +42763,7 @@
       </c>
       <c r="T453" t="inlineStr">
         <is>
-          <t>904532125</t>
+          <t>+998 90 453-21-25</t>
         </is>
       </c>
       <c r="V453" t="inlineStr">
@@ -42408,6 +42796,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>26/27 SH/A106</t>
+        </is>
+      </c>
       <c r="G454" t="inlineStr">
         <is>
           <t>Qudratilla qizi</t>
@@ -42455,7 +42848,7 @@
       </c>
       <c r="T454" t="inlineStr">
         <is>
-          <t>774980728</t>
+          <t>+998 77 498-07-28</t>
         </is>
       </c>
       <c r="V454" t="inlineStr">
@@ -42488,6 +42881,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 229</t>
+        </is>
+      </c>
       <c r="G455" t="inlineStr">
         <is>
           <t>Gulmurod qizi</t>
@@ -42535,7 +42933,7 @@
       </c>
       <c r="T455" t="inlineStr">
         <is>
-          <t>916335473</t>
+          <t>+998 91 633-54-73</t>
         </is>
       </c>
       <c r="V455" t="inlineStr">
@@ -42615,7 +43013,7 @@
       </c>
       <c r="T456" t="inlineStr">
         <is>
-          <t>881236547</t>
+          <t>+998 88 123-65-47</t>
         </is>
       </c>
       <c r="V456" t="inlineStr">
@@ -42695,7 +43093,7 @@
       </c>
       <c r="T457" t="inlineStr">
         <is>
-          <t>900707178</t>
+          <t>+998 90 070-71-78</t>
         </is>
       </c>
       <c r="V457" t="inlineStr">
@@ -42775,7 +43173,7 @@
       </c>
       <c r="T458" t="inlineStr">
         <is>
-          <t>977994948</t>
+          <t>+998 97 799-49-48</t>
         </is>
       </c>
       <c r="V458" t="inlineStr">
@@ -42855,7 +43253,7 @@
       </c>
       <c r="T459" t="inlineStr">
         <is>
-          <t>883897872</t>
+          <t>+998 88 389-78-72</t>
         </is>
       </c>
       <c r="V459" t="inlineStr">
@@ -42935,7 +43333,7 @@
       </c>
       <c r="T460" t="inlineStr">
         <is>
-          <t>908730778</t>
+          <t>+998 90 873-07-78</t>
         </is>
       </c>
       <c r="V460" t="inlineStr">
@@ -43013,6 +43411,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T461" t="inlineStr"/>
       <c r="V461" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -43043,6 +43442,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A114</t>
+        </is>
+      </c>
       <c r="G462" t="inlineStr">
         <is>
           <t>Baxodir qizi</t>
@@ -43090,7 +43494,7 @@
       </c>
       <c r="T462" t="inlineStr">
         <is>
-          <t>974569312</t>
+          <t>+998 97 456-93-12</t>
         </is>
       </c>
       <c r="V462" t="inlineStr">
@@ -43170,7 +43574,7 @@
       </c>
       <c r="T463" t="inlineStr">
         <is>
-          <t>880556808</t>
+          <t>+998 88 055-68-08</t>
         </is>
       </c>
       <c r="V463" t="inlineStr">
@@ -43255,7 +43659,7 @@
       </c>
       <c r="T464" t="inlineStr">
         <is>
-          <t>886341692 / 973868774</t>
+          <t>+998 88 634-16-92 / +998 97 386-87-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V464" t="inlineStr">
@@ -43333,6 +43737,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T465" t="inlineStr"/>
       <c r="V465" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -43408,6 +43813,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T466" t="inlineStr"/>
       <c r="V466" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -43485,7 +43891,7 @@
       </c>
       <c r="T467" t="inlineStr">
         <is>
-          <t>977993969</t>
+          <t>+998 97 799-39-69</t>
         </is>
       </c>
       <c r="V467" t="inlineStr">
@@ -43565,7 +43971,7 @@
       </c>
       <c r="T468" t="inlineStr">
         <is>
-          <t>990959732</t>
+          <t>+998 99 095-97-32</t>
         </is>
       </c>
       <c r="V468" t="inlineStr">
@@ -43645,7 +44051,7 @@
       </c>
       <c r="T469" t="inlineStr">
         <is>
-          <t>945479080</t>
+          <t>+998 94 547-90-80</t>
         </is>
       </c>
       <c r="V469" t="inlineStr">
@@ -43723,6 +44129,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T470" t="inlineStr"/>
       <c r="V470" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -43753,6 +44160,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>26/27 SH/A123</t>
+        </is>
+      </c>
       <c r="G471" t="inlineStr">
         <is>
           <t>Qalandar qizi</t>
@@ -43800,7 +44212,7 @@
       </c>
       <c r="T471" t="inlineStr">
         <is>
-          <t>887687008</t>
+          <t>+998 88 768-70-08</t>
         </is>
       </c>
       <c r="V471" t="inlineStr">
@@ -43833,6 +44245,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>26/27 SH/A174</t>
+        </is>
+      </c>
       <c r="G472" t="inlineStr">
         <is>
           <t>Shuxrat qizi</t>
@@ -43880,7 +44297,7 @@
       </c>
       <c r="T472" t="inlineStr">
         <is>
-          <t>770428225</t>
+          <t>+998 77 042-82-25</t>
         </is>
       </c>
       <c r="V472" t="inlineStr">
@@ -43913,6 +44330,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>26/37 SH/A 125</t>
+        </is>
+      </c>
       <c r="G473" t="inlineStr">
         <is>
           <t>Akmal qizi</t>
@@ -43960,7 +44382,7 @@
       </c>
       <c r="T473" t="inlineStr">
         <is>
-          <t>975877909</t>
+          <t>+998 97 587-79-09</t>
         </is>
       </c>
       <c r="V473" t="inlineStr">
@@ -44038,6 +44460,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T474" t="inlineStr"/>
       <c r="V474" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44120,7 +44543,7 @@
       </c>
       <c r="T475" t="inlineStr">
         <is>
-          <t>910702172 / 90008906</t>
+          <t>+998 91 070-21-72</t>
         </is>
       </c>
       <c r="V475" t="inlineStr">
@@ -44205,7 +44628,7 @@
       </c>
       <c r="T476" t="inlineStr">
         <is>
-          <t>332079255 / 973816690</t>
+          <t>+998 33 207-92-55 / +998 97 381-66-90 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V476" t="inlineStr">
@@ -44285,7 +44708,7 @@
       </c>
       <c r="T477" t="inlineStr">
         <is>
-          <t>912261607</t>
+          <t>+998 91 226-16-07</t>
         </is>
       </c>
       <c r="V477" t="inlineStr">
@@ -44370,7 +44793,7 @@
       </c>
       <c r="T478" t="inlineStr">
         <is>
-          <t>973512025 / 905170817</t>
+          <t>+998 97 351-20-25 / +998 90 517-08-17 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V478" t="inlineStr">
@@ -44448,6 +44871,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T479" t="inlineStr"/>
       <c r="V479" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44523,6 +44947,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T480" t="inlineStr"/>
       <c r="V480" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44553,6 +44978,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 264</t>
+        </is>
+      </c>
       <c r="G481" t="inlineStr">
         <is>
           <t>Nurbek qizi</t>
@@ -44598,6 +45028,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T481" t="inlineStr"/>
       <c r="V481" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44673,6 +45104,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T482" t="inlineStr"/>
       <c r="V482" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44748,6 +45180,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T483" t="inlineStr"/>
       <c r="V483" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44778,6 +45211,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 266</t>
+        </is>
+      </c>
       <c r="G484" t="inlineStr">
         <is>
           <t>Maqsudjon qizi</t>
@@ -44825,7 +45263,7 @@
       </c>
       <c r="T484" t="inlineStr">
         <is>
-          <t>976259907</t>
+          <t>+998 97 625-99-07</t>
         </is>
       </c>
       <c r="V484" t="inlineStr">
@@ -44858,6 +45296,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 272</t>
+        </is>
+      </c>
       <c r="G485" t="inlineStr">
         <is>
           <t>Rahmatovna</t>
@@ -44903,6 +45346,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T485" t="inlineStr"/>
       <c r="V485" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44985,7 +45429,7 @@
       </c>
       <c r="T486" t="inlineStr">
         <is>
-          <t>906792298 / 912245369</t>
+          <t>+998 90 679-22-98 / +998 91 224-53-69 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V486" t="inlineStr">
@@ -45018,6 +45462,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 369</t>
+        </is>
+      </c>
       <c r="G487" t="inlineStr">
         <is>
           <t>Qulmamatovna</t>
@@ -45070,7 +45519,7 @@
       </c>
       <c r="T487" t="inlineStr">
         <is>
-          <t>500303196 / 973841481</t>
+          <t>+998 50 030-31-96 / +998 97 384-14-81 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V487" t="inlineStr">
@@ -45148,6 +45597,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T488" t="inlineStr"/>
       <c r="V488" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45223,11 +45673,7 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T489" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
+      <c r="T489" t="inlineStr"/>
       <c r="V489" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45303,11 +45749,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T490" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
+      <c r="T490" t="inlineStr"/>
       <c r="V490" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45383,6 +45825,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T491" t="inlineStr"/>
       <c r="V491" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45458,11 +45901,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T492" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
+      <c r="T492" t="inlineStr"/>
       <c r="V492" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45538,6 +45977,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T493" t="inlineStr"/>
       <c r="V493" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45568,6 +46008,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 147</t>
+        </is>
+      </c>
       <c r="G494" t="inlineStr">
         <is>
           <t>Omonovna</t>
@@ -45620,7 +46065,7 @@
       </c>
       <c r="T494" t="inlineStr">
         <is>
-          <t>951880530</t>
+          <t>+998 95 188-05-30</t>
         </is>
       </c>
       <c r="V494" t="inlineStr">
@@ -45653,6 +46098,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 263</t>
+        </is>
+      </c>
       <c r="G495" t="inlineStr">
         <is>
           <t>Jasurbek qizi</t>
@@ -45698,6 +46148,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T495" t="inlineStr"/>
       <c r="V495" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45775,7 +46226,7 @@
       </c>
       <c r="T496" t="inlineStr">
         <is>
-          <t>886342828</t>
+          <t>+998 88 634-28-28</t>
         </is>
       </c>
       <c r="V496" t="inlineStr">
@@ -45853,6 +46304,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T497" t="inlineStr"/>
       <c r="V497" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45883,6 +46335,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 260</t>
+        </is>
+      </c>
       <c r="G498" t="inlineStr">
         <is>
           <t>Avlayor qizi</t>
@@ -45930,7 +46387,7 @@
       </c>
       <c r="T498" t="inlineStr">
         <is>
-          <t>774801903</t>
+          <t>+998 77 480-19-03</t>
         </is>
       </c>
       <c r="V498" t="inlineStr">
@@ -46008,6 +46465,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T499" t="inlineStr"/>
       <c r="V499" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46038,6 +46496,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>26/27 SH/A153</t>
+        </is>
+      </c>
       <c r="G500" t="inlineStr">
         <is>
           <t>Muzurovna</t>
@@ -46085,7 +46548,7 @@
       </c>
       <c r="T500" t="inlineStr">
         <is>
-          <t>918128421</t>
+          <t>+998 91 812-84-21</t>
         </is>
       </c>
       <c r="V500" t="inlineStr">
@@ -46163,6 +46626,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T501" t="inlineStr"/>
       <c r="V501" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46193,6 +46657,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 155</t>
+        </is>
+      </c>
       <c r="G502" t="inlineStr">
         <is>
           <t>Zokirjon qizi</t>
@@ -46238,11 +46707,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T502" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
+      <c r="T502" t="inlineStr"/>
       <c r="V502" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46320,7 +46785,7 @@
       </c>
       <c r="T503" t="inlineStr">
         <is>
-          <t>995697812</t>
+          <t>+998 99 569-78-12</t>
         </is>
       </c>
       <c r="V503" t="inlineStr">
@@ -46400,7 +46865,7 @@
       </c>
       <c r="T504" t="inlineStr">
         <is>
-          <t>994523698</t>
+          <t>+998 99 452-36-98</t>
         </is>
       </c>
       <c r="V504" t="inlineStr">
@@ -46480,7 +46945,7 @@
       </c>
       <c r="T505" t="inlineStr">
         <is>
-          <t>990565583</t>
+          <t>+998 99 056-55-83</t>
         </is>
       </c>
       <c r="V505" t="inlineStr">
@@ -46558,6 +47023,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T506" t="inlineStr"/>
       <c r="V506" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46633,6 +47099,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T507" t="inlineStr"/>
       <c r="V507" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46663,6 +47130,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>26/27 SH/A 161</t>
+        </is>
+      </c>
       <c r="G508" t="inlineStr">
         <is>
           <t>Nuriddin qizi</t>
@@ -46708,6 +47180,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T508" t="inlineStr"/>
       <c r="V508" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46783,6 +47256,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T509" t="inlineStr"/>
       <c r="V509" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46860,7 +47334,7 @@
       </c>
       <c r="T510" t="inlineStr">
         <is>
-          <t>882394999</t>
+          <t>+998 88 239-49-99</t>
         </is>
       </c>
       <c r="V510" t="inlineStr">
@@ -46940,7 +47414,7 @@
       </c>
       <c r="T511" t="inlineStr">
         <is>
-          <t>919614568</t>
+          <t>+998 91 961-45-68</t>
         </is>
       </c>
       <c r="V511" t="inlineStr">
@@ -46973,6 +47447,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>26/27 Sh/A165</t>
+        </is>
+      </c>
       <c r="G512" t="inlineStr">
         <is>
           <t>Zafariddin qizi</t>
@@ -47020,7 +47499,7 @@
       </c>
       <c r="T512" t="inlineStr">
         <is>
-          <t>337180106</t>
+          <t>+998 33 718-01-06</t>
         </is>
       </c>
       <c r="V512" t="inlineStr">
@@ -47098,6 +47577,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T513" t="inlineStr"/>
       <c r="V513" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47128,6 +47608,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A246</t>
+        </is>
+      </c>
       <c r="G514" t="inlineStr">
         <is>
           <t>Uktam qizi</t>
@@ -47173,6 +47658,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T514" t="inlineStr"/>
       <c r="V514" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47250,7 +47736,7 @@
       </c>
       <c r="T515" t="inlineStr">
         <is>
-          <t>884703107</t>
+          <t>+998 88 470-31-07</t>
         </is>
       </c>
       <c r="V515" t="inlineStr">
@@ -47328,6 +47814,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T516" t="inlineStr"/>
       <c r="V516" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47405,7 +47892,7 @@
       </c>
       <c r="T517" t="inlineStr">
         <is>
-          <t>906712597</t>
+          <t>+998 90 671-25-97</t>
         </is>
       </c>
       <c r="V517" t="inlineStr">
@@ -47438,6 +47925,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 338</t>
+        </is>
+      </c>
       <c r="G518" t="inlineStr">
         <is>
           <t>G'ayrat qizi</t>
@@ -47483,11 +47975,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T518" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
+      <c r="T518" t="inlineStr"/>
       <c r="V518" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47565,7 +48053,7 @@
       </c>
       <c r="T519" t="inlineStr">
         <is>
-          <t>884512402</t>
+          <t>+998 88 451-24-02</t>
         </is>
       </c>
       <c r="V519" t="inlineStr">
@@ -47643,6 +48131,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T520" t="inlineStr"/>
       <c r="V520" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47720,7 +48209,7 @@
       </c>
       <c r="T521" t="inlineStr">
         <is>
-          <t>908869594</t>
+          <t>+998 90 886-95-94</t>
         </is>
       </c>
       <c r="V521" t="inlineStr">
@@ -47798,6 +48287,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T522" t="inlineStr"/>
       <c r="V522" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47875,7 +48365,7 @@
       </c>
       <c r="T523" t="inlineStr">
         <is>
-          <t>904435716</t>
+          <t>+998 90 443-57-16</t>
         </is>
       </c>
       <c r="V523" t="inlineStr">
@@ -47953,6 +48443,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T524" t="inlineStr"/>
       <c r="V524" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47983,6 +48474,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>26/27 SH/A178</t>
+        </is>
+      </c>
       <c r="G525" t="inlineStr">
         <is>
           <t>Abdulla qizi</t>
@@ -48030,7 +48526,7 @@
       </c>
       <c r="T525" t="inlineStr">
         <is>
-          <t>884901396</t>
+          <t>+998 88 490-13-96</t>
         </is>
       </c>
       <c r="V525" t="inlineStr">
@@ -48110,7 +48606,7 @@
       </c>
       <c r="T526" t="inlineStr">
         <is>
-          <t>942094407</t>
+          <t>+998 94 209-44-07</t>
         </is>
       </c>
       <c r="V526" t="inlineStr">
@@ -48143,6 +48639,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>26/27 sh/a 180</t>
+        </is>
+      </c>
       <c r="G527" t="inlineStr">
         <is>
           <t>G'ayrat qizi</t>
@@ -48188,6 +48689,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T527" t="inlineStr"/>
       <c r="V527" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48258,11 +48760,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T528" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
+      <c r="T528" t="inlineStr"/>
       <c r="V528" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48338,6 +48836,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T529" t="inlineStr"/>
       <c r="V529" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48413,6 +48912,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T530" t="inlineStr"/>
       <c r="V530" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48495,7 +48995,7 @@
       </c>
       <c r="T531" t="inlineStr">
         <is>
-          <t>912185816</t>
+          <t>+998 91 218-58-16</t>
         </is>
       </c>
       <c r="V531" t="inlineStr">
@@ -48528,6 +49028,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A367</t>
+        </is>
+      </c>
       <c r="G532" t="inlineStr">
         <is>
           <t>Shuxrat qizi</t>
@@ -48580,7 +49085,7 @@
       </c>
       <c r="T532" t="inlineStr">
         <is>
-          <t>915979292 / 501118920</t>
+          <t>+998 91 597-92-92 / +998 50 111-89-20 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V532" t="inlineStr">
@@ -48613,6 +49118,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 375</t>
+        </is>
+      </c>
       <c r="G533" t="inlineStr">
         <is>
           <t>Ravshan qizi</t>
@@ -48665,7 +49175,7 @@
       </c>
       <c r="T533" t="inlineStr">
         <is>
-          <t>505109703 / 873227515</t>
+          <t>+998 50 510-97-03 / +998 87 322-75-15 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V533" t="inlineStr">
@@ -48750,7 +49260,7 @@
       </c>
       <c r="T534" t="inlineStr">
         <is>
-          <t>886323773 / 914708493</t>
+          <t>+998 88 632-37-73 / +998 91 470-84-93 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V534" t="inlineStr">
@@ -48828,6 +49338,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T535" t="inlineStr"/>
       <c r="V535" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48910,7 +49421,7 @@
       </c>
       <c r="T536" t="inlineStr">
         <is>
-          <t>918198931</t>
+          <t>+998 91 819-89-31</t>
         </is>
       </c>
       <c r="V536" t="inlineStr">
@@ -48988,6 +49499,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T537" t="inlineStr"/>
       <c r="V537" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49018,6 +49530,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 333</t>
+        </is>
+      </c>
       <c r="G538" t="inlineStr">
         <is>
           <t>Abdurashid qizi</t>
@@ -49063,6 +49580,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T538" t="inlineStr"/>
       <c r="V538" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49093,6 +49611,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>25/26 sh/a 33</t>
+        </is>
+      </c>
       <c r="G539" t="inlineStr">
         <is>
           <t>Azamat qizi</t>
@@ -49138,6 +49661,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T539" t="inlineStr"/>
       <c r="V539" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49213,6 +49737,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T540" t="inlineStr"/>
       <c r="V540" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49295,7 +49820,7 @@
       </c>
       <c r="T541" t="inlineStr">
         <is>
-          <t>975895253 / 873225253</t>
+          <t>+998 97 589-52-53 / +998 87 322-52-53 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V541" t="inlineStr">
@@ -49373,6 +49898,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T542" t="inlineStr"/>
       <c r="V542" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49455,7 +49981,7 @@
       </c>
       <c r="T543" t="inlineStr">
         <is>
-          <t>881309088 / 935831388</t>
+          <t>+998 88 130-90-88 / +998 93 583-13-88 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V543" t="inlineStr">
@@ -49488,6 +50014,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>25/26 SH/A358</t>
+        </is>
+      </c>
       <c r="G544" t="inlineStr">
         <is>
           <t>Jurayevna</t>
@@ -49540,7 +50071,7 @@
       </c>
       <c r="T544" t="inlineStr">
         <is>
-          <t>918142047 / 888040008</t>
+          <t>+998 91 814-20-47 / +998 88 804-00-08 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V544" t="inlineStr">
@@ -49625,7 +50156,7 @@
       </c>
       <c r="T545" t="inlineStr">
         <is>
-          <t>913211605</t>
+          <t>+998 91 321-16-05</t>
         </is>
       </c>
       <c r="V545" t="inlineStr">
@@ -49703,11 +50234,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T546" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
+      <c r="T546" t="inlineStr"/>
       <c r="V546" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49783,6 +50310,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T547" t="inlineStr"/>
       <c r="V547" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49813,6 +50341,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A361</t>
+        </is>
+      </c>
       <c r="G548" t="inlineStr">
         <is>
           <t>Sanjar qizi</t>
@@ -49865,7 +50398,7 @@
       </c>
       <c r="T548" t="inlineStr">
         <is>
-          <t>883862204 / 887789709</t>
+          <t>+998 88 386-22-04 / +998 88 778-97-09 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V548" t="inlineStr">
@@ -49943,11 +50476,7 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T549" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
+      <c r="T549" t="inlineStr"/>
       <c r="V549" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -50020,7 +50549,7 @@
       </c>
       <c r="T550" t="inlineStr">
         <is>
-          <t>991234567</t>
+          <t>+998 99 123-45-67</t>
         </is>
       </c>
       <c r="V550" t="inlineStr">
@@ -50053,6 +50582,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A 346</t>
+        </is>
+      </c>
       <c r="G551" t="inlineStr">
         <is>
           <t>Ruzimurod qizi</t>
@@ -50098,11 +50632,7 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T551" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
+      <c r="T551" t="inlineStr"/>
       <c r="V551" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -50133,6 +50663,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>25/26 Sh/A365</t>
+        </is>
+      </c>
       <c r="G552" t="inlineStr">
         <is>
           <t>Jamshid qizi</t>
@@ -50185,7 +50720,7 @@
       </c>
       <c r="T552" t="inlineStr">
         <is>
-          <t>916402192 / 883807881</t>
+          <t>+998 91 640-21-92 / +998 88 380-78-81 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V552" t="inlineStr">
@@ -50270,7 +50805,7 @@
       </c>
       <c r="T553" t="inlineStr">
         <is>
-          <t>919634966 / 908988509</t>
+          <t>+998 91 963-49-66 / +998 90 898-85-09 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V553" t="inlineStr">
@@ -50350,7 +50885,7 @@
       </c>
       <c r="T554" t="inlineStr">
         <is>
-          <t>973872825 / 912184436</t>
+          <t>+998 97 387-28-25 / +998 91 218-44-36 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V554" t="inlineStr">
@@ -50430,7 +50965,7 @@
       </c>
       <c r="T555" t="inlineStr">
         <is>
-          <t>770521563 / 770511563</t>
+          <t>+998 77 052-15-63 / +998 77 051-15-63 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V555" t="inlineStr">
@@ -50463,6 +50998,11 @@
           <t>Hamshiralik ishi</t>
         </is>
       </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 372</t>
+        </is>
+      </c>
       <c r="G556" t="inlineStr">
         <is>
           <t>Alisherovna</t>
@@ -50515,7 +51055,7 @@
       </c>
       <c r="T556" t="inlineStr">
         <is>
-          <t>777350767 / 973550702</t>
+          <t>+998 77 735-07-67 / +998 97 355-07-02 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="V556" t="inlineStr">
@@ -50593,6 +51133,7 @@
           <t>Kollej</t>
         </is>
       </c>
+      <c r="T557" t="inlineStr"/>
       <c r="V557" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -50668,6 +51209,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T558" t="inlineStr"/>
       <c r="U558" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -50758,6 +51300,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T559" t="inlineStr"/>
       <c r="U559" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -50848,6 +51391,7 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
+      <c r="T560" t="inlineStr"/>
       <c r="U560" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -50960,7 +51504,7 @@
       </c>
       <c r="T561" t="inlineStr">
         <is>
-          <t>887611310</t>
+          <t>+998 88 761-13-10</t>
         </is>
       </c>
       <c r="U561" t="inlineStr">
@@ -51003,6 +51547,11 @@
           <t>To'lov qildi</t>
         </is>
       </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>25/26 SH/A 511</t>
+        </is>
+      </c>
       <c r="F562" t="inlineStr">
         <is>
           <t>30.09.2026</t>
@@ -51065,7 +51614,7 @@
       </c>
       <c r="T562" t="inlineStr">
         <is>
-          <t>94-806-00-14</t>
+          <t>+998 94 806-00-14</t>
         </is>
       </c>
       <c r="U562" t="inlineStr">
@@ -51165,7 +51714,7 @@
       </c>
       <c r="T563" t="inlineStr">
         <is>
-          <t>773893666 / 606090757</t>
+          <t>+998 77 389-36-66 / +998 60 609-07-57 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="U563" t="inlineStr">

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -676,6 +676,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr">
         <is>
           <t>KIRITILDI</t>
@@ -796,6 +806,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -916,6 +936,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1031,6 +1061,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1151,6 +1191,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1321,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1451,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1581,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1696,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,7 +1791,6 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -1725,6 +1814,16 @@
       <c r="Y11" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -1847,6 +1946,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1962,6 +2071,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2082,6 +2201,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2192,6 +2321,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2312,6 +2443,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2432,6 +2573,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2552,6 +2703,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2672,6 +2833,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2787,6 +2958,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2897,6 +3078,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3008,6 +3199,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3123,6 +3324,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3238,6 +3449,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3348,6 +3569,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3468,6 +3699,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3573,6 +3814,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3693,6 +3944,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3794,6 +4055,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3909,6 +4180,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4017,6 +4298,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4137,6 +4428,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4257,6 +4558,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4332,7 +4643,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -4353,6 +4663,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4471,6 +4783,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4581,6 +4903,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4701,6 +5033,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4811,6 +5153,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4931,6 +5283,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5051,6 +5413,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5171,6 +5543,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5286,6 +5668,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5394,6 +5786,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5514,6 +5916,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5634,6 +6046,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5754,6 +6176,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5849,6 +6281,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5969,6 +6411,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6089,6 +6541,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6209,6 +6671,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6314,6 +6786,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6434,6 +6916,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6554,6 +7046,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6674,6 +7176,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6794,6 +7306,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6904,6 +7426,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7029,6 +7561,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7144,6 +7686,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7244,6 +7796,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7364,6 +7926,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7484,6 +8056,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7579,6 +8161,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7692,6 +8284,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7812,6 +8414,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7922,6 +8534,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8042,6 +8664,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8145,6 +8777,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8255,6 +8897,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8375,6 +9027,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8498,6 +9160,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8618,6 +9290,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8738,6 +9420,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8846,6 +9538,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8881,7 +9583,6 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -8907,6 +9608,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9027,6 +9730,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9142,6 +9855,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9262,6 +9985,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9377,6 +10110,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9495,6 +10238,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9580,7 +10333,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -9604,6 +10356,16 @@
       <c r="Y80" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9719,6 +10481,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9839,6 +10611,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9947,6 +10729,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10055,6 +10847,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10145,7 +10947,6 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr">
         <is>
           <t>To'liq</t>
@@ -10169,6 +10970,16 @@
       <c r="Y85" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -10271,6 +11082,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10366,6 +11187,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10446,7 +11277,6 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -10470,6 +11300,16 @@
       <c r="Y88" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -10552,7 +11392,6 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -10576,6 +11415,16 @@
       <c r="Y89" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -10698,6 +11547,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10808,6 +11667,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10928,6 +11797,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11048,6 +11927,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11168,6 +12057,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11293,6 +12192,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11403,6 +12312,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11473,7 +12392,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -11492,6 +12410,16 @@
       <c r="Y97" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -11609,6 +12537,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11717,6 +12655,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11837,6 +12785,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11957,6 +12915,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12072,6 +13040,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12182,6 +13160,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12302,6 +13290,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12422,6 +13420,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12532,6 +13540,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12657,6 +13675,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12777,6 +13805,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12897,6 +13935,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13002,6 +14050,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13092,7 +14150,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -13116,6 +14173,16 @@
       <c r="Y111" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -13236,6 +14303,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13351,6 +14428,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13421,7 +14508,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -13440,6 +14526,16 @@
       <c r="Y114" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -13557,6 +14653,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13672,6 +14778,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13792,6 +14908,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13902,6 +15028,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14022,6 +15158,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14142,6 +15288,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14257,6 +15413,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14367,6 +15533,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14487,6 +15663,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14607,6 +15793,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14727,6 +15923,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14842,6 +16048,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14922,7 +16138,6 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr">
         <is>
           <t>FAYL_YOQ</t>
@@ -14946,6 +16161,16 @@
       <c r="Y127" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -15054,6 +16279,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15169,6 +16404,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15289,6 +16534,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15399,6 +16654,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15514,6 +16779,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15629,6 +16904,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15744,6 +17029,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15864,6 +17159,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15974,6 +17279,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16084,6 +17399,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16204,6 +17529,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16319,6 +17654,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16434,6 +17779,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16549,6 +17904,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16664,6 +18029,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16779,6 +18154,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16897,6 +18282,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16992,6 +18387,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17112,6 +18517,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17215,6 +18630,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17340,6 +18765,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17450,6 +18885,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17563,6 +19008,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17683,6 +19138,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17798,6 +19263,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17917,6 +19392,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18015,6 +19500,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18135,6 +19630,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18250,6 +19755,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18368,6 +19883,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18488,6 +20013,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18608,6 +20143,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18731,6 +20276,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18846,6 +20401,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18941,6 +20506,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19061,6 +20636,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19174,6 +20759,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19294,6 +20889,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19414,6 +21019,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19539,6 +21154,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19654,6 +21279,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19774,6 +21409,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19894,6 +21539,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -20014,6 +21669,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20134,6 +21799,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20249,6 +21924,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>T-40/1</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20364,6 +22049,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20484,6 +22179,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20589,6 +22294,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20684,6 +22399,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20764,7 +22489,6 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr">
         <is>
           <t>Chala</t>
@@ -20778,6 +22502,16 @@
       <c r="Y178" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -20875,6 +22609,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20975,6 +22719,16 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21045,7 +22799,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -21059,6 +22812,16 @@
       <c r="W181" t="inlineStr">
         <is>
           <t>26-06</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -21131,7 +22894,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -21145,6 +22907,16 @@
       <c r="W182" t="inlineStr">
         <is>
           <t>26-02</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -21242,6 +23014,16 @@
           <t>26-02</t>
         </is>
       </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21317,7 +23099,6 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -21331,6 +23112,16 @@
       <c r="W184" t="inlineStr">
         <is>
           <t>26-02</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -21753,7 +23544,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-18</t>
@@ -21839,7 +23629,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
@@ -21925,7 +23714,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
@@ -21986,7 +23774,6 @@
           <t>26.05.2006</t>
         </is>
       </c>
-      <c r="T192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 201 (24-11)</t>
@@ -22162,7 +23949,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
@@ -22223,7 +24009,6 @@
           <t>11.07.2007</t>
         </is>
       </c>
-      <c r="T195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 203 (24-13)</t>
@@ -22274,7 +24059,6 @@
           <t>Omonova Dilorom Toshkent qizi</t>
         </is>
       </c>
-      <c r="T196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 24-12</t>
@@ -22335,7 +24119,6 @@
           <t>07.03.2005</t>
         </is>
       </c>
-      <c r="T197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 201 (24-11)</t>
@@ -22511,7 +24294,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-16</t>
@@ -22597,7 +24379,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
@@ -22615,12 +24396,12 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-31</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>17.04.2026</t>
         </is>
       </c>
     </row>
@@ -22683,7 +24464,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-21</t>
@@ -22699,6 +24479,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z201" t="inlineStr"/>
+      <c r="AA201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22824,7 +24606,6 @@
           <t>07.06.2006</t>
         </is>
       </c>
-      <c r="T203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 204 (24-14)</t>
@@ -22840,6 +24621,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z203" t="inlineStr"/>
+      <c r="AA203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22865,7 +24648,6 @@
           <t>To'rayeva Elsenora Sobir qizi</t>
         </is>
       </c>
-      <c r="T204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 24-12</t>
@@ -22971,6 +24753,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z205" t="inlineStr"/>
+      <c r="AA205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23051,6 +24835,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z206" t="inlineStr"/>
+      <c r="AA206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23111,7 +24897,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
@@ -23197,7 +24982,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T208" t="inlineStr"/>
       <c r="V208" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-20</t>
@@ -23283,7 +25067,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 25-16</t>
@@ -23369,7 +25152,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
@@ -23520,7 +25302,6 @@
           <t>12.04.2006</t>
         </is>
       </c>
-      <c r="T212" t="inlineStr"/>
       <c r="V212" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 202 (24-12)</t>
@@ -23606,7 +25387,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T213" t="inlineStr"/>
       <c r="V213" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
@@ -23757,7 +25537,6 @@
           <t>12.01.2004</t>
         </is>
       </c>
-      <c r="T215" t="inlineStr"/>
       <c r="V215" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 204 (24-14)</t>
@@ -23773,6 +25552,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z215" t="inlineStr"/>
+      <c r="AA215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23808,7 +25589,6 @@
           <t>22.06.2005</t>
         </is>
       </c>
-      <c r="T216" t="inlineStr"/>
       <c r="V216" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 205 (24-15)</t>
@@ -23894,7 +25674,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T217" t="inlineStr"/>
       <c r="V217" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-16</t>
@@ -23955,7 +25734,6 @@
           <t>28.08.2002</t>
         </is>
       </c>
-      <c r="T218" t="inlineStr"/>
       <c r="V218" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 203 (24-13)</t>
@@ -24306,7 +26084,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T222" t="inlineStr"/>
       <c r="V222" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-20</t>
@@ -24322,6 +26099,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z222" t="inlineStr"/>
+      <c r="AA222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24382,7 +26161,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T223" t="inlineStr"/>
       <c r="V223" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
@@ -24443,7 +26221,6 @@
           <t>07.04.2006</t>
         </is>
       </c>
-      <c r="T224" t="inlineStr"/>
       <c r="V224" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 202 (24-12)</t>
@@ -24459,6 +26236,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z224" t="inlineStr"/>
+      <c r="AA224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24494,7 +26273,6 @@
           <t>14.05.2006</t>
         </is>
       </c>
-      <c r="T225" t="inlineStr"/>
       <c r="V225" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs, oldingi guruh 203 (24-13)</t>
@@ -24555,7 +26333,6 @@
           <t>13.05.2006</t>
         </is>
       </c>
-      <c r="T226" t="inlineStr"/>
       <c r="V226" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
@@ -24571,6 +26348,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z226" t="inlineStr"/>
+      <c r="AA226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24721,7 +26500,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T228" t="inlineStr"/>
       <c r="V228" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
@@ -24782,7 +26560,6 @@
           <t>29.12.2000</t>
         </is>
       </c>
-      <c r="T229" t="inlineStr"/>
       <c r="V229" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 205 (24-15)</t>
@@ -24843,7 +26620,6 @@
           <t>19.05.2007</t>
         </is>
       </c>
-      <c r="T230" t="inlineStr"/>
       <c r="V230" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 203 (24-13)</t>
@@ -24859,6 +26635,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z230" t="inlineStr"/>
+      <c r="AA230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25094,7 +26872,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T233" t="inlineStr"/>
       <c r="V233" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
@@ -25175,7 +26952,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T234" t="inlineStr"/>
       <c r="V234" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
@@ -25256,7 +27032,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T235" t="inlineStr"/>
       <c r="V235" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
@@ -25452,6 +27227,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z237" t="inlineStr"/>
+      <c r="AA237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25537,6 +27314,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z238" t="inlineStr"/>
+      <c r="AA238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25622,6 +27401,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z239" t="inlineStr"/>
+      <c r="AA239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -25707,6 +27488,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z240" t="inlineStr"/>
+      <c r="AA240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -25787,6 +27570,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z241" t="inlineStr"/>
+      <c r="AA241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -25867,6 +27652,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z242" t="inlineStr"/>
+      <c r="AA242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -25947,6 +27734,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z243" t="inlineStr"/>
+      <c r="AA243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26027,6 +27816,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z244" t="inlineStr"/>
+      <c r="AA244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26112,6 +27903,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z245" t="inlineStr"/>
+      <c r="AA245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26192,6 +27985,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z246" t="inlineStr"/>
+      <c r="AA246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26272,6 +28067,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z247" t="inlineStr"/>
+      <c r="AA247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26352,6 +28149,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z248" t="inlineStr"/>
+      <c r="AA248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -26432,6 +28231,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z249" t="inlineStr"/>
+      <c r="AA249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -26512,6 +28313,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z250" t="inlineStr"/>
+      <c r="AA250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -26592,6 +28395,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z251" t="inlineStr"/>
+      <c r="AA251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -26677,6 +28482,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z252" t="inlineStr"/>
+      <c r="AA252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -26762,6 +28569,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z253" t="inlineStr"/>
+      <c r="AA253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -26847,6 +28656,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z254" t="inlineStr"/>
+      <c r="AA254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -26927,6 +28738,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z255" t="inlineStr"/>
+      <c r="AA255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27012,6 +28825,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z256" t="inlineStr"/>
+      <c r="AA256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -27092,6 +28907,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z257" t="inlineStr"/>
+      <c r="AA257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -27172,6 +28989,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z258" t="inlineStr"/>
+      <c r="AA258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -27252,6 +29071,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z259" t="inlineStr"/>
+      <c r="AA259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -27332,6 +29153,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z260" t="inlineStr"/>
+      <c r="AA260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -27412,6 +29235,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z261" t="inlineStr"/>
+      <c r="AA261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -27492,6 +29317,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z262" t="inlineStr"/>
+      <c r="AA262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -27572,6 +29399,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z263" t="inlineStr"/>
+      <c r="AA263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -27652,6 +29481,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z264" t="inlineStr"/>
+      <c r="AA264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -27732,6 +29563,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z265" t="inlineStr"/>
+      <c r="AA265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -27812,6 +29645,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z266" t="inlineStr"/>
+      <c r="AA266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -27892,6 +29727,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z267" t="inlineStr"/>
+      <c r="AA267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -27972,6 +29809,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z268" t="inlineStr"/>
+      <c r="AA268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -28052,6 +29891,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z269" t="inlineStr"/>
+      <c r="AA269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -28132,6 +29973,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z270" t="inlineStr"/>
+      <c r="AA270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -28217,6 +30060,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z271" t="inlineStr"/>
+      <c r="AA271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -28297,6 +30142,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z272" t="inlineStr"/>
+      <c r="AA272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -28382,6 +30229,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z273" t="inlineStr"/>
+      <c r="AA273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -28467,6 +30316,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z274" t="inlineStr"/>
+      <c r="AA274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -28552,6 +30403,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z275" t="inlineStr"/>
+      <c r="AA275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -28632,6 +30485,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z276" t="inlineStr"/>
+      <c r="AA276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -28717,6 +30572,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z277" t="inlineStr"/>
+      <c r="AA277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -28797,6 +30654,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z278" t="inlineStr"/>
+      <c r="AA278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -28877,6 +30736,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z279" t="inlineStr"/>
+      <c r="AA279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -28957,6 +30818,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z280" t="inlineStr"/>
+      <c r="AA280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -29037,6 +30900,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z281" t="inlineStr"/>
+      <c r="AA281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -29117,6 +30982,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z282" t="inlineStr"/>
+      <c r="AA282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -29197,6 +31064,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z283" t="inlineStr"/>
+      <c r="AA283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -29277,6 +31146,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z284" t="inlineStr"/>
+      <c r="AA284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -29357,6 +31228,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z285" t="inlineStr"/>
+      <c r="AA285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -29437,6 +31310,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z286" t="inlineStr"/>
+      <c r="AA286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -29517,6 +31392,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z287" t="inlineStr"/>
+      <c r="AA287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -29597,6 +31474,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z288" t="inlineStr"/>
+      <c r="AA288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -29682,6 +31561,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z289" t="inlineStr"/>
+      <c r="AA289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -29762,6 +31643,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z290" t="inlineStr"/>
+      <c r="AA290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -29842,6 +31725,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z291" t="inlineStr"/>
+      <c r="AA291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -29922,6 +31807,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z292" t="inlineStr"/>
+      <c r="AA292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -30007,6 +31894,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z293" t="inlineStr"/>
+      <c r="AA293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -30092,6 +31981,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z294" t="inlineStr"/>
+      <c r="AA294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -30172,6 +32063,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z295" t="inlineStr"/>
+      <c r="AA295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -30252,6 +32145,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z296" t="inlineStr"/>
+      <c r="AA296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -30332,6 +32227,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z297" t="inlineStr"/>
+      <c r="AA297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -30412,6 +32309,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z298" t="inlineStr"/>
+      <c r="AA298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -30492,6 +32391,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z299" t="inlineStr"/>
+      <c r="AA299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -30572,6 +32473,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z300" t="inlineStr"/>
+      <c r="AA300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -30657,6 +32560,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z301" t="inlineStr"/>
+      <c r="AA301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -30742,6 +32647,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z302" t="inlineStr"/>
+      <c r="AA302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -30822,6 +32729,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z303" t="inlineStr"/>
+      <c r="AA303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -30902,6 +32811,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z304" t="inlineStr"/>
+      <c r="AA304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -30982,6 +32893,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z305" t="inlineStr"/>
+      <c r="AA305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -31067,6 +32980,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z306" t="inlineStr"/>
+      <c r="AA306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -31147,6 +33062,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z307" t="inlineStr"/>
+      <c r="AA307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -31227,6 +33144,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z308" t="inlineStr"/>
+      <c r="AA308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -31307,6 +33226,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z309" t="inlineStr"/>
+      <c r="AA309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -31387,6 +33308,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z310" t="inlineStr"/>
+      <c r="AA310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -31467,6 +33390,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z311" t="inlineStr"/>
+      <c r="AA311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -31552,6 +33477,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z312" t="inlineStr"/>
+      <c r="AA312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -31632,6 +33559,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z313" t="inlineStr"/>
+      <c r="AA313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -31712,6 +33641,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z314" t="inlineStr"/>
+      <c r="AA314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -31792,6 +33723,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z315" t="inlineStr"/>
+      <c r="AA315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -31877,6 +33810,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z316" t="inlineStr"/>
+      <c r="AA316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -31957,6 +33892,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z317" t="inlineStr"/>
+      <c r="AA317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -32037,6 +33974,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z318" t="inlineStr"/>
+      <c r="AA318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -32122,6 +34061,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z319" t="inlineStr"/>
+      <c r="AA319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -32202,6 +34143,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z320" t="inlineStr"/>
+      <c r="AA320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -32282,6 +34225,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z321" t="inlineStr"/>
+      <c r="AA321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -32362,6 +34307,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z322" t="inlineStr"/>
+      <c r="AA322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -32442,6 +34389,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z323" t="inlineStr"/>
+      <c r="AA323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -32522,6 +34471,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z324" t="inlineStr"/>
+      <c r="AA324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -32602,6 +34553,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z325" t="inlineStr"/>
+      <c r="AA325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -32682,6 +34635,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z326" t="inlineStr"/>
+      <c r="AA326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -32762,6 +34717,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z327" t="inlineStr"/>
+      <c r="AA327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -32842,6 +34799,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z328" t="inlineStr"/>
+      <c r="AA328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -32922,6 +34881,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z329" t="inlineStr"/>
+      <c r="AA329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -33007,6 +34968,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z330" t="inlineStr"/>
+      <c r="AA330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -33087,6 +35050,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z331" t="inlineStr"/>
+      <c r="AA331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -33167,6 +35132,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z332" t="inlineStr"/>
+      <c r="AA332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -33247,6 +35214,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z333" t="inlineStr"/>
+      <c r="AA333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -33307,7 +35276,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T334" t="inlineStr"/>
       <c r="V334" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -33323,6 +35291,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z334" t="inlineStr"/>
+      <c r="AA334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -33408,6 +35378,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z335" t="inlineStr"/>
+      <c r="AA335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -33488,6 +35460,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z336" t="inlineStr"/>
+      <c r="AA336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -33573,6 +35547,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z337" t="inlineStr"/>
+      <c r="AA337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -33653,6 +35629,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z338" t="inlineStr"/>
+      <c r="AA338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -33733,6 +35711,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z339" t="inlineStr"/>
+      <c r="AA339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -33813,6 +35793,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z340" t="inlineStr"/>
+      <c r="AA340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -33893,6 +35875,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z341" t="inlineStr"/>
+      <c r="AA341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -33973,6 +35957,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z342" t="inlineStr"/>
+      <c r="AA342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -34053,6 +36039,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z343" t="inlineStr"/>
+      <c r="AA343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -34113,7 +36101,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T344" t="inlineStr"/>
       <c r="V344" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34129,6 +36116,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z344" t="inlineStr"/>
+      <c r="AA344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -34214,6 +36203,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z345" t="inlineStr"/>
+      <c r="AA345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -34274,7 +36265,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T346" t="inlineStr"/>
       <c r="V346" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34290,6 +36280,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z346" t="inlineStr"/>
+      <c r="AA346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -34350,7 +36342,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T347" t="inlineStr"/>
       <c r="V347" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34366,6 +36357,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z347" t="inlineStr"/>
+      <c r="AA347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -34431,7 +36424,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T348" t="inlineStr"/>
       <c r="V348" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34447,6 +36439,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z348" t="inlineStr"/>
+      <c r="AA348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -34527,6 +36521,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z349" t="inlineStr"/>
+      <c r="AA349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -34587,7 +36583,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T350" t="inlineStr"/>
       <c r="V350" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34603,6 +36598,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z350" t="inlineStr"/>
+      <c r="AA350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -34663,7 +36660,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T351" t="inlineStr"/>
       <c r="V351" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34679,6 +36675,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z351" t="inlineStr"/>
+      <c r="AA351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -34739,7 +36737,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T352" t="inlineStr"/>
       <c r="V352" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34755,6 +36752,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z352" t="inlineStr"/>
+      <c r="AA352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -34835,6 +36834,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z353" t="inlineStr"/>
+      <c r="AA353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -34895,7 +36896,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T354" t="inlineStr"/>
       <c r="V354" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -34911,6 +36911,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z354" t="inlineStr"/>
+      <c r="AA354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -34991,6 +36993,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z355" t="inlineStr"/>
+      <c r="AA355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -35051,7 +37055,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T356" t="inlineStr"/>
       <c r="V356" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35067,6 +37070,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z356" t="inlineStr"/>
+      <c r="AA356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -35127,7 +37132,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T357" t="inlineStr"/>
       <c r="V357" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35143,6 +37147,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z357" t="inlineStr"/>
+      <c r="AA357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -35223,6 +37229,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z358" t="inlineStr"/>
+      <c r="AA358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -35283,7 +37291,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T359" t="inlineStr"/>
       <c r="V359" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35299,6 +37306,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z359" t="inlineStr"/>
+      <c r="AA359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -35359,7 +37368,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T360" t="inlineStr"/>
       <c r="V360" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35375,6 +37383,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z360" t="inlineStr"/>
+      <c r="AA360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -35455,6 +37465,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z361" t="inlineStr"/>
+      <c r="AA361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -35535,6 +37547,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z362" t="inlineStr"/>
+      <c r="AA362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -35620,6 +37634,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z363" t="inlineStr"/>
+      <c r="AA363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -35680,7 +37696,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T364" t="inlineStr"/>
       <c r="V364" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35696,6 +37711,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z364" t="inlineStr"/>
+      <c r="AA364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -35781,6 +37798,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z365" t="inlineStr"/>
+      <c r="AA365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -35841,7 +37860,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T366" t="inlineStr"/>
       <c r="V366" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35857,6 +37875,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z366" t="inlineStr"/>
+      <c r="AA366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -35917,7 +37937,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T367" t="inlineStr"/>
       <c r="V367" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -35933,6 +37952,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z367" t="inlineStr"/>
+      <c r="AA367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -36013,6 +38034,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z368" t="inlineStr"/>
+      <c r="AA368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -36073,7 +38096,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T369" t="inlineStr"/>
       <c r="V369" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36089,6 +38111,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z369" t="inlineStr"/>
+      <c r="AA369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -36169,6 +38193,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z370" t="inlineStr"/>
+      <c r="AA370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -36254,6 +38280,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z371" t="inlineStr"/>
+      <c r="AA371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -36314,7 +38342,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T372" t="inlineStr"/>
       <c r="V372" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36330,6 +38357,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z372" t="inlineStr"/>
+      <c r="AA372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -36410,6 +38439,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z373" t="inlineStr"/>
+      <c r="AA373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -36490,6 +38521,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z374" t="inlineStr"/>
+      <c r="AA374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -36550,7 +38583,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T375" t="inlineStr"/>
       <c r="V375" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36566,6 +38598,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z375" t="inlineStr"/>
+      <c r="AA375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -36651,6 +38685,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z376" t="inlineStr"/>
+      <c r="AA376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -36731,6 +38767,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z377" t="inlineStr"/>
+      <c r="AA377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -36796,7 +38834,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T378" t="inlineStr"/>
       <c r="V378" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36812,6 +38849,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z378" t="inlineStr"/>
+      <c r="AA378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -36872,7 +38911,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T379" t="inlineStr"/>
       <c r="V379" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -36888,6 +38926,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z379" t="inlineStr"/>
+      <c r="AA379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -36973,6 +39013,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z380" t="inlineStr"/>
+      <c r="AA380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -37053,6 +39095,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z381" t="inlineStr"/>
+      <c r="AA381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -37113,7 +39157,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T382" t="inlineStr"/>
       <c r="V382" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37129,6 +39172,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z382" t="inlineStr"/>
+      <c r="AA382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -37189,7 +39234,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T383" t="inlineStr"/>
       <c r="V383" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37205,6 +39249,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z383" t="inlineStr"/>
+      <c r="AA383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -37285,6 +39331,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z384" t="inlineStr"/>
+      <c r="AA384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -37365,6 +39413,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z385" t="inlineStr"/>
+      <c r="AA385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -37425,7 +39475,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T386" t="inlineStr"/>
       <c r="V386" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37441,6 +39490,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z386" t="inlineStr"/>
+      <c r="AA386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -37521,6 +39572,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z387" t="inlineStr"/>
+      <c r="AA387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -37586,7 +39639,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T388" t="inlineStr"/>
       <c r="V388" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37602,6 +39654,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z388" t="inlineStr"/>
+      <c r="AA388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -37662,7 +39716,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T389" t="inlineStr"/>
       <c r="V389" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37678,6 +39731,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z389" t="inlineStr"/>
+      <c r="AA389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -37738,7 +39793,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T390" t="inlineStr"/>
       <c r="V390" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37754,6 +39808,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z390" t="inlineStr"/>
+      <c r="AA390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -37834,6 +39890,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z391" t="inlineStr"/>
+      <c r="AA391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -37894,7 +39952,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T392" t="inlineStr"/>
       <c r="V392" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -37910,6 +39967,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z392" t="inlineStr"/>
+      <c r="AA392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -37990,6 +40049,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z393" t="inlineStr"/>
+      <c r="AA393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -38050,7 +40111,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T394" t="inlineStr"/>
       <c r="V394" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38066,6 +40126,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z394" t="inlineStr"/>
+      <c r="AA394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -38126,7 +40188,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T395" t="inlineStr"/>
       <c r="V395" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38142,6 +40203,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z395" t="inlineStr"/>
+      <c r="AA395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -38222,6 +40285,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z396" t="inlineStr"/>
+      <c r="AA396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -38302,6 +40367,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z397" t="inlineStr"/>
+      <c r="AA397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -38387,6 +40454,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z398" t="inlineStr"/>
+      <c r="AA398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -38472,6 +40541,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z399" t="inlineStr"/>
+      <c r="AA399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -38532,7 +40603,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T400" t="inlineStr"/>
       <c r="V400" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38548,6 +40618,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z400" t="inlineStr"/>
+      <c r="AA400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -38628,6 +40700,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z401" t="inlineStr"/>
+      <c r="AA401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -38688,7 +40762,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T402" t="inlineStr"/>
       <c r="V402" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38704,6 +40777,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z402" t="inlineStr"/>
+      <c r="AA402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -38764,7 +40839,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T403" t="inlineStr"/>
       <c r="V403" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38780,6 +40854,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z403" t="inlineStr"/>
+      <c r="AA403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -38845,7 +40921,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T404" t="inlineStr"/>
       <c r="V404" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -38861,6 +40936,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z404" t="inlineStr"/>
+      <c r="AA404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -38946,6 +41023,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z405" t="inlineStr"/>
+      <c r="AA405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -39026,6 +41105,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z406" t="inlineStr"/>
+      <c r="AA406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -39106,6 +41187,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z407" t="inlineStr"/>
+      <c r="AA407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -39166,7 +41249,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T408" t="inlineStr"/>
       <c r="V408" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39182,6 +41264,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z408" t="inlineStr"/>
+      <c r="AA408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -39242,7 +41326,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T409" t="inlineStr"/>
       <c r="V409" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39258,6 +41341,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z409" t="inlineStr"/>
+      <c r="AA409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -39338,6 +41423,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z410" t="inlineStr"/>
+      <c r="AA410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -39398,7 +41485,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T411" t="inlineStr"/>
       <c r="V411" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39414,6 +41500,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z411" t="inlineStr"/>
+      <c r="AA411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -39494,6 +41582,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z412" t="inlineStr"/>
+      <c r="AA412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -39574,6 +41664,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z413" t="inlineStr"/>
+      <c r="AA413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -39659,6 +41751,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z414" t="inlineStr"/>
+      <c r="AA414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -39719,7 +41813,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T415" t="inlineStr"/>
       <c r="V415" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39735,6 +41828,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z415" t="inlineStr"/>
+      <c r="AA415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -39815,6 +41910,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z416" t="inlineStr"/>
+      <c r="AA416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -39875,7 +41972,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T417" t="inlineStr"/>
       <c r="V417" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39891,6 +41987,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z417" t="inlineStr"/>
+      <c r="AA417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -39951,7 +42049,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T418" t="inlineStr"/>
       <c r="V418" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -39967,6 +42064,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z418" t="inlineStr"/>
+      <c r="AA418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -40027,7 +42126,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T419" t="inlineStr"/>
       <c r="V419" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40043,6 +42141,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z419" t="inlineStr"/>
+      <c r="AA419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -40103,7 +42203,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T420" t="inlineStr"/>
       <c r="V420" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40119,6 +42218,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z420" t="inlineStr"/>
+      <c r="AA420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -40199,6 +42300,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z421" t="inlineStr"/>
+      <c r="AA421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -40264,7 +42367,6 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="T422" t="inlineStr"/>
       <c r="V422" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40280,6 +42382,8 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
+      <c r="Z422" t="inlineStr"/>
+      <c r="AA422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -40365,6 +42469,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z423" t="inlineStr"/>
+      <c r="AA423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -40450,6 +42556,8 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
+      <c r="Z424" t="inlineStr"/>
+      <c r="AA424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -40530,6 +42638,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z425" t="inlineStr"/>
+      <c r="AA425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -40595,7 +42705,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T426" t="inlineStr"/>
       <c r="V426" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40611,6 +42720,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z426" t="inlineStr"/>
+      <c r="AA426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -40691,6 +42802,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z427" t="inlineStr"/>
+      <c r="AA427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -40776,6 +42889,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z428" t="inlineStr"/>
+      <c r="AA428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -40841,7 +42956,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T429" t="inlineStr"/>
       <c r="V429" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -40857,6 +42971,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z429" t="inlineStr"/>
+      <c r="AA429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -40937,6 +43053,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z430" t="inlineStr"/>
+      <c r="AA430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -40997,7 +43115,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T431" t="inlineStr"/>
       <c r="V431" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41013,6 +43130,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z431" t="inlineStr"/>
+      <c r="AA431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -41098,6 +43217,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z432" t="inlineStr"/>
+      <c r="AA432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -41158,7 +43279,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T433" t="inlineStr"/>
       <c r="V433" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41174,6 +43294,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z433" t="inlineStr"/>
+      <c r="AA433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -41254,6 +43376,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z434" t="inlineStr"/>
+      <c r="AA434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -41314,7 +43438,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T435" t="inlineStr"/>
       <c r="V435" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41330,6 +43453,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z435" t="inlineStr"/>
+      <c r="AA435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -41415,6 +43540,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z436" t="inlineStr"/>
+      <c r="AA436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -41480,7 +43607,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T437" t="inlineStr"/>
       <c r="V437" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41496,6 +43622,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z437" t="inlineStr"/>
+      <c r="AA437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -41576,6 +43704,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z438" t="inlineStr"/>
+      <c r="AA438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -41636,7 +43766,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T439" t="inlineStr"/>
       <c r="V439" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41652,6 +43781,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z439" t="inlineStr"/>
+      <c r="AA439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -41732,6 +43863,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z440" t="inlineStr"/>
+      <c r="AA440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -41792,7 +43925,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T441" t="inlineStr"/>
       <c r="V441" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41808,6 +43940,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z441" t="inlineStr"/>
+      <c r="AA441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -41868,7 +44002,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T442" t="inlineStr"/>
       <c r="V442" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41884,6 +44017,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z442" t="inlineStr"/>
+      <c r="AA442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -41949,7 +44084,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T443" t="inlineStr"/>
       <c r="V443" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -41965,6 +44099,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z443" t="inlineStr"/>
+      <c r="AA443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -42045,6 +44181,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z444" t="inlineStr"/>
+      <c r="AA444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -42105,7 +44243,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T445" t="inlineStr"/>
       <c r="V445" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -42121,6 +44258,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z445" t="inlineStr"/>
+      <c r="AA445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -42206,6 +44345,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z446" t="inlineStr"/>
+      <c r="AA446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -42286,6 +44427,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z447" t="inlineStr"/>
+      <c r="AA447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -42371,6 +44514,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z448" t="inlineStr"/>
+      <c r="AA448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -42451,6 +44596,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z449" t="inlineStr"/>
+      <c r="AA449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -42531,6 +44678,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z450" t="inlineStr"/>
+      <c r="AA450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -42616,6 +44765,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z451" t="inlineStr"/>
+      <c r="AA451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -42696,6 +44847,16 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z452" t="inlineStr">
+        <is>
+          <t>T-16</t>
+        </is>
+      </c>
+      <c r="AA452" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -42781,6 +44942,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z453" t="inlineStr"/>
+      <c r="AA453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -42866,6 +45029,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z454" t="inlineStr"/>
+      <c r="AA454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -42951,6 +45116,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z455" t="inlineStr"/>
+      <c r="AA455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -43031,6 +45198,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z456" t="inlineStr"/>
+      <c r="AA456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -43111,6 +45280,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z457" t="inlineStr"/>
+      <c r="AA457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -43191,6 +45362,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z458" t="inlineStr"/>
+      <c r="AA458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -43271,6 +45444,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z459" t="inlineStr"/>
+      <c r="AA459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -43351,6 +45526,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z460" t="inlineStr"/>
+      <c r="AA460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -43411,7 +45588,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T461" t="inlineStr"/>
       <c r="V461" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -43427,6 +45603,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z461" t="inlineStr"/>
+      <c r="AA461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -43512,6 +45690,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z462" t="inlineStr"/>
+      <c r="AA462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -43592,6 +45772,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z463" t="inlineStr"/>
+      <c r="AA463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -43677,6 +45859,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z464" t="inlineStr"/>
+      <c r="AA464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -43737,7 +45921,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T465" t="inlineStr"/>
       <c r="V465" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -43753,6 +45936,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z465" t="inlineStr"/>
+      <c r="AA465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -43813,7 +45998,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T466" t="inlineStr"/>
       <c r="V466" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -43829,6 +46013,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z466" t="inlineStr"/>
+      <c r="AA466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -43909,6 +46095,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z467" t="inlineStr"/>
+      <c r="AA467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -43989,6 +46177,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z468" t="inlineStr"/>
+      <c r="AA468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -44069,6 +46259,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z469" t="inlineStr"/>
+      <c r="AA469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -44129,7 +46321,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T470" t="inlineStr"/>
       <c r="V470" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44145,6 +46336,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z470" t="inlineStr"/>
+      <c r="AA470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -44230,6 +46423,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z471" t="inlineStr"/>
+      <c r="AA471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -44315,6 +46510,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z472" t="inlineStr"/>
+      <c r="AA472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -44400,6 +46597,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z473" t="inlineStr"/>
+      <c r="AA473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -44460,7 +46659,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T474" t="inlineStr"/>
       <c r="V474" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44476,6 +46674,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z474" t="inlineStr"/>
+      <c r="AA474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -44561,6 +46761,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z475" t="inlineStr"/>
+      <c r="AA475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -44646,6 +46848,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z476" t="inlineStr"/>
+      <c r="AA476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -44726,6 +46930,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z477" t="inlineStr"/>
+      <c r="AA477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -44811,6 +47017,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z478" t="inlineStr"/>
+      <c r="AA478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -44871,7 +47079,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T479" t="inlineStr"/>
       <c r="V479" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44887,6 +47094,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z479" t="inlineStr"/>
+      <c r="AA479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -44947,7 +47156,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T480" t="inlineStr"/>
       <c r="V480" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -44963,6 +47171,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z480" t="inlineStr"/>
+      <c r="AA480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -45028,7 +47238,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T481" t="inlineStr"/>
       <c r="V481" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45044,6 +47253,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z481" t="inlineStr"/>
+      <c r="AA481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -45104,7 +47315,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T482" t="inlineStr"/>
       <c r="V482" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45120,6 +47330,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z482" t="inlineStr"/>
+      <c r="AA482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -45180,7 +47392,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T483" t="inlineStr"/>
       <c r="V483" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45196,6 +47407,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z483" t="inlineStr"/>
+      <c r="AA483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -45281,6 +47494,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z484" t="inlineStr"/>
+      <c r="AA484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -45346,7 +47561,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T485" t="inlineStr"/>
       <c r="V485" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45362,6 +47576,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z485" t="inlineStr"/>
+      <c r="AA485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -45447,6 +47663,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z486" t="inlineStr"/>
+      <c r="AA486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -45537,6 +47755,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z487" t="inlineStr"/>
+      <c r="AA487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -45597,7 +47817,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T488" t="inlineStr"/>
       <c r="V488" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45613,6 +47832,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z488" t="inlineStr"/>
+      <c r="AA488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -45673,7 +47894,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T489" t="inlineStr"/>
       <c r="V489" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45689,6 +47909,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z489" t="inlineStr"/>
+      <c r="AA489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -45749,7 +47971,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T490" t="inlineStr"/>
       <c r="V490" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45765,6 +47986,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z490" t="inlineStr"/>
+      <c r="AA490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -45825,7 +48048,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T491" t="inlineStr"/>
       <c r="V491" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45841,6 +48063,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z491" t="inlineStr"/>
+      <c r="AA491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -45901,7 +48125,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T492" t="inlineStr"/>
       <c r="V492" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45917,6 +48140,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z492" t="inlineStr"/>
+      <c r="AA492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -45977,7 +48202,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T493" t="inlineStr"/>
       <c r="V493" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -45993,6 +48217,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z493" t="inlineStr"/>
+      <c r="AA493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -46083,6 +48309,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z494" t="inlineStr"/>
+      <c r="AA494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -46148,7 +48376,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T495" t="inlineStr"/>
       <c r="V495" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46164,6 +48391,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z495" t="inlineStr"/>
+      <c r="AA495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -46244,6 +48473,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z496" t="inlineStr"/>
+      <c r="AA496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -46304,7 +48535,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T497" t="inlineStr"/>
       <c r="V497" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46320,6 +48550,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z497" t="inlineStr"/>
+      <c r="AA497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -46405,6 +48637,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z498" t="inlineStr"/>
+      <c r="AA498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -46465,7 +48699,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T499" t="inlineStr"/>
       <c r="V499" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46481,6 +48714,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z499" t="inlineStr"/>
+      <c r="AA499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -46566,6 +48801,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z500" t="inlineStr"/>
+      <c r="AA500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -46626,7 +48863,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T501" t="inlineStr"/>
       <c r="V501" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46642,6 +48878,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z501" t="inlineStr"/>
+      <c r="AA501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -46707,7 +48945,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T502" t="inlineStr"/>
       <c r="V502" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -46723,6 +48960,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z502" t="inlineStr"/>
+      <c r="AA502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -46803,6 +49042,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z503" t="inlineStr"/>
+      <c r="AA503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -46883,6 +49124,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z504" t="inlineStr"/>
+      <c r="AA504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -46963,6 +49206,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z505" t="inlineStr"/>
+      <c r="AA505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -47023,7 +49268,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T506" t="inlineStr"/>
       <c r="V506" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47039,6 +49283,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z506" t="inlineStr"/>
+      <c r="AA506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -47099,7 +49345,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T507" t="inlineStr"/>
       <c r="V507" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47115,6 +49360,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z507" t="inlineStr"/>
+      <c r="AA507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -47180,7 +49427,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T508" t="inlineStr"/>
       <c r="V508" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47196,6 +49442,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z508" t="inlineStr"/>
+      <c r="AA508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -47256,7 +49504,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T509" t="inlineStr"/>
       <c r="V509" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47272,6 +49519,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z509" t="inlineStr"/>
+      <c r="AA509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -47352,6 +49601,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z510" t="inlineStr"/>
+      <c r="AA510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -47432,6 +49683,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z511" t="inlineStr"/>
+      <c r="AA511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -47517,6 +49770,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z512" t="inlineStr"/>
+      <c r="AA512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -47577,7 +49832,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T513" t="inlineStr"/>
       <c r="V513" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47593,6 +49847,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z513" t="inlineStr"/>
+      <c r="AA513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -47658,7 +49914,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T514" t="inlineStr"/>
       <c r="V514" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47674,6 +49929,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z514" t="inlineStr"/>
+      <c r="AA514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -47754,6 +50011,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z515" t="inlineStr"/>
+      <c r="AA515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -47814,7 +50073,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T516" t="inlineStr"/>
       <c r="V516" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47830,6 +50088,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z516" t="inlineStr"/>
+      <c r="AA516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -47910,6 +50170,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z517" t="inlineStr"/>
+      <c r="AA517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -47975,7 +50237,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T518" t="inlineStr"/>
       <c r="V518" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -47991,6 +50252,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z518" t="inlineStr"/>
+      <c r="AA518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -48071,6 +50334,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z519" t="inlineStr"/>
+      <c r="AA519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -48131,7 +50396,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T520" t="inlineStr"/>
       <c r="V520" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48147,6 +50411,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z520" t="inlineStr"/>
+      <c r="AA520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -48227,6 +50493,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z521" t="inlineStr"/>
+      <c r="AA521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -48287,7 +50555,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T522" t="inlineStr"/>
       <c r="V522" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48303,6 +50570,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z522" t="inlineStr"/>
+      <c r="AA522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -48383,6 +50652,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z523" t="inlineStr"/>
+      <c r="AA523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -48443,7 +50714,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T524" t="inlineStr"/>
       <c r="V524" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48459,6 +50729,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z524" t="inlineStr"/>
+      <c r="AA524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -48544,6 +50816,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z525" t="inlineStr"/>
+      <c r="AA525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -48624,6 +50898,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z526" t="inlineStr"/>
+      <c r="AA526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -48689,7 +50965,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T527" t="inlineStr"/>
       <c r="V527" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48705,6 +50980,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z527" t="inlineStr"/>
+      <c r="AA527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -48760,7 +51037,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T528" t="inlineStr"/>
       <c r="V528" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48776,6 +51052,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z528" t="inlineStr"/>
+      <c r="AA528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -48836,7 +51114,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T529" t="inlineStr"/>
       <c r="V529" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48852,6 +51129,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z529" t="inlineStr"/>
+      <c r="AA529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -48912,7 +51191,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T530" t="inlineStr"/>
       <c r="V530" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -48928,6 +51206,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z530" t="inlineStr"/>
+      <c r="AA530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -49013,6 +51293,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z531" t="inlineStr"/>
+      <c r="AA531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -49103,6 +51385,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z532" t="inlineStr"/>
+      <c r="AA532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -49193,6 +51477,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z533" t="inlineStr"/>
+      <c r="AA533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -49278,6 +51564,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z534" t="inlineStr"/>
+      <c r="AA534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -49338,7 +51626,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T535" t="inlineStr"/>
       <c r="V535" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49354,6 +51641,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z535" t="inlineStr"/>
+      <c r="AA535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -49439,6 +51728,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z536" t="inlineStr"/>
+      <c r="AA536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -49499,7 +51790,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T537" t="inlineStr"/>
       <c r="V537" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49515,6 +51805,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z537" t="inlineStr"/>
+      <c r="AA537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -49580,7 +51872,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T538" t="inlineStr"/>
       <c r="V538" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49596,6 +51887,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z538" t="inlineStr"/>
+      <c r="AA538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -49661,7 +51954,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T539" t="inlineStr"/>
       <c r="V539" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49677,6 +51969,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z539" t="inlineStr"/>
+      <c r="AA539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -49737,7 +52031,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T540" t="inlineStr"/>
       <c r="V540" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49753,6 +52046,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z540" t="inlineStr"/>
+      <c r="AA540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -49838,6 +52133,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z541" t="inlineStr"/>
+      <c r="AA541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -49898,7 +52195,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T542" t="inlineStr"/>
       <c r="V542" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -49912,6 +52208,16 @@
       <c r="Y542" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z542" t="inlineStr">
+        <is>
+          <t>T-17</t>
+        </is>
+      </c>
+      <c r="AA542" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
         </is>
       </c>
     </row>
@@ -49999,6 +52305,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z543" t="inlineStr"/>
+      <c r="AA543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -50089,6 +52397,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z544" t="inlineStr"/>
+      <c r="AA544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -50174,6 +52484,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z545" t="inlineStr"/>
+      <c r="AA545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -50234,7 +52546,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T546" t="inlineStr"/>
       <c r="V546" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -50250,6 +52561,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z546" t="inlineStr"/>
+      <c r="AA546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -50310,7 +52623,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T547" t="inlineStr"/>
       <c r="V547" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -50326,6 +52638,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z547" t="inlineStr"/>
+      <c r="AA547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -50416,6 +52730,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z548" t="inlineStr"/>
+      <c r="AA548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -50476,7 +52792,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T549" t="inlineStr"/>
       <c r="V549" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -50492,6 +52807,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z549" t="inlineStr"/>
+      <c r="AA549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -50567,6 +52884,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z550" t="inlineStr"/>
+      <c r="AA550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -50632,7 +52951,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T551" t="inlineStr"/>
       <c r="V551" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -50648,6 +52966,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z551" t="inlineStr"/>
+      <c r="AA551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -50738,6 +53058,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z552" t="inlineStr"/>
+      <c r="AA552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -50823,6 +53145,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z553" t="inlineStr"/>
+      <c r="AA553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -50903,6 +53227,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z554" t="inlineStr"/>
+      <c r="AA554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -50983,6 +53309,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z555" t="inlineStr"/>
+      <c r="AA555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -51073,6 +53401,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z556" t="inlineStr"/>
+      <c r="AA556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -51133,7 +53463,6 @@
           <t>Kollej</t>
         </is>
       </c>
-      <c r="T557" t="inlineStr"/>
       <c r="V557" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
@@ -51147,6 +53476,16 @@
       <c r="Y557" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z557" t="inlineStr">
+        <is>
+          <t>T-28</t>
+        </is>
+      </c>
+      <c r="AA557" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
         </is>
       </c>
     </row>
@@ -51209,7 +53548,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T558" t="inlineStr"/>
       <c r="U558" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -51235,6 +53573,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z558" t="inlineStr"/>
+      <c r="AA558" t="inlineStr"/>
       <c r="AB558" t="inlineStr">
         <is>
           <t>KIRITILDI</t>
@@ -51300,7 +53640,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T559" t="inlineStr"/>
       <c r="U559" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -51326,6 +53665,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z559" t="inlineStr"/>
+      <c r="AA559" t="inlineStr"/>
       <c r="AB559" t="inlineStr">
         <is>
           <t>KIRITILDI</t>
@@ -51391,7 +53732,6 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T560" t="inlineStr"/>
       <c r="U560" t="inlineStr">
         <is>
           <t>TOPILDI</t>
@@ -51417,6 +53757,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z560" t="inlineStr"/>
+      <c r="AA560" t="inlineStr"/>
       <c r="AB560" t="inlineStr">
         <is>
           <t>KIRITILDI</t>
@@ -51522,6 +53864,16 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
+      <c r="Z561" t="inlineStr">
+        <is>
+          <t>T-40/2</t>
+        </is>
+      </c>
+      <c r="AA561" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
       <c r="AB561" t="inlineStr">
         <is>
           <t>KIRITILDI</t>
@@ -51632,6 +53984,8 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
+      <c r="Z562" t="inlineStr"/>
+      <c r="AA562" t="inlineStr"/>
       <c r="AB562" t="inlineStr">
         <is>
           <t>KIRITILDI</t>
@@ -51735,6 +54089,16 @@
       <c r="Y563" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z563" t="inlineStr">
+        <is>
+          <t>T-41</t>
+        </is>
+      </c>
+      <c r="AA563" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="AB563" t="inlineStr">

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -2321,8 +2321,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4663,8 +4661,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -9608,8 +9604,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -22391,7 +22385,7 @@
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
@@ -22401,12 +22395,12 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>T-40/2</t>
+          <t>---</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>06.10.2026</t>
         </is>
       </c>
     </row>
@@ -24479,8 +24473,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z201" t="inlineStr"/>
-      <c r="AA201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -24621,8 +24613,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z203" t="inlineStr"/>
-      <c r="AA203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -24753,8 +24743,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z205" t="inlineStr"/>
-      <c r="AA205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -24835,8 +24823,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z206" t="inlineStr"/>
-      <c r="AA206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -25552,8 +25538,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z215" t="inlineStr"/>
-      <c r="AA215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -26099,8 +26083,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z222" t="inlineStr"/>
-      <c r="AA222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -26236,8 +26218,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr"/>
-      <c r="AA224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -26348,8 +26328,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z226" t="inlineStr"/>
-      <c r="AA226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -26635,8 +26613,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z230" t="inlineStr"/>
-      <c r="AA230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -27227,8 +27203,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z237" t="inlineStr"/>
-      <c r="AA237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -27314,8 +27288,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z238" t="inlineStr"/>
-      <c r="AA238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -27401,8 +27373,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z239" t="inlineStr"/>
-      <c r="AA239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -27488,8 +27458,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z240" t="inlineStr"/>
-      <c r="AA240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27570,8 +27538,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z241" t="inlineStr"/>
-      <c r="AA241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27652,8 +27618,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z242" t="inlineStr"/>
-      <c r="AA242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27734,8 +27698,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z243" t="inlineStr"/>
-      <c r="AA243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27816,8 +27778,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z244" t="inlineStr"/>
-      <c r="AA244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27903,8 +27863,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z245" t="inlineStr"/>
-      <c r="AA245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27985,8 +27943,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z246" t="inlineStr"/>
-      <c r="AA246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28067,8 +28023,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z247" t="inlineStr"/>
-      <c r="AA247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28149,8 +28103,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z248" t="inlineStr"/>
-      <c r="AA248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28231,8 +28183,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z249" t="inlineStr"/>
-      <c r="AA249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28313,8 +28263,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z250" t="inlineStr"/>
-      <c r="AA250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28395,8 +28343,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z251" t="inlineStr"/>
-      <c r="AA251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28482,8 +28428,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z252" t="inlineStr"/>
-      <c r="AA252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28569,8 +28513,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z253" t="inlineStr"/>
-      <c r="AA253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28656,8 +28598,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z254" t="inlineStr"/>
-      <c r="AA254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28738,8 +28678,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z255" t="inlineStr"/>
-      <c r="AA255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -28825,8 +28763,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z256" t="inlineStr"/>
-      <c r="AA256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28907,8 +28843,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z257" t="inlineStr"/>
-      <c r="AA257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28989,8 +28923,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z258" t="inlineStr"/>
-      <c r="AA258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -29071,8 +29003,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z259" t="inlineStr"/>
-      <c r="AA259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29153,8 +29083,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z260" t="inlineStr"/>
-      <c r="AA260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29235,8 +29163,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z261" t="inlineStr"/>
-      <c r="AA261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29317,8 +29243,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z262" t="inlineStr"/>
-      <c r="AA262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29399,8 +29323,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z263" t="inlineStr"/>
-      <c r="AA263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -29481,8 +29403,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z264" t="inlineStr"/>
-      <c r="AA264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -29563,8 +29483,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z265" t="inlineStr"/>
-      <c r="AA265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -29645,8 +29563,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z266" t="inlineStr"/>
-      <c r="AA266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -29727,8 +29643,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z267" t="inlineStr"/>
-      <c r="AA267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -29809,8 +29723,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z268" t="inlineStr"/>
-      <c r="AA268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -29891,8 +29803,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z269" t="inlineStr"/>
-      <c r="AA269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -29973,8 +29883,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z270" t="inlineStr"/>
-      <c r="AA270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -30060,8 +29968,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z271" t="inlineStr"/>
-      <c r="AA271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -30142,8 +30048,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z272" t="inlineStr"/>
-      <c r="AA272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -30229,8 +30133,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z273" t="inlineStr"/>
-      <c r="AA273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -30316,8 +30218,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z274" t="inlineStr"/>
-      <c r="AA274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30403,8 +30303,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z275" t="inlineStr"/>
-      <c r="AA275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30485,8 +30383,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z276" t="inlineStr"/>
-      <c r="AA276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30572,8 +30468,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z277" t="inlineStr"/>
-      <c r="AA277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -30654,8 +30548,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z278" t="inlineStr"/>
-      <c r="AA278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -30736,8 +30628,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z279" t="inlineStr"/>
-      <c r="AA279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -30818,8 +30708,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z280" t="inlineStr"/>
-      <c r="AA280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -30900,8 +30788,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z281" t="inlineStr"/>
-      <c r="AA281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -30982,8 +30868,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z282" t="inlineStr"/>
-      <c r="AA282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -31064,8 +30948,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z283" t="inlineStr"/>
-      <c r="AA283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -31146,8 +31028,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z284" t="inlineStr"/>
-      <c r="AA284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -31228,8 +31108,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z285" t="inlineStr"/>
-      <c r="AA285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -31310,8 +31188,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z286" t="inlineStr"/>
-      <c r="AA286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -31392,8 +31268,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z287" t="inlineStr"/>
-      <c r="AA287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -31474,8 +31348,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z288" t="inlineStr"/>
-      <c r="AA288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -31561,8 +31433,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z289" t="inlineStr"/>
-      <c r="AA289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -31643,8 +31513,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z290" t="inlineStr"/>
-      <c r="AA290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -31725,8 +31593,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z291" t="inlineStr"/>
-      <c r="AA291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -31807,8 +31673,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z292" t="inlineStr"/>
-      <c r="AA292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -31894,8 +31758,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z293" t="inlineStr"/>
-      <c r="AA293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -31981,8 +31843,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z294" t="inlineStr"/>
-      <c r="AA294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -32063,8 +31923,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z295" t="inlineStr"/>
-      <c r="AA295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -32145,8 +32003,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z296" t="inlineStr"/>
-      <c r="AA296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -32227,8 +32083,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z297" t="inlineStr"/>
-      <c r="AA297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -32309,8 +32163,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z298" t="inlineStr"/>
-      <c r="AA298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -32391,8 +32243,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z299" t="inlineStr"/>
-      <c r="AA299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -32473,8 +32323,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z300" t="inlineStr"/>
-      <c r="AA300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -32560,8 +32408,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z301" t="inlineStr"/>
-      <c r="AA301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -32647,8 +32493,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z302" t="inlineStr"/>
-      <c r="AA302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -32729,8 +32573,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z303" t="inlineStr"/>
-      <c r="AA303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -32811,8 +32653,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z304" t="inlineStr"/>
-      <c r="AA304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -32893,8 +32733,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z305" t="inlineStr"/>
-      <c r="AA305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -32980,8 +32818,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z306" t="inlineStr"/>
-      <c r="AA306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -33062,8 +32898,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z307" t="inlineStr"/>
-      <c r="AA307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -33144,8 +32978,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z308" t="inlineStr"/>
-      <c r="AA308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -33226,8 +33058,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z309" t="inlineStr"/>
-      <c r="AA309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -33308,8 +33138,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z310" t="inlineStr"/>
-      <c r="AA310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -33390,8 +33218,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z311" t="inlineStr"/>
-      <c r="AA311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -33477,8 +33303,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z312" t="inlineStr"/>
-      <c r="AA312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -33559,8 +33383,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z313" t="inlineStr"/>
-      <c r="AA313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -33641,8 +33463,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z314" t="inlineStr"/>
-      <c r="AA314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -33723,8 +33543,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z315" t="inlineStr"/>
-      <c r="AA315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -33810,8 +33628,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z316" t="inlineStr"/>
-      <c r="AA316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -33892,8 +33708,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z317" t="inlineStr"/>
-      <c r="AA317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -33974,8 +33788,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z318" t="inlineStr"/>
-      <c r="AA318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -34061,8 +33873,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z319" t="inlineStr"/>
-      <c r="AA319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -34143,8 +33953,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z320" t="inlineStr"/>
-      <c r="AA320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -34225,8 +34033,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z321" t="inlineStr"/>
-      <c r="AA321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -34307,8 +34113,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z322" t="inlineStr"/>
-      <c r="AA322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -34389,8 +34193,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z323" t="inlineStr"/>
-      <c r="AA323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -34471,8 +34273,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z324" t="inlineStr"/>
-      <c r="AA324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -34553,8 +34353,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z325" t="inlineStr"/>
-      <c r="AA325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -34635,8 +34433,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z326" t="inlineStr"/>
-      <c r="AA326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -34717,8 +34513,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z327" t="inlineStr"/>
-      <c r="AA327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -34799,8 +34593,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z328" t="inlineStr"/>
-      <c r="AA328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -34881,8 +34673,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z329" t="inlineStr"/>
-      <c r="AA329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -34968,8 +34758,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z330" t="inlineStr"/>
-      <c r="AA330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -35050,8 +34838,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z331" t="inlineStr"/>
-      <c r="AA331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -35132,8 +34918,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z332" t="inlineStr"/>
-      <c r="AA332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -35214,8 +34998,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z333" t="inlineStr"/>
-      <c r="AA333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -35291,8 +35073,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z334" t="inlineStr"/>
-      <c r="AA334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -35378,8 +35158,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z335" t="inlineStr"/>
-      <c r="AA335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -35460,8 +35238,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z336" t="inlineStr"/>
-      <c r="AA336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -35547,8 +35323,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z337" t="inlineStr"/>
-      <c r="AA337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -35629,8 +35403,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z338" t="inlineStr"/>
-      <c r="AA338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -35711,8 +35483,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z339" t="inlineStr"/>
-      <c r="AA339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -35793,8 +35563,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z340" t="inlineStr"/>
-      <c r="AA340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -35875,8 +35643,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z341" t="inlineStr"/>
-      <c r="AA341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -35957,8 +35723,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z342" t="inlineStr"/>
-      <c r="AA342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -36039,8 +35803,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z343" t="inlineStr"/>
-      <c r="AA343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -36116,8 +35878,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z344" t="inlineStr"/>
-      <c r="AA344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -36203,8 +35963,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z345" t="inlineStr"/>
-      <c r="AA345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -36280,8 +36038,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z346" t="inlineStr"/>
-      <c r="AA346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -36357,8 +36113,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z347" t="inlineStr"/>
-      <c r="AA347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -36439,8 +36193,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z348" t="inlineStr"/>
-      <c r="AA348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -36521,8 +36273,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z349" t="inlineStr"/>
-      <c r="AA349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -36598,8 +36348,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z350" t="inlineStr"/>
-      <c r="AA350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -36675,8 +36423,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z351" t="inlineStr"/>
-      <c r="AA351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -36752,8 +36498,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z352" t="inlineStr"/>
-      <c r="AA352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -36834,8 +36578,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z353" t="inlineStr"/>
-      <c r="AA353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -36911,8 +36653,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z354" t="inlineStr"/>
-      <c r="AA354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -36993,8 +36733,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z355" t="inlineStr"/>
-      <c r="AA355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -37070,8 +36808,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z356" t="inlineStr"/>
-      <c r="AA356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -37147,8 +36883,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z357" t="inlineStr"/>
-      <c r="AA357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -37229,8 +36963,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z358" t="inlineStr"/>
-      <c r="AA358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -37306,8 +37038,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z359" t="inlineStr"/>
-      <c r="AA359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -37383,8 +37113,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z360" t="inlineStr"/>
-      <c r="AA360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -37465,8 +37193,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z361" t="inlineStr"/>
-      <c r="AA361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -37547,8 +37273,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z362" t="inlineStr"/>
-      <c r="AA362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -37634,8 +37358,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z363" t="inlineStr"/>
-      <c r="AA363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -37711,8 +37433,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z364" t="inlineStr"/>
-      <c r="AA364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -37798,8 +37518,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z365" t="inlineStr"/>
-      <c r="AA365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -37875,8 +37593,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z366" t="inlineStr"/>
-      <c r="AA366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -37952,8 +37668,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z367" t="inlineStr"/>
-      <c r="AA367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -38034,8 +37748,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z368" t="inlineStr"/>
-      <c r="AA368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -38111,8 +37823,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z369" t="inlineStr"/>
-      <c r="AA369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -38193,8 +37903,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z370" t="inlineStr"/>
-      <c r="AA370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -38280,8 +37988,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z371" t="inlineStr"/>
-      <c r="AA371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -38357,8 +38063,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z372" t="inlineStr"/>
-      <c r="AA372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -38439,8 +38143,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z373" t="inlineStr"/>
-      <c r="AA373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -38521,8 +38223,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z374" t="inlineStr"/>
-      <c r="AA374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -38598,8 +38298,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z375" t="inlineStr"/>
-      <c r="AA375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -38685,8 +38383,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z376" t="inlineStr"/>
-      <c r="AA376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -38767,8 +38463,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z377" t="inlineStr"/>
-      <c r="AA377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -38849,8 +38543,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z378" t="inlineStr"/>
-      <c r="AA378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -38926,8 +38618,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z379" t="inlineStr"/>
-      <c r="AA379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -39013,8 +38703,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z380" t="inlineStr"/>
-      <c r="AA380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -39095,8 +38783,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z381" t="inlineStr"/>
-      <c r="AA381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -39172,8 +38858,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z382" t="inlineStr"/>
-      <c r="AA382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -39249,8 +38933,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z383" t="inlineStr"/>
-      <c r="AA383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -39331,8 +39013,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z384" t="inlineStr"/>
-      <c r="AA384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -39413,8 +39093,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z385" t="inlineStr"/>
-      <c r="AA385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -39490,8 +39168,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z386" t="inlineStr"/>
-      <c r="AA386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -39572,8 +39248,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z387" t="inlineStr"/>
-      <c r="AA387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -39654,8 +39328,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z388" t="inlineStr"/>
-      <c r="AA388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -39731,8 +39403,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z389" t="inlineStr"/>
-      <c r="AA389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -39808,8 +39478,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z390" t="inlineStr"/>
-      <c r="AA390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -39890,8 +39558,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z391" t="inlineStr"/>
-      <c r="AA391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -39967,8 +39633,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z392" t="inlineStr"/>
-      <c r="AA392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -40049,8 +39713,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z393" t="inlineStr"/>
-      <c r="AA393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -40126,8 +39788,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z394" t="inlineStr"/>
-      <c r="AA394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -40203,8 +39863,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z395" t="inlineStr"/>
-      <c r="AA395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -40285,8 +39943,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z396" t="inlineStr"/>
-      <c r="AA396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -40367,8 +40023,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z397" t="inlineStr"/>
-      <c r="AA397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -40454,8 +40108,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z398" t="inlineStr"/>
-      <c r="AA398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -40541,8 +40193,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z399" t="inlineStr"/>
-      <c r="AA399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -40618,8 +40268,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z400" t="inlineStr"/>
-      <c r="AA400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -40700,8 +40348,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z401" t="inlineStr"/>
-      <c r="AA401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -40777,8 +40423,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z402" t="inlineStr"/>
-      <c r="AA402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -40854,8 +40498,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z403" t="inlineStr"/>
-      <c r="AA403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -40936,8 +40578,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z404" t="inlineStr"/>
-      <c r="AA404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -41023,8 +40663,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z405" t="inlineStr"/>
-      <c r="AA405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -41105,8 +40743,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z406" t="inlineStr"/>
-      <c r="AA406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -41187,8 +40823,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z407" t="inlineStr"/>
-      <c r="AA407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -41264,8 +40898,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z408" t="inlineStr"/>
-      <c r="AA408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -41341,8 +40973,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z409" t="inlineStr"/>
-      <c r="AA409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -41423,8 +41053,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z410" t="inlineStr"/>
-      <c r="AA410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -41500,8 +41128,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z411" t="inlineStr"/>
-      <c r="AA411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -41582,8 +41208,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z412" t="inlineStr"/>
-      <c r="AA412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -41664,8 +41288,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z413" t="inlineStr"/>
-      <c r="AA413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -41751,8 +41373,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z414" t="inlineStr"/>
-      <c r="AA414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -41828,8 +41448,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z415" t="inlineStr"/>
-      <c r="AA415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -41910,8 +41528,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z416" t="inlineStr"/>
-      <c r="AA416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -41987,8 +41603,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z417" t="inlineStr"/>
-      <c r="AA417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -42064,8 +41678,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z418" t="inlineStr"/>
-      <c r="AA418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -42141,8 +41753,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z419" t="inlineStr"/>
-      <c r="AA419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -42218,8 +41828,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z420" t="inlineStr"/>
-      <c r="AA420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -42300,8 +41908,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z421" t="inlineStr"/>
-      <c r="AA421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -42382,8 +41988,6 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
-      <c r="Z422" t="inlineStr"/>
-      <c r="AA422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -42469,8 +42073,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z423" t="inlineStr"/>
-      <c r="AA423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -42556,8 +42158,6 @@
           <t>KUTILMOQDA</t>
         </is>
       </c>
-      <c r="Z424" t="inlineStr"/>
-      <c r="AA424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -42638,8 +42238,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z425" t="inlineStr"/>
-      <c r="AA425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -42720,8 +42318,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z426" t="inlineStr"/>
-      <c r="AA426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -42802,8 +42398,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z427" t="inlineStr"/>
-      <c r="AA427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -42889,8 +42483,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z428" t="inlineStr"/>
-      <c r="AA428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -42971,8 +42563,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z429" t="inlineStr"/>
-      <c r="AA429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -43053,8 +42643,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z430" t="inlineStr"/>
-      <c r="AA430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -43130,8 +42718,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z431" t="inlineStr"/>
-      <c r="AA431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -43217,8 +42803,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z432" t="inlineStr"/>
-      <c r="AA432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -43294,8 +42878,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z433" t="inlineStr"/>
-      <c r="AA433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -43376,8 +42958,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z434" t="inlineStr"/>
-      <c r="AA434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -43453,8 +43033,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z435" t="inlineStr"/>
-      <c r="AA435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -43540,8 +43118,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z436" t="inlineStr"/>
-      <c r="AA436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -43622,8 +43198,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z437" t="inlineStr"/>
-      <c r="AA437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -43704,8 +43278,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z438" t="inlineStr"/>
-      <c r="AA438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -43781,8 +43353,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z439" t="inlineStr"/>
-      <c r="AA439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -43863,8 +43433,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z440" t="inlineStr"/>
-      <c r="AA440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -43940,8 +43508,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z441" t="inlineStr"/>
-      <c r="AA441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -44017,8 +43583,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z442" t="inlineStr"/>
-      <c r="AA442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -44099,8 +43663,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z443" t="inlineStr"/>
-      <c r="AA443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -44181,8 +43743,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z444" t="inlineStr"/>
-      <c r="AA444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -44258,8 +43818,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z445" t="inlineStr"/>
-      <c r="AA445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -44345,8 +43903,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z446" t="inlineStr"/>
-      <c r="AA446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -44427,8 +43983,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z447" t="inlineStr"/>
-      <c r="AA447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -44514,8 +44068,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z448" t="inlineStr"/>
-      <c r="AA448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -44596,8 +44148,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z449" t="inlineStr"/>
-      <c r="AA449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -44678,8 +44228,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z450" t="inlineStr"/>
-      <c r="AA450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -44765,8 +44313,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z451" t="inlineStr"/>
-      <c r="AA451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -44942,8 +44488,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z453" t="inlineStr"/>
-      <c r="AA453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -45029,8 +44573,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z454" t="inlineStr"/>
-      <c r="AA454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -45116,8 +44658,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z455" t="inlineStr"/>
-      <c r="AA455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -45198,8 +44738,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z456" t="inlineStr"/>
-      <c r="AA456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -45280,8 +44818,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z457" t="inlineStr"/>
-      <c r="AA457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -45362,8 +44898,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z458" t="inlineStr"/>
-      <c r="AA458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -45444,8 +44978,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z459" t="inlineStr"/>
-      <c r="AA459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -45526,8 +45058,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z460" t="inlineStr"/>
-      <c r="AA460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -45603,8 +45133,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z461" t="inlineStr"/>
-      <c r="AA461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -45690,8 +45218,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z462" t="inlineStr"/>
-      <c r="AA462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -45772,8 +45298,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z463" t="inlineStr"/>
-      <c r="AA463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -45859,8 +45383,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z464" t="inlineStr"/>
-      <c r="AA464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -45936,8 +45458,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z465" t="inlineStr"/>
-      <c r="AA465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -46013,8 +45533,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z466" t="inlineStr"/>
-      <c r="AA466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -46095,8 +45613,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z467" t="inlineStr"/>
-      <c r="AA467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -46177,8 +45693,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z468" t="inlineStr"/>
-      <c r="AA468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -46259,8 +45773,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z469" t="inlineStr"/>
-      <c r="AA469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -46336,8 +45848,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z470" t="inlineStr"/>
-      <c r="AA470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -46423,8 +45933,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z471" t="inlineStr"/>
-      <c r="AA471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -46510,8 +46018,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z472" t="inlineStr"/>
-      <c r="AA472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -46597,8 +46103,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z473" t="inlineStr"/>
-      <c r="AA473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -46674,8 +46178,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z474" t="inlineStr"/>
-      <c r="AA474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -46761,8 +46263,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z475" t="inlineStr"/>
-      <c r="AA475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -46848,8 +46348,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z476" t="inlineStr"/>
-      <c r="AA476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -46930,8 +46428,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z477" t="inlineStr"/>
-      <c r="AA477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -47017,8 +46513,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z478" t="inlineStr"/>
-      <c r="AA478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -47094,8 +46588,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z479" t="inlineStr"/>
-      <c r="AA479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -47171,8 +46663,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z480" t="inlineStr"/>
-      <c r="AA480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -47253,8 +46743,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z481" t="inlineStr"/>
-      <c r="AA481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -47330,8 +46818,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z482" t="inlineStr"/>
-      <c r="AA482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -47407,8 +46893,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z483" t="inlineStr"/>
-      <c r="AA483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -47494,8 +46978,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z484" t="inlineStr"/>
-      <c r="AA484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -47576,8 +47058,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z485" t="inlineStr"/>
-      <c r="AA485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -47663,8 +47143,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z486" t="inlineStr"/>
-      <c r="AA486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -47755,8 +47233,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z487" t="inlineStr"/>
-      <c r="AA487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -47832,8 +47308,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z488" t="inlineStr"/>
-      <c r="AA488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -47909,8 +47383,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z489" t="inlineStr"/>
-      <c r="AA489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -47986,8 +47458,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z490" t="inlineStr"/>
-      <c r="AA490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -48063,8 +47533,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z491" t="inlineStr"/>
-      <c r="AA491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -48140,8 +47608,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z492" t="inlineStr"/>
-      <c r="AA492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -48217,8 +47683,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z493" t="inlineStr"/>
-      <c r="AA493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -48309,8 +47773,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z494" t="inlineStr"/>
-      <c r="AA494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -48391,8 +47853,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z495" t="inlineStr"/>
-      <c r="AA495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -48473,8 +47933,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z496" t="inlineStr"/>
-      <c r="AA496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -48550,8 +48008,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z497" t="inlineStr"/>
-      <c r="AA497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -48637,8 +48093,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z498" t="inlineStr"/>
-      <c r="AA498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -48714,8 +48168,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z499" t="inlineStr"/>
-      <c r="AA499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -48801,8 +48253,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z500" t="inlineStr"/>
-      <c r="AA500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -48878,8 +48328,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z501" t="inlineStr"/>
-      <c r="AA501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -48960,8 +48408,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z502" t="inlineStr"/>
-      <c r="AA502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -49042,8 +48488,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z503" t="inlineStr"/>
-      <c r="AA503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -49124,8 +48568,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z504" t="inlineStr"/>
-      <c r="AA504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -49206,8 +48648,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z505" t="inlineStr"/>
-      <c r="AA505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -49283,8 +48723,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z506" t="inlineStr"/>
-      <c r="AA506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -49360,8 +48798,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z507" t="inlineStr"/>
-      <c r="AA507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -49442,8 +48878,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z508" t="inlineStr"/>
-      <c r="AA508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -49519,8 +48953,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z509" t="inlineStr"/>
-      <c r="AA509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -49601,8 +49033,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z510" t="inlineStr"/>
-      <c r="AA510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -49683,8 +49113,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z511" t="inlineStr"/>
-      <c r="AA511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -49770,8 +49198,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z512" t="inlineStr"/>
-      <c r="AA512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -49847,8 +49273,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z513" t="inlineStr"/>
-      <c r="AA513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -49929,8 +49353,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z514" t="inlineStr"/>
-      <c r="AA514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -50011,8 +49433,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z515" t="inlineStr"/>
-      <c r="AA515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -50088,8 +49508,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z516" t="inlineStr"/>
-      <c r="AA516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -50170,8 +49588,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z517" t="inlineStr"/>
-      <c r="AA517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -50252,8 +49668,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z518" t="inlineStr"/>
-      <c r="AA518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -50334,8 +49748,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z519" t="inlineStr"/>
-      <c r="AA519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -50411,8 +49823,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z520" t="inlineStr"/>
-      <c r="AA520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -50493,8 +49903,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z521" t="inlineStr"/>
-      <c r="AA521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -50570,8 +49978,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z522" t="inlineStr"/>
-      <c r="AA522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -50652,8 +50058,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z523" t="inlineStr"/>
-      <c r="AA523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -50729,8 +50133,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z524" t="inlineStr"/>
-      <c r="AA524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -50816,8 +50218,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z525" t="inlineStr"/>
-      <c r="AA525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -50898,8 +50298,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z526" t="inlineStr"/>
-      <c r="AA526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -50980,8 +50378,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z527" t="inlineStr"/>
-      <c r="AA527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -51052,8 +50448,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z528" t="inlineStr"/>
-      <c r="AA528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -51129,8 +50523,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z529" t="inlineStr"/>
-      <c r="AA529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -51206,8 +50598,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z530" t="inlineStr"/>
-      <c r="AA530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -51293,8 +50683,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z531" t="inlineStr"/>
-      <c r="AA531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -51385,8 +50773,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z532" t="inlineStr"/>
-      <c r="AA532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -51477,8 +50863,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z533" t="inlineStr"/>
-      <c r="AA533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -51564,8 +50948,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z534" t="inlineStr"/>
-      <c r="AA534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -51641,8 +51023,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z535" t="inlineStr"/>
-      <c r="AA535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -51728,8 +51108,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z536" t="inlineStr"/>
-      <c r="AA536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -51805,8 +51183,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z537" t="inlineStr"/>
-      <c r="AA537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -51887,8 +51263,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z538" t="inlineStr"/>
-      <c r="AA538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -51969,8 +51343,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z539" t="inlineStr"/>
-      <c r="AA539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -52046,8 +51418,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z540" t="inlineStr"/>
-      <c r="AA540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -52133,8 +51503,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z541" t="inlineStr"/>
-      <c r="AA541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -52305,8 +51673,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z543" t="inlineStr"/>
-      <c r="AA543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -52397,8 +51763,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z544" t="inlineStr"/>
-      <c r="AA544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -52484,8 +51848,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z545" t="inlineStr"/>
-      <c r="AA545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -52561,8 +51923,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z546" t="inlineStr"/>
-      <c r="AA546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -52638,8 +51998,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z547" t="inlineStr"/>
-      <c r="AA547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -52730,8 +52088,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z548" t="inlineStr"/>
-      <c r="AA548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -52807,8 +52163,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z549" t="inlineStr"/>
-      <c r="AA549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -52884,8 +52238,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z550" t="inlineStr"/>
-      <c r="AA550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -52966,8 +52318,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z551" t="inlineStr"/>
-      <c r="AA551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -53058,8 +52408,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z552" t="inlineStr"/>
-      <c r="AA552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -53145,8 +52493,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z553" t="inlineStr"/>
-      <c r="AA553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -53227,8 +52573,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z554" t="inlineStr"/>
-      <c r="AA554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -53309,8 +52653,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z555" t="inlineStr"/>
-      <c r="AA555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -53401,8 +52743,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z556" t="inlineStr"/>
-      <c r="AA556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -53573,8 +52913,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z558" t="inlineStr"/>
-      <c r="AA558" t="inlineStr"/>
       <c r="AB558" t="inlineStr">
         <is>
           <t>KIRITILDI</t>
@@ -53665,8 +53003,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z559" t="inlineStr"/>
-      <c r="AA559" t="inlineStr"/>
       <c r="AB559" t="inlineStr">
         <is>
           <t>KIRITILDI</t>
@@ -53757,8 +53093,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z560" t="inlineStr"/>
-      <c r="AA560" t="inlineStr"/>
       <c r="AB560" t="inlineStr">
         <is>
           <t>KIRITILDI</t>
@@ -53984,8 +53318,6 @@
           <t>TASDIQLANDI</t>
         </is>
       </c>
-      <c r="Z562" t="inlineStr"/>
-      <c r="AA562" t="inlineStr"/>
       <c r="AB562" t="inlineStr">
         <is>
           <t>KIRITILDI</t>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -39395,12 +39395,22 @@
       </c>
       <c r="W389" t="inlineStr">
         <is>
-          <t>25-17</t>
+          <t>Akademik ta'til olganlar</t>
         </is>
       </c>
       <c r="Y389" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t>T-52</t>
+        </is>
+      </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>05.10.2026</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -23005,17 +23005,17 @@
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>T-40/2</t>
+          <t>---</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>09.10.2026</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -22705,7 +22705,7 @@
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="Y180" t="inlineStr">
@@ -22715,12 +22715,12 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>T-40/2</t>
+          <t>---</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>09.10.2026</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -37105,12 +37105,22 @@
       </c>
       <c r="W360" t="inlineStr">
         <is>
-          <t>25-16</t>
+          <t>Akademik ta'til olganlar</t>
         </is>
       </c>
       <c r="Y360" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>T-50</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>02.10.2026</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -52830,7 +52830,7 @@
       </c>
       <c r="W557" t="inlineStr">
         <is>
-          <t>25-19</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="Y557" t="inlineStr">
@@ -52840,12 +52840,12 @@
       </c>
       <c r="Z557" t="inlineStr">
         <is>
-          <t>T-28</t>
+          <t>T-53</t>
         </is>
       </c>
       <c r="AA557" t="inlineStr">
         <is>
-          <t>20.03.2026</t>
+          <t>09.10.2026</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB563"/>
+  <dimension ref="A1:AB564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10219,7 +10219,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-07</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -22595,7 +22595,7 @@
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-07</t>
         </is>
       </c>
       <c r="Y179" t="inlineStr">
@@ -23105,17 +23105,17 @@
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>T-40/2</t>
+          <t>---</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>10.10.2026</t>
         </is>
       </c>
     </row>
@@ -37750,12 +37750,22 @@
       </c>
       <c r="W368" t="inlineStr">
         <is>
-          <t>25-16</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="Y368" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>T-54</t>
+        </is>
+      </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
         </is>
       </c>
     </row>
@@ -40835,12 +40845,22 @@
       </c>
       <c r="W407" t="inlineStr">
         <is>
-          <t>25-18</t>
+          <t>Akademik ta'til olganlar</t>
         </is>
       </c>
       <c r="Y407" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z407" t="inlineStr">
+        <is>
+          <t>T-55</t>
+        </is>
+      </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
@@ -41690,12 +41710,22 @@
       </c>
       <c r="W418" t="inlineStr">
         <is>
-          <t>25-18</t>
+          <t>Akademik ta'til olganlar</t>
         </is>
       </c>
       <c r="Y418" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="Z418" t="inlineStr">
+        <is>
+          <t>T-56</t>
+        </is>
+      </c>
+      <c r="AA418" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
@@ -53456,6 +53486,113 @@
       <c r="AB563" t="inlineStr">
         <is>
           <t>KIRITILMAGAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>563</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Jumayeva Sabina</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Hamshiralik ishi - 3 yillik</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>Sobir qizi</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Jumayeva Sabina Sobir qizi</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>AD9154749</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>62411085590063</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>26.10.2024</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>24.11.2008</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>Mavjud</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>UM 03752398</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr"/>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>13-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="T564" t="inlineStr"/>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="W564" t="inlineStr">
+        <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="Y564" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+      <c r="AB564" t="inlineStr">
+        <is>
+          <t>KIRITILDI</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Toliq_Royxati.xlsx
+++ b/data/Talabalar_Toliq_Royxati.xlsx
@@ -27135,7 +27135,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>26/27 Sh/A 268</t>
+          <t>268</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -27220,7 +27220,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>26/27 SH/A 216</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>26/27 SH/A 33</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -27390,7 +27390,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>26/27 SH/A269</t>
+          <t>269</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -27795,7 +27795,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>25/26 sh/a 6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -28360,7 +28360,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>25/26 SH/A 33</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>26/27 Sh/A 220</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>26/27 sh/a 277</t>
+          <t>277</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -28695,7 +28695,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>25/26 SH/A57</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -29900,7 +29900,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>26/27 SH/A 226</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -30065,7 +30065,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>26/27 SH/A252</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -30150,7 +30150,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>26/27 SH/A 285</t>
+          <t>285</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -30235,7 +30235,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>26/27 SH/A 285</t>
+          <t>285</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -30400,7 +30400,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>26/27 SH/A 286</t>
+          <t>286</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -31365,7 +31365,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>26/27 SH/A 288</t>
+          <t>288</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -31690,7 +31690,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>26/27 SH/A 259</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -31775,7 +31775,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>26/27 sh/a 235</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -32340,7 +32340,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>26/27 Sh/A 239</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -32425,7 +32425,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>24/25 SH/A 41</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -32750,7 +32750,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>26/27 SH/A 241</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -33235,7 +33235,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>25/26 SH/A 286</t>
+          <t>286</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -33560,7 +33560,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>25/26 SH/A 506</t>
+          <t>506</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -33805,7 +33805,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>25/26 Sh/A509</t>
+          <t>509</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -34690,7 +34690,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>25/26 SH/A 520</t>
+          <t>520</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -35090,7 +35090,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>25/26 sh/a 186</t>
+          <t>186</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -35255,7 +35255,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 116</t>
+          <t>116</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -36130,7 +36130,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>26/27 Sh/A 327</t>
+          <t>327</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -37300,7 +37300,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>26/27 SH/A 15</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -37460,7 +37460,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>26/27 SH/A 10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -37940,7 +37940,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>25/26 SH/A84</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -38335,7 +38335,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>26/27 SH/A 26</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -38500,7 +38500,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>26/27 SH/A 28</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -38655,7 +38655,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 107</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -39285,7 +39285,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>26/27 SH/A40</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
@@ -40070,7 +40070,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 140</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -40155,7 +40155,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>25/26 SH/A149</t>
+          <t>149</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -40545,7 +40545,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 142</t>
+          <t>142</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -40625,7 +40625,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>25/26 SH/A150</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -41345,7 +41345,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>26/27 SH/A66</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
@@ -42055,7 +42055,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>26/27 SH/A 74</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
@@ -42305,7 +42305,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>26/27 SH/A 76</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
@@ -42465,7 +42465,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>26/27 sh/a 78</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
@@ -42550,7 +42550,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>26/27 Sh/A79</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
@@ -42785,7 +42785,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>25/26 sh/a 385</t>
+          <t>385</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
@@ -43100,7 +43100,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 159</t>
+          <t>159</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
@@ -43185,7 +43185,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>25/26 SH/A 177</t>
+          <t>177</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
@@ -43650,7 +43650,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>26/27 Sh/A94</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
@@ -43885,7 +43885,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>26/27 SH/A 98</t>
+          <t>98</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
@@ -44050,7 +44050,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>26/27 sh/a 100</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
@@ -44295,7 +44295,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>26/27 Sh/A 103</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
@@ -44470,7 +44470,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>26/27 SH/A105</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
@@ -44555,7 +44555,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>26/27 SH/A106</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
@@ -44640,7 +44640,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>25/26 SH/A 229</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
@@ -45200,7 +45200,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>26/27 Sh/A114</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -45915,7 +45915,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>26/27 SH/A123</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
@@ -46000,7 +46000,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>26/27 SH/A174</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
@@ -46085,7 +46085,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>26/37 SH/A 125</t>
+          <t>125</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
@@ -46730,7 +46730,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>25/26 SH/A 264</t>
+          <t>264</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
@@ -46960,7 +46960,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 266</t>
+          <t>266</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -47045,7 +47045,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>25/26 SH/A 272</t>
+          <t>272</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -47210,7 +47210,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>25/26 SH/A 369</t>
+          <t>369</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -47750,7 +47750,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>26/27 sh/a 147</t>
+          <t>147</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
@@ -47840,7 +47840,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>25/26 SH/A 263</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -48075,7 +48075,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 260</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
@@ -48235,7 +48235,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>26/27 SH/A153</t>
+          <t>153</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
@@ -48395,7 +48395,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>26/27 sh/a 155</t>
+          <t>155</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
@@ -48865,7 +48865,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>26/27 SH/A 161</t>
+          <t>161</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -49180,7 +49180,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>26/27 Sh/A165</t>
+          <t>165</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
@@ -49340,7 +49340,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>25/26 Sh/A246</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
@@ -49655,7 +49655,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>25/26 SH/A 338</t>
+          <t>338</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>26/27 SH/A178</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
@@ -50365,7 +50365,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>26/27 sh/a 180</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -50750,7 +50750,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>25/26 Sh/A367</t>
+          <t>367</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -50840,7 +50840,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>25/26 SH/A 375</t>
+          <t>375</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
@@ -51250,7 +51250,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>25/26 sh/a 333</t>
+          <t>333</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
@@ -51330,7 +51330,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>25/26 sh/a 33</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
@@ -51740,7 +51740,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>25/26 SH/A358</t>
+          <t>358</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
@@ -52065,7 +52065,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>25/26 Sh/A361</t>
+          <t>361</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
@@ -52305,7 +52305,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>25/26 Sh/A 346</t>
+          <t>346</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
@@ -52385,7 +52385,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>25/26 Sh/A365</t>
+          <t>365</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
@@ -52720,7 +52720,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>25/26 SH/A 372</t>
+          <t>372</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
@@ -53285,7 +53285,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>25/26 SH/A 511</t>
+          <t>511</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
@@ -53558,7 +53558,6 @@
           <t>UM 03752398</t>
         </is>
       </c>
-      <c r="P564" t="inlineStr"/>
       <c r="Q564" t="inlineStr">
         <is>
           <t>13-sonli umumiy o'rta ta'lim maktabi</t>
@@ -53574,7 +53573,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="T564" t="inlineStr"/>
       <c r="U564" t="inlineStr">
         <is>
           <t>TOPILDI</t>
